--- a/data/research/npb.xlsx
+++ b/data/research/npb.xlsx
@@ -12,7 +12,6 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Picks'!$A$1:$CO$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Picks'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -21,9 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.0###"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -37,6 +38,11 @@
       <name val="Aptos"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="001F2937"/>
       <sz val="10"/>
     </font>
     <font>
@@ -67,11 +73,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <color rgb="001F2937"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Aptos"/>
@@ -135,61 +136,61 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -197,6 +198,30 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -272,6 +297,108 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO4" headerRowCount="1">
+  <autoFilter ref="A1:CO4"/>
+  <tableColumns count="93">
+    <tableColumn id="1" name="pick_id"/>
+    <tableColumn id="2" name="created_at_utc"/>
+    <tableColumn id="3" name="event_start_utc"/>
+    <tableColumn id="4" name="event_id"/>
+    <tableColumn id="5" name="league"/>
+    <tableColumn id="6" name="away_team"/>
+    <tableColumn id="7" name="home_team"/>
+    <tableColumn id="8" name="market_type"/>
+    <tableColumn id="9" name="selection"/>
+    <tableColumn id="10" name="line"/>
+    <tableColumn id="11" name="sportsbook"/>
+    <tableColumn id="12" name="american_odds"/>
+    <tableColumn id="13" name="decimal_odds"/>
+    <tableColumn id="14" name="market_implied_probability"/>
+    <tableColumn id="15" name="model_probability"/>
+    <tableColumn id="16" name="model_uncertainty"/>
+    <tableColumn id="17" name="edge"/>
+    <tableColumn id="18" name="confidence_score"/>
+    <tableColumn id="19" name="units"/>
+    <tableColumn id="20" name="model_version"/>
+    <tableColumn id="21" name="status"/>
+    <tableColumn id="22" name="result"/>
+    <tableColumn id="23" name="away_score"/>
+    <tableColumn id="24" name="home_score"/>
+    <tableColumn id="25" name="closing_line"/>
+    <tableColumn id="26" name="closing_american_odds"/>
+    <tableColumn id="27" name="closing_implied_probability"/>
+    <tableColumn id="28" name="probability_clv"/>
+    <tableColumn id="29" name="pnl_units"/>
+    <tableColumn id="30" name="settled_at_utc"/>
+    <tableColumn id="31" name="rationale"/>
+    <tableColumn id="32" name="risks"/>
+    <tableColumn id="33" name="review_status"/>
+    <tableColumn id="34" name="loss_classification"/>
+    <tableColumn id="35" name="loss_cause"/>
+    <tableColumn id="36" name="corrective_action"/>
+    <tableColumn id="37" name="call_type"/>
+    <tableColumn id="38" name="ledger_schema_version"/>
+    <tableColumn id="39" name="record_type"/>
+    <tableColumn id="40" name="decision"/>
+    <tableColumn id="41" name="reason_code"/>
+    <tableColumn id="42" name="canonical_away_team_id"/>
+    <tableColumn id="43" name="canonical_away_team_name"/>
+    <tableColumn id="44" name="original_away_team"/>
+    <tableColumn id="45" name="canonical_home_team_id"/>
+    <tableColumn id="46" name="canonical_home_team_name"/>
+    <tableColumn id="47" name="original_home_team"/>
+    <tableColumn id="48" name="banned_team_id"/>
+    <tableColumn id="49" name="banned_team_name"/>
+    <tableColumn id="50" name="model_origin"/>
+    <tableColumn id="51" name="baseline_identifier"/>
+    <tableColumn id="52" name="model_state_at_decision"/>
+    <tableColumn id="53" name="model_artifact_hash"/>
+    <tableColumn id="54" name="calibration_method"/>
+    <tableColumn id="55" name="calibration_version"/>
+    <tableColumn id="56" name="calibration_artifact_hash"/>
+    <tableColumn id="57" name="feature_schema_version"/>
+    <tableColumn id="58" name="entity_map_version"/>
+    <tableColumn id="59" name="code_revision"/>
+    <tableColumn id="60" name="observed_at_utc"/>
+    <tableColumn id="61" name="correlation_tags"/>
+    <tableColumn id="62" name="decision_line"/>
+    <tableColumn id="63" name="decision_american_odds"/>
+    <tableColumn id="64" name="decision_decimal_odds"/>
+    <tableColumn id="65" name="decision_raw_implied_probability"/>
+    <tableColumn id="66" name="decision_no_vig_probability"/>
+    <tableColumn id="67" name="decision_consensus_probability"/>
+    <tableColumn id="68" name="decision_consensus_line"/>
+    <tableColumn id="69" name="closing_decimal_odds"/>
+    <tableColumn id="70" name="closing_raw_implied_probability"/>
+    <tableColumn id="71" name="closing_no_vig_probability"/>
+    <tableColumn id="72" name="closing_consensus_probability"/>
+    <tableColumn id="73" name="closing_consensus_line"/>
+    <tableColumn id="74" name="legacy_units"/>
+    <tableColumn id="75" name="void_reason"/>
+    <tableColumn id="76" name="research_score_units"/>
+    <tableColumn id="77" name="research_pnl_units"/>
+    <tableColumn id="78" name="research_scored_at_utc"/>
+    <tableColumn id="79" name="research_scoring_note"/>
+    <tableColumn id="80" name="migrated_from_version"/>
+    <tableColumn id="81" name="elo_probability"/>
+    <tableColumn id="82" name="trend_gap"/>
+    <tableColumn id="83" name="park_factor"/>
+    <tableColumn id="84" name="weather_factor"/>
+    <tableColumn id="85" name="pitcher_era_gap"/>
+    <tableColumn id="86" name="probable_starter_era_gap"/>
+    <tableColumn id="87" name="unavailable_features"/>
+    <tableColumn id="88" name="defensive_trend_gap"/>
+    <tableColumn id="89" name="neutral_elo_rating_difference"/>
+    <tableColumn id="90" name="rest_disparity"/>
+    <tableColumn id="91" name="back_to_back_gap"/>
+    <tableColumn id="92" name="games_last_7_gap"/>
+    <tableColumn id="93" name="schedule_missingness"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -625,19 +752,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$2)</f>
+        <f>COUNTA('Picks'!$A$2:$A$4)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$2,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$4,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$4,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")+COUNTIFS('Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$4,"settled",'Picks'!$V$2:$V$4,"win")+COUNTIFS('Picks'!$U$2:$U$4,"settled",'Picks'!$V$2:$V$4,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -665,19 +792,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$2,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$4,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$4,"&gt;0",'Picks'!$V$2:$V$4,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$4,"&gt;0",'Picks'!$V$2:$V$4,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"win")/(COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"win")+COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$4,"&gt;0",'Picks'!$V$2:$V$4,"win")/(COUNTIFS('Picks'!$BX$2:$BX$4,"&gt;0",'Picks'!$V$2:$V$4,"win")+COUNTIFS('Picks'!$BX$2:$BX$4,"&gt;0",'Picks'!$V$2:$V$4,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$2)/SUM('Picks'!$BX$2:$BX$2),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$4)/SUM('Picks'!$BX$2:$BX$4),0)</f>
         <v/>
       </c>
     </row>
@@ -705,19 +832,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$2)</f>
+        <f>SUM('Picks'!$BY$2:$BY$4)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$2,"&lt;&gt;",'Picks'!$AB$2:$AB$2),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$4,"&lt;&gt;",'Picks'!$AB$2:$AB$4),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$2,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$4,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$4,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$2,'Picks'!$AM$2:$AM$2,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$4,'Picks'!$AM$2:$AM$4,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -772,15 +899,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$4,$A14,'Picks'!$U$2:$U$4,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$4,$A14,'Picks'!$U$2:$U$4,"settled",'Picks'!$V$2:$V$4,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$4,$A14,'Picks'!$U$2:$U$4,"settled",'Picks'!$V$2:$V$4,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -788,11 +915,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$2,'Picks'!$H$2:$H$2,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$4,'Picks'!$H$2:$H$4,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$2,'Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$4,'Picks'!$H$2:$H$4,$A14,'Picks'!$U$2:$U$4,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -803,15 +930,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$4,$A15,'Picks'!$U$2:$U$4,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$4,$A15,'Picks'!$U$2:$U$4,"settled",'Picks'!$V$2:$V$4,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$4,$A15,'Picks'!$U$2:$U$4,"settled",'Picks'!$V$2:$V$4,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -819,11 +946,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$2,'Picks'!$H$2:$H$2,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$4,'Picks'!$H$2:$H$4,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$2,'Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$4,'Picks'!$H$2:$H$4,$A15,'Picks'!$U$2:$U$4,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -834,15 +961,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$4,$A16,'Picks'!$U$2:$U$4,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$4,$A16,'Picks'!$U$2:$U$4,"settled",'Picks'!$V$2:$V$4,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$4,$A16,'Picks'!$U$2:$U$4,"settled",'Picks'!$V$2:$V$4,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -850,11 +977,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$2,'Picks'!$H$2:$H$2,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$4,'Picks'!$H$2:$H$4,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$2,'Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$4,'Picks'!$H$2:$H$4,$A16,'Picks'!$U$2:$U$4,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -883,7 +1010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO1"/>
+  <dimension ref="A1:CO4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1448,9 +1575,794 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>3a2fbe541260425f</t>
+        </is>
+      </c>
+      <c r="B2" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:17:16.064524Z</t>
+        </is>
+      </c>
+      <c r="C2" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D2" s="24" t="inlineStr">
+        <is>
+          <t>66797</t>
+        </is>
+      </c>
+      <c r="E2" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F2" s="24" t="inlineStr">
+        <is>
+          <t>Orix Buffaloes</t>
+        </is>
+      </c>
+      <c r="G2" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="H2" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I2" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J2" s="25" t="n"/>
+      <c r="K2" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L2" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="M2" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="N2" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="O2" s="28" t="n">
+        <v>0.598142</v>
+      </c>
+      <c r="P2" s="28" t="n"/>
+      <c r="Q2" s="28" t="n">
+        <v>-0.011233</v>
+      </c>
+      <c r="R2" s="26" t="n">
+        <v>14</v>
+      </c>
+      <c r="S2" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T2" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U2" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V2" s="24" t="n"/>
+      <c r="W2" s="26" t="n"/>
+      <c r="X2" s="26" t="n"/>
+      <c r="Y2" s="25" t="n"/>
+      <c r="Z2" s="26" t="n"/>
+      <c r="AA2" s="28" t="n"/>
+      <c r="AB2" s="28" t="n"/>
+      <c r="AC2" s="30" t="n"/>
+      <c r="AD2" s="24" t="n"/>
+      <c r="AE2" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6100 (market_slug=aec-npb-ssl-obr-2026-08-02). Tie probability=0.0279.</t>
+        </is>
+      </c>
+      <c r="AF2" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG2" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH2" s="24" t="n"/>
+      <c r="AI2" s="31" t="n"/>
+      <c r="AJ2" s="31" t="n"/>
+      <c r="AK2" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL2" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM2" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN2" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO2" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP2" s="24" t="inlineStr">
+        <is>
+          <t>Orix Buffaloes</t>
+        </is>
+      </c>
+      <c r="AQ2" s="24" t="inlineStr">
+        <is>
+          <t>Orix Buffaloes</t>
+        </is>
+      </c>
+      <c r="AR2" s="24" t="inlineStr">
+        <is>
+          <t>Orix Buffaloes</t>
+        </is>
+      </c>
+      <c r="AS2" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AT2" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AU2" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AV2" s="24" t="n"/>
+      <c r="AW2" s="24" t="n"/>
+      <c r="AX2" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY2" s="24" t="n"/>
+      <c r="AZ2" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA2" s="24" t="inlineStr">
+        <is>
+          <t>7bc7902a4eb8ef0d1e3f86c086eab30d4166d1bb4c513506b84d49652b442bb9</t>
+        </is>
+      </c>
+      <c r="BB2" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC2" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD2" s="24" t="inlineStr">
+        <is>
+          <t>7bc7902a4eb8ef0d1e3f86c086eab30d4166d1bb4c513506b84d49652b442bb9</t>
+        </is>
+      </c>
+      <c r="BE2" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF2" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG2" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH2" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:17:15.048364Z</t>
+        </is>
+      </c>
+      <c r="BI2" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ2" s="25" t="n"/>
+      <c r="BK2" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="BL2" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BM2" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="BN2" s="28" t="n"/>
+      <c r="BO2" s="28" t="n"/>
+      <c r="BP2" s="25" t="n"/>
+      <c r="BQ2" s="27" t="n"/>
+      <c r="BR2" s="28" t="n"/>
+      <c r="BS2" s="28" t="n"/>
+      <c r="BT2" s="28" t="n"/>
+      <c r="BU2" s="25" t="n"/>
+      <c r="BV2" s="29" t="n"/>
+      <c r="BW2" s="24" t="n"/>
+      <c r="BX2" s="30" t="n"/>
+      <c r="BY2" s="27" t="n"/>
+      <c r="BZ2" s="24" t="n"/>
+      <c r="CA2" s="31" t="n"/>
+      <c r="CB2" s="24" t="n"/>
+      <c r="CC2" s="24" t="n"/>
+      <c r="CD2" s="24" t="n"/>
+      <c r="CE2" s="24" t="n"/>
+      <c r="CF2" s="24" t="n"/>
+      <c r="CG2" s="24" t="n"/>
+      <c r="CH2" s="24" t="n"/>
+      <c r="CI2" s="24" t="n"/>
+      <c r="CJ2" s="24" t="n"/>
+      <c r="CK2" s="24" t="n"/>
+      <c r="CL2" s="24" t="n"/>
+      <c r="CM2" s="24" t="n"/>
+      <c r="CN2" s="24" t="n"/>
+      <c r="CO2" s="24" t="n"/>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>34e57813cfe44538</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:17:16.064524Z</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D3" s="24" t="inlineStr">
+        <is>
+          <t>66805</t>
+        </is>
+      </c>
+      <c r="E3" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F3" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="G3" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="H3" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I3" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L3" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="M3" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="N3" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="O3" s="28" t="n">
+        <v>0.589889</v>
+      </c>
+      <c r="P3" s="28" t="n"/>
+      <c r="Q3" s="28" t="n">
+        <v>-0.019486</v>
+      </c>
+      <c r="R3" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="S3" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T3" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U3" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V3" s="24" t="n"/>
+      <c r="W3" s="26" t="n"/>
+      <c r="X3" s="26" t="n"/>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="26" t="n"/>
+      <c r="AA3" s="28" t="n"/>
+      <c r="AB3" s="28" t="n"/>
+      <c r="AC3" s="30" t="n"/>
+      <c r="AD3" s="24" t="n"/>
+      <c r="AE3" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6100 (market_slug=aec-npb-tys-hta-2026-08-02). Tie probability=0.0287.</t>
+        </is>
+      </c>
+      <c r="AF3" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG3" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH3" s="24" t="n"/>
+      <c r="AI3" s="31" t="n"/>
+      <c r="AJ3" s="31" t="n"/>
+      <c r="AK3" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM3" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN3" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO3" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP3" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AQ3" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AR3" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AS3" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AT3" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AU3" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AV3" s="24" t="n"/>
+      <c r="AW3" s="24" t="n"/>
+      <c r="AX3" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY3" s="24" t="n"/>
+      <c r="AZ3" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA3" s="24" t="inlineStr">
+        <is>
+          <t>7bc7902a4eb8ef0d1e3f86c086eab30d4166d1bb4c513506b84d49652b442bb9</t>
+        </is>
+      </c>
+      <c r="BB3" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC3" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD3" s="24" t="inlineStr">
+        <is>
+          <t>7bc7902a4eb8ef0d1e3f86c086eab30d4166d1bb4c513506b84d49652b442bb9</t>
+        </is>
+      </c>
+      <c r="BE3" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF3" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG3" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH3" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:17:15.586699Z</t>
+        </is>
+      </c>
+      <c r="BI3" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ3" s="25" t="n"/>
+      <c r="BK3" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="BL3" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BM3" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="BN3" s="28" t="n"/>
+      <c r="BO3" s="28" t="n"/>
+      <c r="BP3" s="25" t="n"/>
+      <c r="BQ3" s="27" t="n"/>
+      <c r="BR3" s="28" t="n"/>
+      <c r="BS3" s="28" t="n"/>
+      <c r="BT3" s="28" t="n"/>
+      <c r="BU3" s="25" t="n"/>
+      <c r="BV3" s="29" t="n"/>
+      <c r="BW3" s="24" t="n"/>
+      <c r="BX3" s="30" t="n"/>
+      <c r="BY3" s="27" t="n"/>
+      <c r="BZ3" s="24" t="n"/>
+      <c r="CA3" s="31" t="n"/>
+      <c r="CB3" s="24" t="n"/>
+      <c r="CC3" s="24" t="n"/>
+      <c r="CD3" s="24" t="n"/>
+      <c r="CE3" s="24" t="n"/>
+      <c r="CF3" s="24" t="n"/>
+      <c r="CG3" s="24" t="n"/>
+      <c r="CH3" s="24" t="n"/>
+      <c r="CI3" s="24" t="n"/>
+      <c r="CJ3" s="24" t="n"/>
+      <c r="CK3" s="24" t="n"/>
+      <c r="CL3" s="24" t="n"/>
+      <c r="CM3" s="24" t="n"/>
+      <c r="CN3" s="24" t="n"/>
+      <c r="CO3" s="24" t="n"/>
+    </row>
+    <row r="4" ht="36" customHeight="1">
+      <c r="A4" s="24" t="inlineStr">
+        <is>
+          <t>44671e3eb66b45e5</t>
+        </is>
+      </c>
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:17:16.064524Z</t>
+        </is>
+      </c>
+      <c r="C4" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>66806</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F4" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="G4" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="H4" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I4" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L4" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M4" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="N4" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="O4" s="28" t="n">
+        <v>0.516289</v>
+      </c>
+      <c r="P4" s="28" t="n"/>
+      <c r="Q4" s="28" t="n">
+        <v>-0.002942</v>
+      </c>
+      <c r="R4" s="26" t="n">
+        <v>19</v>
+      </c>
+      <c r="S4" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U4" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V4" s="24" t="n"/>
+      <c r="W4" s="26" t="n"/>
+      <c r="X4" s="26" t="n"/>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="26" t="n"/>
+      <c r="AA4" s="28" t="n"/>
+      <c r="AB4" s="28" t="n"/>
+      <c r="AC4" s="30" t="n"/>
+      <c r="AD4" s="24" t="n"/>
+      <c r="AE4" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5200 (market_slug=aec-npb-hci-cdh-2026-08-02). Tie probability=0.0352.</t>
+        </is>
+      </c>
+      <c r="AF4" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG4" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH4" s="24" t="n"/>
+      <c r="AI4" s="31" t="n"/>
+      <c r="AJ4" s="31" t="n"/>
+      <c r="AK4" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL4" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM4" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN4" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO4" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP4" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="AQ4" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="AR4" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="AS4" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="AT4" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="AU4" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="AV4" s="24" t="n"/>
+      <c r="AW4" s="24" t="n"/>
+      <c r="AX4" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY4" s="24" t="n"/>
+      <c r="AZ4" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA4" s="24" t="inlineStr">
+        <is>
+          <t>7bc7902a4eb8ef0d1e3f86c086eab30d4166d1bb4c513506b84d49652b442bb9</t>
+        </is>
+      </c>
+      <c r="BB4" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC4" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD4" s="24" t="inlineStr">
+        <is>
+          <t>7bc7902a4eb8ef0d1e3f86c086eab30d4166d1bb4c513506b84d49652b442bb9</t>
+        </is>
+      </c>
+      <c r="BE4" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF4" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG4" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH4" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T07:17:16.064370Z</t>
+        </is>
+      </c>
+      <c r="BI4" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ4" s="25" t="n"/>
+      <c r="BK4" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="BL4" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="BM4" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="BN4" s="28" t="n"/>
+      <c r="BO4" s="28" t="n"/>
+      <c r="BP4" s="25" t="n"/>
+      <c r="BQ4" s="27" t="n"/>
+      <c r="BR4" s="28" t="n"/>
+      <c r="BS4" s="28" t="n"/>
+      <c r="BT4" s="28" t="n"/>
+      <c r="BU4" s="25" t="n"/>
+      <c r="BV4" s="29" t="n"/>
+      <c r="BW4" s="24" t="n"/>
+      <c r="BX4" s="30" t="n"/>
+      <c r="BY4" s="27" t="n"/>
+      <c r="BZ4" s="24" t="n"/>
+      <c r="CA4" s="31" t="n"/>
+      <c r="CB4" s="24" t="n"/>
+      <c r="CC4" s="24" t="n"/>
+      <c r="CD4" s="24" t="n"/>
+      <c r="CE4" s="24" t="n"/>
+      <c r="CF4" s="24" t="n"/>
+      <c r="CG4" s="24" t="n"/>
+      <c r="CH4" s="24" t="n"/>
+      <c r="CI4" s="24" t="n"/>
+      <c r="CJ4" s="24" t="n"/>
+      <c r="CK4" s="24" t="n"/>
+      <c r="CL4" s="24" t="n"/>
+      <c r="CM4" s="24" t="n"/>
+      <c r="CN4" s="24" t="n"/>
+      <c r="CO4" s="24" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:CO1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/data/research/npb.xlsx
+++ b/data/research/npb.xlsx
@@ -1839,12 +1839,12 @@
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
         <is>
-          <t>34e57813cfe44538</t>
+          <t>410262d0c1934015</t>
         </is>
       </c>
       <c r="B3" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:17:16.064524Z</t>
+          <t>2026-08-02T08:20:42.087614Z</t>
         </is>
       </c>
       <c r="C3" s="24" t="inlineStr">
@@ -2015,7 +2015,7 @@
       </c>
       <c r="BA3" s="24" t="inlineStr">
         <is>
-          <t>7bc7902a4eb8ef0d1e3f86c086eab30d4166d1bb4c513506b84d49652b442bb9</t>
+          <t>2a6cf3b60204b321f39347f04e6fe642c4fbe02fc5d69a03243771cd77d85043</t>
         </is>
       </c>
       <c r="BB3" s="24" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="BD3" s="24" t="inlineStr">
         <is>
-          <t>7bc7902a4eb8ef0d1e3f86c086eab30d4166d1bb4c513506b84d49652b442bb9</t>
+          <t>2a6cf3b60204b321f39347f04e6fe642c4fbe02fc5d69a03243771cd77d85043</t>
         </is>
       </c>
       <c r="BE3" s="24" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="BH3" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:17:15.586699Z</t>
+          <t>2026-08-02T08:20:41.605573Z</t>
         </is>
       </c>
       <c r="BI3" s="24" t="inlineStr">
@@ -2100,12 +2100,12 @@
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
         <is>
-          <t>44671e3eb66b45e5</t>
+          <t>45e1046342e5401e</t>
         </is>
       </c>
       <c r="B4" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:17:16.064524Z</t>
+          <t>2026-08-02T08:20:42.087614Z</t>
         </is>
       </c>
       <c r="C4" s="24" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="BA4" s="24" t="inlineStr">
         <is>
-          <t>7bc7902a4eb8ef0d1e3f86c086eab30d4166d1bb4c513506b84d49652b442bb9</t>
+          <t>2a6cf3b60204b321f39347f04e6fe642c4fbe02fc5d69a03243771cd77d85043</t>
         </is>
       </c>
       <c r="BB4" s="24" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="BD4" s="24" t="inlineStr">
         <is>
-          <t>7bc7902a4eb8ef0d1e3f86c086eab30d4166d1bb4c513506b84d49652b442bb9</t>
+          <t>2a6cf3b60204b321f39347f04e6fe642c4fbe02fc5d69a03243771cd77d85043</t>
         </is>
       </c>
       <c r="BE4" s="24" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="BH4" s="24" t="inlineStr">
         <is>
-          <t>2026-08-02T07:17:16.064370Z</t>
+          <t>2026-08-02T08:20:42.087439Z</t>
         </is>
       </c>
       <c r="BI4" s="24" t="inlineStr">

--- a/data/research/npb.xlsx
+++ b/data/research/npb.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CO4" headerRowCount="1">
-  <autoFilter ref="A1:CO4"/>
-  <tableColumns count="93">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CP4" headerRowCount="1">
+  <autoFilter ref="A1:CP4"/>
+  <tableColumns count="94">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -396,6 +396,7 @@
     <tableColumn id="91" name="back_to_back_gap"/>
     <tableColumn id="92" name="games_last_7_gap"/>
     <tableColumn id="93" name="schedule_missingness"/>
+    <tableColumn id="94" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1010,7 +1011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO4"/>
+  <dimension ref="A1:CP4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1106,6 +1107,7 @@
     <col width="18" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
     <col width="22" customWidth="1" min="93" max="93"/>
+    <col width="17" customWidth="1" min="94" max="94"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1572,6 +1574,11 @@
       <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
+        </is>
+      </c>
+      <c r="CP1" s="23" t="inlineStr">
+        <is>
+          <t>trade_candidate</t>
         </is>
       </c>
     </row>
@@ -1835,6 +1842,7 @@
       <c r="CM2" s="24" t="n"/>
       <c r="CN2" s="24" t="n"/>
       <c r="CO2" s="24" t="n"/>
+      <c r="CP2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2096,6 +2104,7 @@
       <c r="CM3" s="24" t="n"/>
       <c r="CN3" s="24" t="n"/>
       <c r="CO3" s="24" t="n"/>
+      <c r="CP3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2357,6 +2366,7 @@
       <c r="CM4" s="24" t="n"/>
       <c r="CN4" s="24" t="n"/>
       <c r="CO4" s="24" t="n"/>
+      <c r="CP4" s="24" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/research/npb.xlsx
+++ b/data/research/npb.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CP4" headerRowCount="1">
-  <autoFilter ref="A1:CP4"/>
-  <tableColumns count="94">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ4" headerRowCount="1">
+  <autoFilter ref="A1:CQ4"/>
+  <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -396,7 +396,8 @@
     <tableColumn id="91" name="back_to_back_gap"/>
     <tableColumn id="92" name="games_last_7_gap"/>
     <tableColumn id="93" name="schedule_missingness"/>
-    <tableColumn id="94" name="trade_candidate"/>
+    <tableColumn id="94" name="market_residual_probability"/>
+    <tableColumn id="95" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1011,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CP4"/>
+  <dimension ref="A1:CQ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1107,7 +1108,8 @@
     <col width="18" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
     <col width="22" customWidth="1" min="93" max="93"/>
-    <col width="17" customWidth="1" min="94" max="94"/>
+    <col width="22" customWidth="1" min="94" max="94"/>
+    <col width="17" customWidth="1" min="95" max="95"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1577,6 +1579,11 @@
         </is>
       </c>
       <c r="CP1" s="23" t="inlineStr">
+        <is>
+          <t>market_residual_probability</t>
+        </is>
+      </c>
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1843,6 +1850,7 @@
       <c r="CN2" s="24" t="n"/>
       <c r="CO2" s="24" t="n"/>
       <c r="CP2" s="24" t="n"/>
+      <c r="CQ2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2105,6 +2113,7 @@
       <c r="CN3" s="24" t="n"/>
       <c r="CO3" s="24" t="n"/>
       <c r="CP3" s="24" t="n"/>
+      <c r="CQ3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2367,6 +2376,7 @@
       <c r="CN4" s="24" t="n"/>
       <c r="CO4" s="24" t="n"/>
       <c r="CP4" s="24" t="n"/>
+      <c r="CQ4" s="24" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/research/npb.xlsx
+++ b/data/research/npb.xlsx
@@ -1670,18 +1670,32 @@
       </c>
       <c r="U2" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V2" s="24" t="n"/>
-      <c r="W2" s="26" t="n"/>
-      <c r="X2" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V2" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W2" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" s="26" t="n">
+        <v>5</v>
+      </c>
       <c r="Y2" s="25" t="n"/>
       <c r="Z2" s="26" t="n"/>
       <c r="AA2" s="28" t="n"/>
       <c r="AB2" s="28" t="n"/>
-      <c r="AC2" s="30" t="n"/>
-      <c r="AD2" s="24" t="n"/>
+      <c r="AC2" s="30" t="n">
+        <v>0.8013</v>
+      </c>
+      <c r="AD2" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:19:02.727428Z</t>
+        </is>
+      </c>
       <c r="AE2" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.6100 (market_slug=aec-npb-ssl-obr-2026-08-02). Tie probability=0.0279.</t>
@@ -1933,18 +1947,32 @@
       </c>
       <c r="U3" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V3" s="24" t="n"/>
-      <c r="W3" s="26" t="n"/>
-      <c r="X3" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V3" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W3" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="X3" s="26" t="n">
+        <v>3</v>
+      </c>
       <c r="Y3" s="25" t="n"/>
       <c r="Z3" s="26" t="n"/>
       <c r="AA3" s="28" t="n"/>
       <c r="AB3" s="28" t="n"/>
-      <c r="AC3" s="30" t="n"/>
-      <c r="AD3" s="24" t="n"/>
+      <c r="AC3" s="30" t="n">
+        <v>0.8013</v>
+      </c>
+      <c r="AD3" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:19:02.786059Z</t>
+        </is>
+      </c>
       <c r="AE3" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.6100 (market_slug=aec-npb-tys-hta-2026-08-02). Tie probability=0.0287.</t>
@@ -2196,18 +2224,32 @@
       </c>
       <c r="U4" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V4" s="24" t="n"/>
-      <c r="W4" s="26" t="n"/>
-      <c r="X4" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V4" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W4" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" s="26" t="n">
+        <v>4</v>
+      </c>
       <c r="Y4" s="25" t="n"/>
       <c r="Z4" s="26" t="n"/>
       <c r="AA4" s="28" t="n"/>
       <c r="AB4" s="28" t="n"/>
-      <c r="AC4" s="30" t="n"/>
-      <c r="AD4" s="24" t="n"/>
+      <c r="AC4" s="30" t="n">
+        <v>0.9258999999999999</v>
+      </c>
+      <c r="AD4" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-02T18:19:02.832015Z</t>
+        </is>
+      </c>
       <c r="AE4" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.5200 (market_slug=aec-npb-hci-cdh-2026-08-02). Tie probability=0.0352.</t>

--- a/data/research/npb.xlsx
+++ b/data/research/npb.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ4" headerRowCount="1">
-  <autoFilter ref="A1:CQ4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ5" headerRowCount="1">
+  <autoFilter ref="A1:CQ5"/>
   <tableColumns count="95">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -754,19 +754,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$4)</f>
+        <f>COUNTA('Picks'!$A$2:$A$5)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$4,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$5,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$4,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$5,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$4,"settled",'Picks'!$V$2:$V$4,"win")+COUNTIFS('Picks'!$U$2:$U$4,"settled",'Picks'!$V$2:$V$4,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")+COUNTIFS('Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +794,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$4,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$5,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$4,"&gt;0",'Picks'!$V$2:$V$4,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$4,"&gt;0",'Picks'!$V$2:$V$4,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$4,"&gt;0",'Picks'!$V$2:$V$4,"win")/(COUNTIFS('Picks'!$BX$2:$BX$4,"&gt;0",'Picks'!$V$2:$V$4,"win")+COUNTIFS('Picks'!$BX$2:$BX$4,"&gt;0",'Picks'!$V$2:$V$4,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"win")/(COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"win")+COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$4)/SUM('Picks'!$BX$2:$BX$4),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$5)/SUM('Picks'!$BX$2:$BX$5),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +834,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$4)</f>
+        <f>SUM('Picks'!$BY$2:$BY$5)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$4,"&lt;&gt;",'Picks'!$AB$2:$AB$4),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$5,"&lt;&gt;",'Picks'!$AB$2:$AB$5),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$4,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$4,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$5,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$5,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$4,'Picks'!$AM$2:$AM$4,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$5,'Picks'!$AM$2:$AM$5,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +901,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$4,$A14,'Picks'!$U$2:$U$4,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$4,$A14,'Picks'!$U$2:$U$4,"settled",'Picks'!$V$2:$V$4,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$4,$A14,'Picks'!$U$2:$U$4,"settled",'Picks'!$V$2:$V$4,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +917,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$4,'Picks'!$H$2:$H$4,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$5,'Picks'!$H$2:$H$5,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$4,'Picks'!$H$2:$H$4,$A14,'Picks'!$U$2:$U$4,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$5,'Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +932,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$4,$A15,'Picks'!$U$2:$U$4,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$4,$A15,'Picks'!$U$2:$U$4,"settled",'Picks'!$V$2:$V$4,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$4,$A15,'Picks'!$U$2:$U$4,"settled",'Picks'!$V$2:$V$4,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +948,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$4,'Picks'!$H$2:$H$4,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$5,'Picks'!$H$2:$H$5,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$4,'Picks'!$H$2:$H$4,$A15,'Picks'!$U$2:$U$4,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$5,'Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +963,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$4,$A16,'Picks'!$U$2:$U$4,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$4,$A16,'Picks'!$U$2:$U$4,"settled",'Picks'!$V$2:$V$4,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$4,$A16,'Picks'!$U$2:$U$4,"settled",'Picks'!$V$2:$V$4,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +979,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$4,'Picks'!$H$2:$H$4,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$5,'Picks'!$H$2:$H$5,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$4,'Picks'!$H$2:$H$4,$A16,'Picks'!$U$2:$U$4,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$5,'Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ4"/>
+  <dimension ref="A1:CQ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2420,6 +2420,287 @@
       <c r="CP4" s="24" t="n"/>
       <c r="CQ4" s="24" t="n"/>
     </row>
+    <row r="5" ht="36" customHeight="1">
+      <c r="A5" s="24" t="inlineStr">
+        <is>
+          <t>e5ed76f20434451f</t>
+        </is>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T06:33:34.637203Z</t>
+        </is>
+      </c>
+      <c r="C5" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D5" s="24" t="inlineStr">
+        <is>
+          <t>67498</t>
+        </is>
+      </c>
+      <c r="E5" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F5" s="24" t="inlineStr">
+        <is>
+          <t>Tohoku Rakuten Golden Eagles</t>
+        </is>
+      </c>
+      <c r="G5" s="24" t="inlineStr">
+        <is>
+          <t>Orix Buffaloes</t>
+        </is>
+      </c>
+      <c r="H5" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I5" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L5" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="M5" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="N5" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="O5" s="28" t="n">
+        <v>0.550397</v>
+      </c>
+      <c r="P5" s="28" t="n"/>
+      <c r="Q5" s="28" t="n">
+        <v>0.000847</v>
+      </c>
+      <c r="R5" s="26" t="n">
+        <v>20</v>
+      </c>
+      <c r="S5" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U5" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V5" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W5" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="X5" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="26" t="n"/>
+      <c r="AA5" s="28" t="n"/>
+      <c r="AB5" s="28" t="n"/>
+      <c r="AC5" s="30" t="n">
+        <v>0.8197</v>
+      </c>
+      <c r="AD5" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T19:52:12.453085Z</t>
+        </is>
+      </c>
+      <c r="AE5" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5500 (market_slug=aec-npb-obr-trge-2026-08-03). Tie probability=0.0321.</t>
+        </is>
+      </c>
+      <c r="AF5" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG5" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH5" s="24" t="n"/>
+      <c r="AI5" s="31" t="n"/>
+      <c r="AJ5" s="31" t="n"/>
+      <c r="AK5" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL5" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM5" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN5" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO5" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP5" s="24" t="inlineStr">
+        <is>
+          <t>Tohoku Rakuten Golden Eagles</t>
+        </is>
+      </c>
+      <c r="AQ5" s="24" t="inlineStr">
+        <is>
+          <t>Tohoku Rakuten Golden Eagles</t>
+        </is>
+      </c>
+      <c r="AR5" s="24" t="inlineStr">
+        <is>
+          <t>Tohoku Rakuten Golden Eagles</t>
+        </is>
+      </c>
+      <c r="AS5" s="24" t="inlineStr">
+        <is>
+          <t>Orix Buffaloes</t>
+        </is>
+      </c>
+      <c r="AT5" s="24" t="inlineStr">
+        <is>
+          <t>Orix Buffaloes</t>
+        </is>
+      </c>
+      <c r="AU5" s="24" t="inlineStr">
+        <is>
+          <t>Orix Buffaloes</t>
+        </is>
+      </c>
+      <c r="AV5" s="24" t="n"/>
+      <c r="AW5" s="24" t="n"/>
+      <c r="AX5" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY5" s="24" t="n"/>
+      <c r="AZ5" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA5" s="24" t="inlineStr">
+        <is>
+          <t>fe60ea981cb60cbb4cd1f8007017436a9fb4fad2d99764931f7f0d7461cd4907</t>
+        </is>
+      </c>
+      <c r="BB5" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC5" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD5" s="24" t="inlineStr">
+        <is>
+          <t>fe60ea981cb60cbb4cd1f8007017436a9fb4fad2d99764931f7f0d7461cd4907</t>
+        </is>
+      </c>
+      <c r="BE5" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF5" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG5" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH5" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-03T06:33:34.636987Z</t>
+        </is>
+      </c>
+      <c r="BI5" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ5" s="25" t="n"/>
+      <c r="BK5" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="BL5" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="BM5" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="BN5" s="28" t="n"/>
+      <c r="BO5" s="28" t="n"/>
+      <c r="BP5" s="25" t="n"/>
+      <c r="BQ5" s="27" t="n"/>
+      <c r="BR5" s="28" t="n"/>
+      <c r="BS5" s="28" t="n"/>
+      <c r="BT5" s="28" t="n"/>
+      <c r="BU5" s="25" t="n"/>
+      <c r="BV5" s="29" t="n"/>
+      <c r="BW5" s="24" t="n"/>
+      <c r="BX5" s="30" t="n"/>
+      <c r="BY5" s="27" t="n"/>
+      <c r="BZ5" s="24" t="n"/>
+      <c r="CA5" s="31" t="n"/>
+      <c r="CB5" s="24" t="n"/>
+      <c r="CC5" s="24" t="n"/>
+      <c r="CD5" s="24" t="n"/>
+      <c r="CE5" s="24" t="n"/>
+      <c r="CF5" s="24" t="n"/>
+      <c r="CG5" s="24" t="n"/>
+      <c r="CH5" s="24" t="n"/>
+      <c r="CI5" s="24" t="n"/>
+      <c r="CJ5" s="24" t="n"/>
+      <c r="CK5" s="24" t="n"/>
+      <c r="CL5" s="24" t="n"/>
+      <c r="CM5" s="24" t="n"/>
+      <c r="CN5" s="24" t="n"/>
+      <c r="CO5" s="24" t="n"/>
+      <c r="CP5" s="24" t="n"/>
+      <c r="CQ5" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/npb.xlsx
+++ b/data/research/npb.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CQ5" headerRowCount="1">
-  <autoFilter ref="A1:CQ5"/>
-  <tableColumns count="95">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CR10" headerRowCount="1">
+  <autoFilter ref="A1:CR10"/>
+  <tableColumns count="96">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -392,12 +392,13 @@
     <tableColumn id="87" name="unavailable_features"/>
     <tableColumn id="88" name="defensive_trend_gap"/>
     <tableColumn id="89" name="neutral_elo_rating_difference"/>
-    <tableColumn id="90" name="rest_disparity"/>
-    <tableColumn id="91" name="back_to_back_gap"/>
-    <tableColumn id="92" name="games_last_7_gap"/>
-    <tableColumn id="93" name="schedule_missingness"/>
-    <tableColumn id="94" name="market_residual_probability"/>
-    <tableColumn id="95" name="trade_candidate"/>
+    <tableColumn id="90" name="bullpen_weakness_gap"/>
+    <tableColumn id="91" name="rest_disparity"/>
+    <tableColumn id="92" name="back_to_back_gap"/>
+    <tableColumn id="93" name="games_last_7_gap"/>
+    <tableColumn id="94" name="schedule_missingness"/>
+    <tableColumn id="95" name="market_residual_probability"/>
+    <tableColumn id="96" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -754,19 +755,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$5)</f>
+        <f>COUNTA('Picks'!$A$2:$A$10)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$5,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$10,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$5,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$10,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")+COUNTIFS('Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")+COUNTIFS('Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -794,19 +795,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$5,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$10,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"win")/(COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"win")+COUNTIFS('Picks'!$BX$2:$BX$5,"&gt;0",'Picks'!$V$2:$V$5,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")/(COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")+COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$5)/SUM('Picks'!$BX$2:$BX$5),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$10)/SUM('Picks'!$BX$2:$BX$10),0)</f>
         <v/>
       </c>
     </row>
@@ -834,19 +835,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$5)</f>
+        <f>SUM('Picks'!$BY$2:$BY$10)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$5,"&lt;&gt;",'Picks'!$AB$2:$AB$5),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$10,"&lt;&gt;",'Picks'!$AB$2:$AB$10),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$5,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$5,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$10,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$10,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$5,'Picks'!$AM$2:$AM$5,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$10,'Picks'!$AM$2:$AM$10,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -901,15 +902,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -917,11 +918,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$5,'Picks'!$H$2:$H$5,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$5,'Picks'!$H$2:$H$5,$A14,'Picks'!$U$2:$U$5,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -932,15 +933,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -948,11 +949,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$5,'Picks'!$H$2:$H$5,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$5,'Picks'!$H$2:$H$5,$A15,'Picks'!$U$2:$U$5,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -963,15 +964,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled",'Picks'!$V$2:$V$5,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -979,11 +980,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$5,'Picks'!$H$2:$H$5,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$5,'Picks'!$H$2:$H$5,$A16,'Picks'!$U$2:$U$5,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1012,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ5"/>
+  <dimension ref="A1:CR10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1104,12 +1105,13 @@
     <col width="22" customWidth="1" min="87" max="87"/>
     <col width="21" customWidth="1" min="88" max="88"/>
     <col width="22" customWidth="1" min="89" max="89"/>
-    <col width="16" customWidth="1" min="90" max="90"/>
-    <col width="18" customWidth="1" min="91" max="91"/>
+    <col width="22" customWidth="1" min="90" max="90"/>
+    <col width="16" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
-    <col width="22" customWidth="1" min="93" max="93"/>
+    <col width="18" customWidth="1" min="93" max="93"/>
     <col width="22" customWidth="1" min="94" max="94"/>
-    <col width="17" customWidth="1" min="95" max="95"/>
+    <col width="22" customWidth="1" min="95" max="95"/>
+    <col width="17" customWidth="1" min="96" max="96"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1560,30 +1562,35 @@
       </c>
       <c r="CL1" s="23" t="inlineStr">
         <is>
+          <t>bullpen_weakness_gap</t>
+        </is>
+      </c>
+      <c r="CM1" s="23" t="inlineStr">
+        <is>
           <t>rest_disparity</t>
         </is>
       </c>
-      <c r="CM1" s="23" t="inlineStr">
+      <c r="CN1" s="23" t="inlineStr">
         <is>
           <t>back_to_back_gap</t>
         </is>
       </c>
-      <c r="CN1" s="23" t="inlineStr">
+      <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>games_last_7_gap</t>
         </is>
       </c>
-      <c r="CO1" s="23" t="inlineStr">
+      <c r="CP1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
         </is>
       </c>
-      <c r="CP1" s="23" t="inlineStr">
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>market_residual_probability</t>
         </is>
       </c>
-      <c r="CQ1" s="23" t="inlineStr">
+      <c r="CR1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1865,6 +1872,7 @@
       <c r="CO2" s="24" t="n"/>
       <c r="CP2" s="24" t="n"/>
       <c r="CQ2" s="24" t="n"/>
+      <c r="CR2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2142,6 +2150,7 @@
       <c r="CO3" s="24" t="n"/>
       <c r="CP3" s="24" t="n"/>
       <c r="CQ3" s="24" t="n"/>
+      <c r="CR3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2419,6 +2428,7 @@
       <c r="CO4" s="24" t="n"/>
       <c r="CP4" s="24" t="n"/>
       <c r="CQ4" s="24" t="n"/>
+      <c r="CR4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2695,9 +2705,1350 @@
       <c r="CN5" s="24" t="n"/>
       <c r="CO5" s="24" t="n"/>
       <c r="CP5" s="24" t="n"/>
-      <c r="CQ5" s="24" t="inlineStr">
+      <c r="CQ5" s="24" t="n"/>
+      <c r="CR5" s="24" t="inlineStr">
         <is>
           <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1">
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>835cd2f91e9447d0</t>
+        </is>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:17:41.271393Z</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:45:00Z</t>
+        </is>
+      </c>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>68272</t>
+        </is>
+      </c>
+      <c r="E6" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F6" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="G6" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="H6" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I6" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J6" s="25" t="n"/>
+      <c r="K6" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L6" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="M6" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="N6" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="O6" s="28" t="n">
+        <v>0.524037</v>
+      </c>
+      <c r="P6" s="28" t="n"/>
+      <c r="Q6" s="28" t="n">
+        <v>-0.095735</v>
+      </c>
+      <c r="R6" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U6" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V6" s="24" t="n"/>
+      <c r="W6" s="26" t="n"/>
+      <c r="X6" s="26" t="n"/>
+      <c r="Y6" s="25" t="n"/>
+      <c r="Z6" s="26" t="n"/>
+      <c r="AA6" s="28" t="n"/>
+      <c r="AB6" s="28" t="n"/>
+      <c r="AC6" s="30" t="n"/>
+      <c r="AD6" s="24" t="n"/>
+      <c r="AE6" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6200 (market_slug=aec-npb-ybo-hta-2026-08-04). Tie probability=0.0344.</t>
+        </is>
+      </c>
+      <c r="AF6" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG6" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH6" s="24" t="n"/>
+      <c r="AI6" s="31" t="n"/>
+      <c r="AJ6" s="31" t="n"/>
+      <c r="AK6" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL6" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM6" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN6" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO6" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP6" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AQ6" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AR6" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AS6" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AT6" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AU6" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AV6" s="24" t="n"/>
+      <c r="AW6" s="24" t="n"/>
+      <c r="AX6" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY6" s="24" t="n"/>
+      <c r="AZ6" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA6" s="24" t="inlineStr">
+        <is>
+          <t>6d6669d47bc91bfec82db00ad3cb5bea565b364709e20a7346cef2b95011e4a9</t>
+        </is>
+      </c>
+      <c r="BB6" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC6" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD6" s="24" t="inlineStr">
+        <is>
+          <t>6d6669d47bc91bfec82db00ad3cb5bea565b364709e20a7346cef2b95011e4a9</t>
+        </is>
+      </c>
+      <c r="BE6" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF6" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG6" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH6" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T05:17:38.867915Z</t>
+        </is>
+      </c>
+      <c r="BI6" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ6" s="25" t="n"/>
+      <c r="BK6" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="BL6" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="BM6" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="BN6" s="28" t="n"/>
+      <c r="BO6" s="28" t="n"/>
+      <c r="BP6" s="25" t="n"/>
+      <c r="BQ6" s="27" t="n"/>
+      <c r="BR6" s="28" t="n"/>
+      <c r="BS6" s="28" t="n"/>
+      <c r="BT6" s="28" t="n"/>
+      <c r="BU6" s="25" t="n"/>
+      <c r="BV6" s="29" t="n"/>
+      <c r="BW6" s="24" t="n"/>
+      <c r="BX6" s="30" t="n"/>
+      <c r="BY6" s="27" t="n"/>
+      <c r="BZ6" s="24" t="n"/>
+      <c r="CA6" s="31" t="n"/>
+      <c r="CB6" s="24" t="n"/>
+      <c r="CC6" s="24" t="n"/>
+      <c r="CD6" s="24" t="n"/>
+      <c r="CE6" s="24" t="n"/>
+      <c r="CF6" s="24" t="n"/>
+      <c r="CG6" s="24" t="n"/>
+      <c r="CH6" s="24" t="n"/>
+      <c r="CI6" s="24" t="n"/>
+      <c r="CJ6" s="24" t="n"/>
+      <c r="CK6" s="24" t="n"/>
+      <c r="CL6" s="24" t="n"/>
+      <c r="CM6" s="24" t="n"/>
+      <c r="CN6" s="24" t="n"/>
+      <c r="CO6" s="24" t="n"/>
+      <c r="CP6" s="24" t="n"/>
+      <c r="CQ6" s="24" t="n"/>
+      <c r="CR6" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1">
+      <c r="A7" s="24" t="inlineStr">
+        <is>
+          <t>07cba45ff6704ad2</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:55:29.194644Z</t>
+        </is>
+      </c>
+      <c r="C7" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>68273</t>
+        </is>
+      </c>
+      <c r="E7" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F7" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="G7" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="H7" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I7" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J7" s="25" t="n"/>
+      <c r="K7" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L7" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="M7" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="N7" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="O7" s="28" t="n">
+        <v>0.596977</v>
+      </c>
+      <c r="P7" s="28" t="n"/>
+      <c r="Q7" s="28" t="n">
+        <v>-0.062887</v>
+      </c>
+      <c r="R7" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T7" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U7" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V7" s="24" t="n"/>
+      <c r="W7" s="26" t="n"/>
+      <c r="X7" s="26" t="n"/>
+      <c r="Y7" s="25" t="n"/>
+      <c r="Z7" s="26" t="n"/>
+      <c r="AA7" s="28" t="n"/>
+      <c r="AB7" s="28" t="n"/>
+      <c r="AC7" s="30" t="n"/>
+      <c r="AD7" s="24" t="n"/>
+      <c r="AE7" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6600 (market_slug=aec-npb-cdh-tys-2026-08-04). Tie probability=0.0280.</t>
+        </is>
+      </c>
+      <c r="AF7" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG7" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH7" s="24" t="n"/>
+      <c r="AI7" s="31" t="n"/>
+      <c r="AJ7" s="31" t="n"/>
+      <c r="AK7" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL7" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM7" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN7" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO7" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP7" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AQ7" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AR7" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AS7" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="AT7" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="AU7" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="AV7" s="24" t="n"/>
+      <c r="AW7" s="24" t="n"/>
+      <c r="AX7" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY7" s="24" t="n"/>
+      <c r="AZ7" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA7" s="24" t="inlineStr">
+        <is>
+          <t>bc4fda3fccd78fdc3bca8f7cc4fb910c9fcb1d51c5557416c7b46467f043e355</t>
+        </is>
+      </c>
+      <c r="BB7" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC7" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD7" s="24" t="inlineStr">
+        <is>
+          <t>bc4fda3fccd78fdc3bca8f7cc4fb910c9fcb1d51c5557416c7b46467f043e355</t>
+        </is>
+      </c>
+      <c r="BE7" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF7" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG7" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH7" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:55:27.161124Z</t>
+        </is>
+      </c>
+      <c r="BI7" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ7" s="25" t="n"/>
+      <c r="BK7" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="BL7" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="BM7" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="BN7" s="28" t="n"/>
+      <c r="BO7" s="28" t="n"/>
+      <c r="BP7" s="25" t="n"/>
+      <c r="BQ7" s="27" t="n"/>
+      <c r="BR7" s="28" t="n"/>
+      <c r="BS7" s="28" t="n"/>
+      <c r="BT7" s="28" t="n"/>
+      <c r="BU7" s="25" t="n"/>
+      <c r="BV7" s="29" t="n"/>
+      <c r="BW7" s="24" t="n"/>
+      <c r="BX7" s="30" t="n"/>
+      <c r="BY7" s="27" t="n"/>
+      <c r="BZ7" s="24" t="n"/>
+      <c r="CA7" s="31" t="n"/>
+      <c r="CB7" s="24" t="n"/>
+      <c r="CC7" s="24" t="n"/>
+      <c r="CD7" s="24" t="n"/>
+      <c r="CE7" s="24" t="n"/>
+      <c r="CF7" s="24" t="n"/>
+      <c r="CG7" s="24" t="n"/>
+      <c r="CH7" s="24" t="n"/>
+      <c r="CI7" s="24" t="n"/>
+      <c r="CJ7" s="24" t="n"/>
+      <c r="CK7" s="24" t="n"/>
+      <c r="CL7" s="24" t="n"/>
+      <c r="CM7" s="24" t="n"/>
+      <c r="CN7" s="24" t="n"/>
+      <c r="CO7" s="24" t="n"/>
+      <c r="CP7" s="24" t="n"/>
+      <c r="CQ7" s="24" t="n"/>
+      <c r="CR7" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1">
+      <c r="A8" s="24" t="inlineStr">
+        <is>
+          <t>5565c1c847ae409c</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:55:29.194644Z</t>
+        </is>
+      </c>
+      <c r="C8" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>68274</t>
+        </is>
+      </c>
+      <c r="E8" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="G8" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="H8" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I8" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J8" s="25" t="n"/>
+      <c r="K8" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L8" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="M8" s="27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="N8" s="28" t="n">
+        <v>0.480769</v>
+      </c>
+      <c r="O8" s="28" t="n">
+        <v>0.545695</v>
+      </c>
+      <c r="P8" s="28" t="n"/>
+      <c r="Q8" s="28" t="n">
+        <v>0.064926</v>
+      </c>
+      <c r="R8" s="26" t="n">
+        <v>52</v>
+      </c>
+      <c r="S8" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U8" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V8" s="24" t="n"/>
+      <c r="W8" s="26" t="n"/>
+      <c r="X8" s="26" t="n"/>
+      <c r="Y8" s="25" t="n"/>
+      <c r="Z8" s="26" t="n"/>
+      <c r="AA8" s="28" t="n"/>
+      <c r="AB8" s="28" t="n"/>
+      <c r="AC8" s="30" t="n"/>
+      <c r="AD8" s="24" t="n"/>
+      <c r="AE8" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.4800 (market_slug=aec-npb-hci-ygo-2026-08-04). Tie probability=0.0325.</t>
+        </is>
+      </c>
+      <c r="AF8" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG8" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH8" s="24" t="n"/>
+      <c r="AI8" s="31" t="n"/>
+      <c r="AJ8" s="31" t="n"/>
+      <c r="AK8" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL8" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM8" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN8" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO8" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP8" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="AQ8" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="AR8" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="AS8" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="AT8" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="AU8" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="AV8" s="24" t="n"/>
+      <c r="AW8" s="24" t="n"/>
+      <c r="AX8" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY8" s="24" t="n"/>
+      <c r="AZ8" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA8" s="24" t="inlineStr">
+        <is>
+          <t>bc4fda3fccd78fdc3bca8f7cc4fb910c9fcb1d51c5557416c7b46467f043e355</t>
+        </is>
+      </c>
+      <c r="BB8" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC8" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD8" s="24" t="inlineStr">
+        <is>
+          <t>bc4fda3fccd78fdc3bca8f7cc4fb910c9fcb1d51c5557416c7b46467f043e355</t>
+        </is>
+      </c>
+      <c r="BE8" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF8" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG8" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH8" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:55:27.795687Z</t>
+        </is>
+      </c>
+      <c r="BI8" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ8" s="25" t="n"/>
+      <c r="BK8" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="BL8" s="27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM8" s="28" t="n">
+        <v>0.480769</v>
+      </c>
+      <c r="BN8" s="28" t="n"/>
+      <c r="BO8" s="28" t="n"/>
+      <c r="BP8" s="25" t="n"/>
+      <c r="BQ8" s="27" t="n"/>
+      <c r="BR8" s="28" t="n"/>
+      <c r="BS8" s="28" t="n"/>
+      <c r="BT8" s="28" t="n"/>
+      <c r="BU8" s="25" t="n"/>
+      <c r="BV8" s="29" t="n"/>
+      <c r="BW8" s="24" t="n"/>
+      <c r="BX8" s="30" t="n"/>
+      <c r="BY8" s="27" t="n"/>
+      <c r="BZ8" s="24" t="n"/>
+      <c r="CA8" s="31" t="n"/>
+      <c r="CB8" s="24" t="n"/>
+      <c r="CC8" s="24" t="n"/>
+      <c r="CD8" s="24" t="n"/>
+      <c r="CE8" s="24" t="n"/>
+      <c r="CF8" s="24" t="n"/>
+      <c r="CG8" s="24" t="n"/>
+      <c r="CH8" s="24" t="n"/>
+      <c r="CI8" s="24" t="n"/>
+      <c r="CJ8" s="24" t="n"/>
+      <c r="CK8" s="24" t="n"/>
+      <c r="CL8" s="24" t="n"/>
+      <c r="CM8" s="24" t="n"/>
+      <c r="CN8" s="24" t="n"/>
+      <c r="CO8" s="24" t="n"/>
+      <c r="CP8" s="24" t="n"/>
+      <c r="CQ8" s="24" t="n"/>
+      <c r="CR8" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="36" customHeight="1">
+      <c r="A9" s="24" t="inlineStr">
+        <is>
+          <t>95f669c37c9d41e9</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:55:29.194644Z</t>
+        </is>
+      </c>
+      <c r="C9" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>68275</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F9" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="G9" s="24" t="inlineStr">
+        <is>
+          <t>Chiba Lotte Marines</t>
+        </is>
+      </c>
+      <c r="H9" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I9" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J9" s="25" t="n"/>
+      <c r="K9" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L9" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M9" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="N9" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="O9" s="28" t="n">
+        <v>0.528517</v>
+      </c>
+      <c r="P9" s="28" t="n"/>
+      <c r="Q9" s="28" t="n">
+        <v>-0.042298</v>
+      </c>
+      <c r="R9" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U9" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V9" s="24" t="n"/>
+      <c r="W9" s="26" t="n"/>
+      <c r="X9" s="26" t="n"/>
+      <c r="Y9" s="25" t="n"/>
+      <c r="Z9" s="26" t="n"/>
+      <c r="AA9" s="28" t="n"/>
+      <c r="AB9" s="28" t="n"/>
+      <c r="AC9" s="30" t="n"/>
+      <c r="AD9" s="24" t="n"/>
+      <c r="AE9" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5700 (market_slug=aec-npb-clm-ssl-2026-08-04). Tie probability=0.0340.</t>
+        </is>
+      </c>
+      <c r="AF9" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG9" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH9" s="24" t="n"/>
+      <c r="AI9" s="31" t="n"/>
+      <c r="AJ9" s="31" t="n"/>
+      <c r="AK9" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL9" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM9" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN9" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO9" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP9" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AQ9" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AR9" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AS9" s="24" t="inlineStr">
+        <is>
+          <t>Chiba Lotte Marines</t>
+        </is>
+      </c>
+      <c r="AT9" s="24" t="inlineStr">
+        <is>
+          <t>Chiba Lotte Marines</t>
+        </is>
+      </c>
+      <c r="AU9" s="24" t="inlineStr">
+        <is>
+          <t>Chiba Lotte Marines</t>
+        </is>
+      </c>
+      <c r="AV9" s="24" t="n"/>
+      <c r="AW9" s="24" t="n"/>
+      <c r="AX9" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY9" s="24" t="n"/>
+      <c r="AZ9" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA9" s="24" t="inlineStr">
+        <is>
+          <t>bc4fda3fccd78fdc3bca8f7cc4fb910c9fcb1d51c5557416c7b46467f043e355</t>
+        </is>
+      </c>
+      <c r="BB9" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC9" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD9" s="24" t="inlineStr">
+        <is>
+          <t>bc4fda3fccd78fdc3bca8f7cc4fb910c9fcb1d51c5557416c7b46467f043e355</t>
+        </is>
+      </c>
+      <c r="BE9" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF9" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG9" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH9" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:55:28.470678Z</t>
+        </is>
+      </c>
+      <c r="BI9" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ9" s="25" t="n"/>
+      <c r="BK9" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BL9" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BM9" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="BN9" s="28" t="n"/>
+      <c r="BO9" s="28" t="n"/>
+      <c r="BP9" s="25" t="n"/>
+      <c r="BQ9" s="27" t="n"/>
+      <c r="BR9" s="28" t="n"/>
+      <c r="BS9" s="28" t="n"/>
+      <c r="BT9" s="28" t="n"/>
+      <c r="BU9" s="25" t="n"/>
+      <c r="BV9" s="29" t="n"/>
+      <c r="BW9" s="24" t="n"/>
+      <c r="BX9" s="30" t="n"/>
+      <c r="BY9" s="27" t="n"/>
+      <c r="BZ9" s="24" t="n"/>
+      <c r="CA9" s="31" t="n"/>
+      <c r="CB9" s="24" t="n"/>
+      <c r="CC9" s="24" t="n"/>
+      <c r="CD9" s="24" t="n"/>
+      <c r="CE9" s="24" t="n"/>
+      <c r="CF9" s="24" t="n"/>
+      <c r="CG9" s="24" t="n"/>
+      <c r="CH9" s="24" t="n"/>
+      <c r="CI9" s="24" t="n"/>
+      <c r="CJ9" s="24" t="n"/>
+      <c r="CK9" s="24" t="n"/>
+      <c r="CL9" s="24" t="n"/>
+      <c r="CM9" s="24" t="n"/>
+      <c r="CN9" s="24" t="n"/>
+      <c r="CO9" s="24" t="n"/>
+      <c r="CP9" s="24" t="n"/>
+      <c r="CQ9" s="24" t="n"/>
+      <c r="CR9" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="36" customHeight="1">
+      <c r="A10" s="24" t="inlineStr">
+        <is>
+          <t>a6465e9b4f2148ae</t>
+        </is>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:55:29.194644Z</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>68276</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F10" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="G10" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I10" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J10" s="25" t="n"/>
+      <c r="K10" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L10" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="M10" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="N10" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="O10" s="28" t="n">
+        <v>0.579364</v>
+      </c>
+      <c r="P10" s="28" t="n"/>
+      <c r="Q10" s="28" t="n">
+        <v>-0.030011</v>
+      </c>
+      <c r="R10" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="S10" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T10" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U10" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V10" s="24" t="n"/>
+      <c r="W10" s="26" t="n"/>
+      <c r="X10" s="26" t="n"/>
+      <c r="Y10" s="25" t="n"/>
+      <c r="Z10" s="26" t="n"/>
+      <c r="AA10" s="28" t="n"/>
+      <c r="AB10" s="28" t="n"/>
+      <c r="AC10" s="30" t="n"/>
+      <c r="AD10" s="24" t="n"/>
+      <c r="AE10" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6100 (market_slug=aec-npb-fsh-nhf-2026-08-04). Tie probability=0.0295.</t>
+        </is>
+      </c>
+      <c r="AF10" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG10" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH10" s="24" t="n"/>
+      <c r="AI10" s="31" t="n"/>
+      <c r="AJ10" s="31" t="n"/>
+      <c r="AK10" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL10" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM10" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN10" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO10" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP10" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AQ10" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AR10" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AS10" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="AT10" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="AU10" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="AV10" s="24" t="n"/>
+      <c r="AW10" s="24" t="n"/>
+      <c r="AX10" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY10" s="24" t="n"/>
+      <c r="AZ10" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA10" s="24" t="inlineStr">
+        <is>
+          <t>bc4fda3fccd78fdc3bca8f7cc4fb910c9fcb1d51c5557416c7b46467f043e355</t>
+        </is>
+      </c>
+      <c r="BB10" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC10" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD10" s="24" t="inlineStr">
+        <is>
+          <t>bc4fda3fccd78fdc3bca8f7cc4fb910c9fcb1d51c5557416c7b46467f043e355</t>
+        </is>
+      </c>
+      <c r="BE10" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF10" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG10" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH10" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:55:29.194611Z</t>
+        </is>
+      </c>
+      <c r="BI10" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ10" s="25" t="n"/>
+      <c r="BK10" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="BL10" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BM10" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="BN10" s="28" t="n"/>
+      <c r="BO10" s="28" t="n"/>
+      <c r="BP10" s="25" t="n"/>
+      <c r="BQ10" s="27" t="n"/>
+      <c r="BR10" s="28" t="n"/>
+      <c r="BS10" s="28" t="n"/>
+      <c r="BT10" s="28" t="n"/>
+      <c r="BU10" s="25" t="n"/>
+      <c r="BV10" s="29" t="n"/>
+      <c r="BW10" s="24" t="n"/>
+      <c r="BX10" s="30" t="n"/>
+      <c r="BY10" s="27" t="n"/>
+      <c r="BZ10" s="24" t="n"/>
+      <c r="CA10" s="31" t="n"/>
+      <c r="CB10" s="24" t="n"/>
+      <c r="CC10" s="24" t="n"/>
+      <c r="CD10" s="24" t="n"/>
+      <c r="CE10" s="24" t="n"/>
+      <c r="CF10" s="24" t="n"/>
+      <c r="CG10" s="24" t="n"/>
+      <c r="CH10" s="24" t="n"/>
+      <c r="CI10" s="24" t="n"/>
+      <c r="CJ10" s="24" t="n"/>
+      <c r="CK10" s="24" t="n"/>
+      <c r="CL10" s="24" t="n"/>
+      <c r="CM10" s="24" t="n"/>
+      <c r="CN10" s="24" t="n"/>
+      <c r="CO10" s="24" t="n"/>
+      <c r="CP10" s="24" t="n"/>
+      <c r="CQ10" s="24" t="n"/>
+      <c r="CR10" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>

--- a/data/research/npb.xlsx
+++ b/data/research/npb.xlsx
@@ -300,9 +300,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CR10" headerRowCount="1">
-  <autoFilter ref="A1:CR10"/>
-  <tableColumns count="96">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS10" headerRowCount="1">
+  <autoFilter ref="A1:CS10"/>
+  <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
     <tableColumn id="3" name="event_start_utc"/>
@@ -393,12 +393,13 @@
     <tableColumn id="88" name="defensive_trend_gap"/>
     <tableColumn id="89" name="neutral_elo_rating_difference"/>
     <tableColumn id="90" name="bullpen_weakness_gap"/>
-    <tableColumn id="91" name="rest_disparity"/>
-    <tableColumn id="92" name="back_to_back_gap"/>
-    <tableColumn id="93" name="games_last_7_gap"/>
-    <tableColumn id="94" name="schedule_missingness"/>
-    <tableColumn id="95" name="market_residual_probability"/>
-    <tableColumn id="96" name="trade_candidate"/>
+    <tableColumn id="91" name="starter_era_gap"/>
+    <tableColumn id="92" name="rest_disparity"/>
+    <tableColumn id="93" name="back_to_back_gap"/>
+    <tableColumn id="94" name="games_last_7_gap"/>
+    <tableColumn id="95" name="schedule_missingness"/>
+    <tableColumn id="96" name="market_residual_probability"/>
+    <tableColumn id="97" name="trade_candidate"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1013,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CR10"/>
+  <dimension ref="A1:CS10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1106,12 +1107,13 @@
     <col width="21" customWidth="1" min="88" max="88"/>
     <col width="22" customWidth="1" min="89" max="89"/>
     <col width="22" customWidth="1" min="90" max="90"/>
-    <col width="16" customWidth="1" min="91" max="91"/>
-    <col width="18" customWidth="1" min="92" max="92"/>
+    <col width="17" customWidth="1" min="91" max="91"/>
+    <col width="16" customWidth="1" min="92" max="92"/>
     <col width="18" customWidth="1" min="93" max="93"/>
-    <col width="22" customWidth="1" min="94" max="94"/>
+    <col width="18" customWidth="1" min="94" max="94"/>
     <col width="22" customWidth="1" min="95" max="95"/>
-    <col width="17" customWidth="1" min="96" max="96"/>
+    <col width="22" customWidth="1" min="96" max="96"/>
+    <col width="17" customWidth="1" min="97" max="97"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1567,30 +1569,35 @@
       </c>
       <c r="CM1" s="23" t="inlineStr">
         <is>
+          <t>starter_era_gap</t>
+        </is>
+      </c>
+      <c r="CN1" s="23" t="inlineStr">
+        <is>
           <t>rest_disparity</t>
         </is>
       </c>
-      <c r="CN1" s="23" t="inlineStr">
+      <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>back_to_back_gap</t>
         </is>
       </c>
-      <c r="CO1" s="23" t="inlineStr">
+      <c r="CP1" s="23" t="inlineStr">
         <is>
           <t>games_last_7_gap</t>
         </is>
       </c>
-      <c r="CP1" s="23" t="inlineStr">
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
         </is>
       </c>
-      <c r="CQ1" s="23" t="inlineStr">
+      <c r="CR1" s="23" t="inlineStr">
         <is>
           <t>market_residual_probability</t>
         </is>
       </c>
-      <c r="CR1" s="23" t="inlineStr">
+      <c r="CS1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
         </is>
@@ -1873,6 +1880,7 @@
       <c r="CP2" s="24" t="n"/>
       <c r="CQ2" s="24" t="n"/>
       <c r="CR2" s="24" t="n"/>
+      <c r="CS2" s="24" t="n"/>
     </row>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
@@ -2151,6 +2159,7 @@
       <c r="CP3" s="24" t="n"/>
       <c r="CQ3" s="24" t="n"/>
       <c r="CR3" s="24" t="n"/>
+      <c r="CS3" s="24" t="n"/>
     </row>
     <row r="4" ht="36" customHeight="1">
       <c r="A4" s="24" t="inlineStr">
@@ -2429,6 +2438,7 @@
       <c r="CP4" s="24" t="n"/>
       <c r="CQ4" s="24" t="n"/>
       <c r="CR4" s="24" t="n"/>
+      <c r="CS4" s="24" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1">
       <c r="A5" s="24" t="inlineStr">
@@ -2706,7 +2716,8 @@
       <c r="CO5" s="24" t="n"/>
       <c r="CP5" s="24" t="n"/>
       <c r="CQ5" s="24" t="n"/>
-      <c r="CR5" s="24" t="inlineStr">
+      <c r="CR5" s="24" t="n"/>
+      <c r="CS5" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -2974,7 +2985,8 @@
       <c r="CO6" s="24" t="n"/>
       <c r="CP6" s="24" t="n"/>
       <c r="CQ6" s="24" t="n"/>
-      <c r="CR6" s="24" t="inlineStr">
+      <c r="CR6" s="24" t="n"/>
+      <c r="CS6" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3242,7 +3254,8 @@
       <c r="CO7" s="24" t="n"/>
       <c r="CP7" s="24" t="n"/>
       <c r="CQ7" s="24" t="n"/>
-      <c r="CR7" s="24" t="inlineStr">
+      <c r="CR7" s="24" t="n"/>
+      <c r="CS7" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3510,7 +3523,8 @@
       <c r="CO8" s="24" t="n"/>
       <c r="CP8" s="24" t="n"/>
       <c r="CQ8" s="24" t="n"/>
-      <c r="CR8" s="24" t="inlineStr">
+      <c r="CR8" s="24" t="n"/>
+      <c r="CS8" s="24" t="inlineStr">
         <is>
           <t>True</t>
         </is>
@@ -3778,7 +3792,8 @@
       <c r="CO9" s="24" t="n"/>
       <c r="CP9" s="24" t="n"/>
       <c r="CQ9" s="24" t="n"/>
-      <c r="CR9" s="24" t="inlineStr">
+      <c r="CR9" s="24" t="n"/>
+      <c r="CS9" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4046,7 +4061,8 @@
       <c r="CO10" s="24" t="n"/>
       <c r="CP10" s="24" t="n"/>
       <c r="CQ10" s="24" t="n"/>
-      <c r="CR10" s="24" t="inlineStr">
+      <c r="CR10" s="24" t="n"/>
+      <c r="CS10" s="24" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/data/research/npb.xlsx
+++ b/data/research/npb.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS10" headerRowCount="1">
-  <autoFilter ref="A1:CS10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS16" headerRowCount="1">
+  <autoFilter ref="A1:CS16"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$10)</f>
+        <f>COUNTA('Picks'!$A$2:$A$16)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$10,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$16,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$10,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$16,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")+COUNTIFS('Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")+COUNTIFS('Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$10,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$16,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")/(COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")+COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")/(COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")+COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$10)/SUM('Picks'!$BX$2:$BX$10),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$16)/SUM('Picks'!$BX$2:$BX$16),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$10)</f>
+        <f>SUM('Picks'!$BY$2:$BY$16)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$10,"&lt;&gt;",'Picks'!$AB$2:$AB$10),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$16,"&lt;&gt;",'Picks'!$AB$2:$AB$16),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$10,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$10,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$16,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$16,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$10,'Picks'!$AM$2:$AM$10,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$16,'Picks'!$AM$2:$AM$16,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS10"/>
+  <dimension ref="A1:CS16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -2804,18 +2804,32 @@
       </c>
       <c r="U6" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V6" s="24" t="n"/>
-      <c r="W6" s="26" t="n"/>
-      <c r="X6" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V6" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W6" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y6" s="25" t="n"/>
       <c r="Z6" s="26" t="n"/>
       <c r="AA6" s="28" t="n"/>
       <c r="AB6" s="28" t="n"/>
-      <c r="AC6" s="30" t="n"/>
-      <c r="AD6" s="24" t="n"/>
+      <c r="AC6" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD6" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:04:43.764923Z</t>
+        </is>
+      </c>
       <c r="AE6" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.6200 (market_slug=aec-npb-ybo-hta-2026-08-04). Tie probability=0.0344.</t>
@@ -2828,7 +2842,7 @@
       </c>
       <c r="AG6" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH6" s="24" t="n"/>
@@ -3073,18 +3087,32 @@
       </c>
       <c r="U7" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V7" s="24" t="n"/>
-      <c r="W7" s="26" t="n"/>
-      <c r="X7" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V7" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W7" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X7" s="26" t="n">
+        <v>4</v>
+      </c>
       <c r="Y7" s="25" t="n"/>
       <c r="Z7" s="26" t="n"/>
       <c r="AA7" s="28" t="n"/>
       <c r="AB7" s="28" t="n"/>
-      <c r="AC7" s="30" t="n"/>
-      <c r="AD7" s="24" t="n"/>
+      <c r="AC7" s="30" t="n">
+        <v>0.6443</v>
+      </c>
+      <c r="AD7" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:04:43.845421Z</t>
+        </is>
+      </c>
       <c r="AE7" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.6600 (market_slug=aec-npb-cdh-tys-2026-08-04). Tie probability=0.0280.</t>
@@ -3342,18 +3370,32 @@
       </c>
       <c r="U8" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V8" s="24" t="n"/>
-      <c r="W8" s="26" t="n"/>
-      <c r="X8" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V8" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W8" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X8" s="26" t="n">
+        <v>4</v>
+      </c>
       <c r="Y8" s="25" t="n"/>
       <c r="Z8" s="26" t="n"/>
       <c r="AA8" s="28" t="n"/>
       <c r="AB8" s="28" t="n"/>
-      <c r="AC8" s="30" t="n"/>
-      <c r="AD8" s="24" t="n"/>
+      <c r="AC8" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD8" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:04:43.918073Z</t>
+        </is>
+      </c>
       <c r="AE8" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.4800 (market_slug=aec-npb-hci-ygo-2026-08-04). Tie probability=0.0325.</t>
@@ -3366,7 +3408,7 @@
       </c>
       <c r="AG8" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH8" s="24" t="n"/>
@@ -3611,18 +3653,32 @@
       </c>
       <c r="U9" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V9" s="24" t="n"/>
-      <c r="W9" s="26" t="n"/>
-      <c r="X9" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V9" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W9" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X9" s="26" t="n">
+        <v>5</v>
+      </c>
       <c r="Y9" s="25" t="n"/>
       <c r="Z9" s="26" t="n"/>
       <c r="AA9" s="28" t="n"/>
       <c r="AB9" s="28" t="n"/>
-      <c r="AC9" s="30" t="n"/>
-      <c r="AD9" s="24" t="n"/>
+      <c r="AC9" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD9" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:04:43.989853Z</t>
+        </is>
+      </c>
       <c r="AE9" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.5700 (market_slug=aec-npb-clm-ssl-2026-08-04). Tie probability=0.0340.</t>
@@ -3635,7 +3691,7 @@
       </c>
       <c r="AG9" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH9" s="24" t="n"/>
@@ -3880,18 +3936,32 @@
       </c>
       <c r="U10" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V10" s="24" t="n"/>
-      <c r="W10" s="26" t="n"/>
-      <c r="X10" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V10" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y10" s="25" t="n"/>
       <c r="Z10" s="26" t="n"/>
       <c r="AA10" s="28" t="n"/>
       <c r="AB10" s="28" t="n"/>
-      <c r="AC10" s="30" t="n"/>
-      <c r="AD10" s="24" t="n"/>
+      <c r="AC10" s="30" t="n">
+        <v>0.8013</v>
+      </c>
+      <c r="AD10" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:04:44.062623Z</t>
+        </is>
+      </c>
       <c r="AE10" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.6100 (market_slug=aec-npb-fsh-nhf-2026-08-04). Tie probability=0.0295.</t>
@@ -4068,6 +4138,1620 @@
         </is>
       </c>
     </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>ba889f1490334b55</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:53.416116Z</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T08:45:00Z</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>69524</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="H11" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J11" s="25" t="n"/>
+      <c r="K11" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L11" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M11" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N11" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O11" s="28" t="n">
+        <v>0.512165</v>
+      </c>
+      <c r="P11" s="28" t="n"/>
+      <c r="Q11" s="28" t="n">
+        <v>-0.087835</v>
+      </c>
+      <c r="R11" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U11" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V11" s="24" t="n"/>
+      <c r="W11" s="26" t="n"/>
+      <c r="X11" s="26" t="n"/>
+      <c r="Y11" s="25" t="n"/>
+      <c r="Z11" s="26" t="n"/>
+      <c r="AA11" s="28" t="n"/>
+      <c r="AB11" s="28" t="n"/>
+      <c r="AC11" s="30" t="n"/>
+      <c r="AD11" s="24" t="n"/>
+      <c r="AE11" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6000 (market_slug=aec-npb-ybo-hta-2026-08-05). Tie probability=0.0354.</t>
+        </is>
+      </c>
+      <c r="AF11" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG11" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH11" s="24" t="n"/>
+      <c r="AI11" s="31" t="n"/>
+      <c r="AJ11" s="31" t="n"/>
+      <c r="AK11" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM11" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN11" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO11" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP11" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AQ11" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AR11" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AS11" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AT11" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AU11" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AV11" s="24" t="n"/>
+      <c r="AW11" s="24" t="n"/>
+      <c r="AX11" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY11" s="24" t="n"/>
+      <c r="AZ11" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA11" s="24" t="inlineStr">
+        <is>
+          <t>587c95488a5eab49a474c082a9d83bc1218cd1ce498682f7305ccc207cdae6d9</t>
+        </is>
+      </c>
+      <c r="BB11" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC11" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD11" s="24" t="inlineStr">
+        <is>
+          <t>587c95488a5eab49a474c082a9d83bc1218cd1ce498682f7305ccc207cdae6d9</t>
+        </is>
+      </c>
+      <c r="BE11" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF11" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG11" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:49.025090Z</t>
+        </is>
+      </c>
+      <c r="BI11" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ11" s="25" t="n"/>
+      <c r="BK11" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL11" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM11" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN11" s="28" t="n"/>
+      <c r="BO11" s="28" t="n"/>
+      <c r="BP11" s="25" t="n"/>
+      <c r="BQ11" s="27" t="n"/>
+      <c r="BR11" s="28" t="n"/>
+      <c r="BS11" s="28" t="n"/>
+      <c r="BT11" s="28" t="n"/>
+      <c r="BU11" s="25" t="n"/>
+      <c r="BV11" s="29" t="n"/>
+      <c r="BW11" s="24" t="n"/>
+      <c r="BX11" s="30" t="n"/>
+      <c r="BY11" s="27" t="n"/>
+      <c r="BZ11" s="24" t="n"/>
+      <c r="CA11" s="31" t="n"/>
+      <c r="CB11" s="24" t="n"/>
+      <c r="CC11" s="24" t="n"/>
+      <c r="CD11" s="24" t="n"/>
+      <c r="CE11" s="24" t="n"/>
+      <c r="CF11" s="24" t="n"/>
+      <c r="CG11" s="24" t="n"/>
+      <c r="CH11" s="24" t="n"/>
+      <c r="CI11" s="24" t="n"/>
+      <c r="CJ11" s="24" t="n"/>
+      <c r="CK11" s="24" t="n"/>
+      <c r="CL11" s="24" t="n"/>
+      <c r="CM11" s="24" t="n"/>
+      <c r="CN11" s="24" t="n"/>
+      <c r="CO11" s="24" t="n"/>
+      <c r="CP11" s="24" t="n"/>
+      <c r="CQ11" s="24" t="n"/>
+      <c r="CR11" s="24" t="n"/>
+      <c r="CS11" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>4fee8ebfb11943f8</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:53.416116Z</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>69525</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="H12" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J12" s="25" t="n"/>
+      <c r="K12" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L12" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="M12" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="N12" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="O12" s="28" t="n">
+        <v>0.605094</v>
+      </c>
+      <c r="P12" s="28" t="n"/>
+      <c r="Q12" s="28" t="n">
+        <v>0.055544</v>
+      </c>
+      <c r="R12" s="26" t="n">
+        <v>48</v>
+      </c>
+      <c r="S12" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T12" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U12" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V12" s="24" t="n"/>
+      <c r="W12" s="26" t="n"/>
+      <c r="X12" s="26" t="n"/>
+      <c r="Y12" s="25" t="n"/>
+      <c r="Z12" s="26" t="n"/>
+      <c r="AA12" s="28" t="n"/>
+      <c r="AB12" s="28" t="n"/>
+      <c r="AC12" s="30" t="n"/>
+      <c r="AD12" s="24" t="n"/>
+      <c r="AE12" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5500 (market_slug=aec-npb-cdh-tys-2026-08-05). Tie probability=0.0272.</t>
+        </is>
+      </c>
+      <c r="AF12" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG12" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH12" s="24" t="n"/>
+      <c r="AI12" s="31" t="n"/>
+      <c r="AJ12" s="31" t="n"/>
+      <c r="AK12" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL12" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM12" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN12" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO12" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP12" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AQ12" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AR12" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AS12" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="AT12" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="AU12" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="AV12" s="24" t="n"/>
+      <c r="AW12" s="24" t="n"/>
+      <c r="AX12" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY12" s="24" t="n"/>
+      <c r="AZ12" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA12" s="24" t="inlineStr">
+        <is>
+          <t>587c95488a5eab49a474c082a9d83bc1218cd1ce498682f7305ccc207cdae6d9</t>
+        </is>
+      </c>
+      <c r="BB12" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC12" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD12" s="24" t="inlineStr">
+        <is>
+          <t>587c95488a5eab49a474c082a9d83bc1218cd1ce498682f7305ccc207cdae6d9</t>
+        </is>
+      </c>
+      <c r="BE12" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF12" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG12" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:49.865696Z</t>
+        </is>
+      </c>
+      <c r="BI12" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ12" s="25" t="n"/>
+      <c r="BK12" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="BL12" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="BM12" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="BN12" s="28" t="n"/>
+      <c r="BO12" s="28" t="n"/>
+      <c r="BP12" s="25" t="n"/>
+      <c r="BQ12" s="27" t="n"/>
+      <c r="BR12" s="28" t="n"/>
+      <c r="BS12" s="28" t="n"/>
+      <c r="BT12" s="28" t="n"/>
+      <c r="BU12" s="25" t="n"/>
+      <c r="BV12" s="29" t="n"/>
+      <c r="BW12" s="24" t="n"/>
+      <c r="BX12" s="30" t="n"/>
+      <c r="BY12" s="27" t="n"/>
+      <c r="BZ12" s="24" t="n"/>
+      <c r="CA12" s="31" t="n"/>
+      <c r="CB12" s="24" t="n"/>
+      <c r="CC12" s="24" t="n"/>
+      <c r="CD12" s="24" t="n"/>
+      <c r="CE12" s="24" t="n"/>
+      <c r="CF12" s="24" t="n"/>
+      <c r="CG12" s="24" t="n"/>
+      <c r="CH12" s="24" t="n"/>
+      <c r="CI12" s="24" t="n"/>
+      <c r="CJ12" s="24" t="n"/>
+      <c r="CK12" s="24" t="n"/>
+      <c r="CL12" s="24" t="n"/>
+      <c r="CM12" s="24" t="n"/>
+      <c r="CN12" s="24" t="n"/>
+      <c r="CO12" s="24" t="n"/>
+      <c r="CP12" s="24" t="n"/>
+      <c r="CQ12" s="24" t="n"/>
+      <c r="CR12" s="24" t="n"/>
+      <c r="CS12" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>6e9d79eeb8954b77</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:53.416116Z</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>69526</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="G13" s="24" t="inlineStr">
+        <is>
+          <t>Chiba Lotte Marines</t>
+        </is>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I13" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J13" s="25" t="n"/>
+      <c r="K13" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L13" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="M13" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="N13" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="O13" s="28" t="n">
+        <v>0.511776</v>
+      </c>
+      <c r="P13" s="28" t="n"/>
+      <c r="Q13" s="28" t="n">
+        <v>-0.01874</v>
+      </c>
+      <c r="R13" s="26" t="n">
+        <v>11</v>
+      </c>
+      <c r="S13" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U13" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V13" s="24" t="n"/>
+      <c r="W13" s="26" t="n"/>
+      <c r="X13" s="26" t="n"/>
+      <c r="Y13" s="25" t="n"/>
+      <c r="Z13" s="26" t="n"/>
+      <c r="AA13" s="28" t="n"/>
+      <c r="AB13" s="28" t="n"/>
+      <c r="AC13" s="30" t="n"/>
+      <c r="AD13" s="24" t="n"/>
+      <c r="AE13" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5300 (market_slug=aec-npb-clm-ssl-2026-08-05). Tie probability=0.0354.</t>
+        </is>
+      </c>
+      <c r="AF13" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG13" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH13" s="24" t="n"/>
+      <c r="AI13" s="31" t="n"/>
+      <c r="AJ13" s="31" t="n"/>
+      <c r="AK13" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM13" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN13" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO13" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP13" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AQ13" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AR13" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AS13" s="24" t="inlineStr">
+        <is>
+          <t>Chiba Lotte Marines</t>
+        </is>
+      </c>
+      <c r="AT13" s="24" t="inlineStr">
+        <is>
+          <t>Chiba Lotte Marines</t>
+        </is>
+      </c>
+      <c r="AU13" s="24" t="inlineStr">
+        <is>
+          <t>Chiba Lotte Marines</t>
+        </is>
+      </c>
+      <c r="AV13" s="24" t="n"/>
+      <c r="AW13" s="24" t="n"/>
+      <c r="AX13" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY13" s="24" t="n"/>
+      <c r="AZ13" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA13" s="24" t="inlineStr">
+        <is>
+          <t>587c95488a5eab49a474c082a9d83bc1218cd1ce498682f7305ccc207cdae6d9</t>
+        </is>
+      </c>
+      <c r="BB13" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC13" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD13" s="24" t="inlineStr">
+        <is>
+          <t>587c95488a5eab49a474c082a9d83bc1218cd1ce498682f7305ccc207cdae6d9</t>
+        </is>
+      </c>
+      <c r="BE13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG13" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:50.743012Z</t>
+        </is>
+      </c>
+      <c r="BI13" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ13" s="25" t="n"/>
+      <c r="BK13" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="BL13" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BM13" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="BN13" s="28" t="n"/>
+      <c r="BO13" s="28" t="n"/>
+      <c r="BP13" s="25" t="n"/>
+      <c r="BQ13" s="27" t="n"/>
+      <c r="BR13" s="28" t="n"/>
+      <c r="BS13" s="28" t="n"/>
+      <c r="BT13" s="28" t="n"/>
+      <c r="BU13" s="25" t="n"/>
+      <c r="BV13" s="29" t="n"/>
+      <c r="BW13" s="24" t="n"/>
+      <c r="BX13" s="30" t="n"/>
+      <c r="BY13" s="27" t="n"/>
+      <c r="BZ13" s="24" t="n"/>
+      <c r="CA13" s="31" t="n"/>
+      <c r="CB13" s="24" t="n"/>
+      <c r="CC13" s="24" t="n"/>
+      <c r="CD13" s="24" t="n"/>
+      <c r="CE13" s="24" t="n"/>
+      <c r="CF13" s="24" t="n"/>
+      <c r="CG13" s="24" t="n"/>
+      <c r="CH13" s="24" t="n"/>
+      <c r="CI13" s="24" t="n"/>
+      <c r="CJ13" s="24" t="n"/>
+      <c r="CK13" s="24" t="n"/>
+      <c r="CL13" s="24" t="n"/>
+      <c r="CM13" s="24" t="n"/>
+      <c r="CN13" s="24" t="n"/>
+      <c r="CO13" s="24" t="n"/>
+      <c r="CP13" s="24" t="n"/>
+      <c r="CQ13" s="24" t="n"/>
+      <c r="CR13" s="24" t="n"/>
+      <c r="CS13" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>e390daaf0112448a</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:53.416116Z</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>69527</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>Tohoku Rakuten Golden Eagles</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="inlineStr">
+        <is>
+          <t>Orix Buffaloes</t>
+        </is>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J14" s="25" t="n"/>
+      <c r="K14" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L14" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="M14" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="N14" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="O14" s="28" t="n">
+        <v>0.565314</v>
+      </c>
+      <c r="P14" s="28" t="n"/>
+      <c r="Q14" s="28" t="n">
+        <v>-0.064316</v>
+      </c>
+      <c r="R14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U14" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V14" s="24" t="n"/>
+      <c r="W14" s="26" t="n"/>
+      <c r="X14" s="26" t="n"/>
+      <c r="Y14" s="25" t="n"/>
+      <c r="Z14" s="26" t="n"/>
+      <c r="AA14" s="28" t="n"/>
+      <c r="AB14" s="28" t="n"/>
+      <c r="AC14" s="30" t="n"/>
+      <c r="AD14" s="24" t="n"/>
+      <c r="AE14" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6300 (market_slug=aec-npb-obr-trge-2026-08-05). Tie probability=0.0307.</t>
+        </is>
+      </c>
+      <c r="AF14" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG14" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH14" s="24" t="n"/>
+      <c r="AI14" s="31" t="n"/>
+      <c r="AJ14" s="31" t="n"/>
+      <c r="AK14" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL14" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM14" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN14" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO14" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP14" s="24" t="inlineStr">
+        <is>
+          <t>Tohoku Rakuten Golden Eagles</t>
+        </is>
+      </c>
+      <c r="AQ14" s="24" t="inlineStr">
+        <is>
+          <t>Tohoku Rakuten Golden Eagles</t>
+        </is>
+      </c>
+      <c r="AR14" s="24" t="inlineStr">
+        <is>
+          <t>Tohoku Rakuten Golden Eagles</t>
+        </is>
+      </c>
+      <c r="AS14" s="24" t="inlineStr">
+        <is>
+          <t>Orix Buffaloes</t>
+        </is>
+      </c>
+      <c r="AT14" s="24" t="inlineStr">
+        <is>
+          <t>Orix Buffaloes</t>
+        </is>
+      </c>
+      <c r="AU14" s="24" t="inlineStr">
+        <is>
+          <t>Orix Buffaloes</t>
+        </is>
+      </c>
+      <c r="AV14" s="24" t="n"/>
+      <c r="AW14" s="24" t="n"/>
+      <c r="AX14" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY14" s="24" t="n"/>
+      <c r="AZ14" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA14" s="24" t="inlineStr">
+        <is>
+          <t>587c95488a5eab49a474c082a9d83bc1218cd1ce498682f7305ccc207cdae6d9</t>
+        </is>
+      </c>
+      <c r="BB14" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC14" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD14" s="24" t="inlineStr">
+        <is>
+          <t>587c95488a5eab49a474c082a9d83bc1218cd1ce498682f7305ccc207cdae6d9</t>
+        </is>
+      </c>
+      <c r="BE14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG14" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:51.558960Z</t>
+        </is>
+      </c>
+      <c r="BI14" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ14" s="25" t="n"/>
+      <c r="BK14" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="BL14" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="BM14" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="BN14" s="28" t="n"/>
+      <c r="BO14" s="28" t="n"/>
+      <c r="BP14" s="25" t="n"/>
+      <c r="BQ14" s="27" t="n"/>
+      <c r="BR14" s="28" t="n"/>
+      <c r="BS14" s="28" t="n"/>
+      <c r="BT14" s="28" t="n"/>
+      <c r="BU14" s="25" t="n"/>
+      <c r="BV14" s="29" t="n"/>
+      <c r="BW14" s="24" t="n"/>
+      <c r="BX14" s="30" t="n"/>
+      <c r="BY14" s="27" t="n"/>
+      <c r="BZ14" s="24" t="n"/>
+      <c r="CA14" s="31" t="n"/>
+      <c r="CB14" s="24" t="n"/>
+      <c r="CC14" s="24" t="n"/>
+      <c r="CD14" s="24" t="n"/>
+      <c r="CE14" s="24" t="n"/>
+      <c r="CF14" s="24" t="n"/>
+      <c r="CG14" s="24" t="n"/>
+      <c r="CH14" s="24" t="n"/>
+      <c r="CI14" s="24" t="n"/>
+      <c r="CJ14" s="24" t="n"/>
+      <c r="CK14" s="24" t="n"/>
+      <c r="CL14" s="24" t="n"/>
+      <c r="CM14" s="24" t="n"/>
+      <c r="CN14" s="24" t="n"/>
+      <c r="CO14" s="24" t="n"/>
+      <c r="CP14" s="24" t="n"/>
+      <c r="CQ14" s="24" t="n"/>
+      <c r="CR14" s="24" t="n"/>
+      <c r="CS14" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>7824cc7441d94f63</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:53.416116Z</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>69528</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J15" s="25" t="n"/>
+      <c r="K15" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L15" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M15" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N15" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O15" s="28" t="n">
+        <v>0.587499</v>
+      </c>
+      <c r="P15" s="28" t="n"/>
+      <c r="Q15" s="28" t="n">
+        <v>-0.002665</v>
+      </c>
+      <c r="R15" s="26" t="n">
+        <v>19</v>
+      </c>
+      <c r="S15" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T15" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U15" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="n"/>
+      <c r="W15" s="26" t="n"/>
+      <c r="X15" s="26" t="n"/>
+      <c r="Y15" s="25" t="n"/>
+      <c r="Z15" s="26" t="n"/>
+      <c r="AA15" s="28" t="n"/>
+      <c r="AB15" s="28" t="n"/>
+      <c r="AC15" s="30" t="n"/>
+      <c r="AD15" s="24" t="n"/>
+      <c r="AE15" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5900 (market_slug=aec-npb-fsh-nhf-2026-08-05). Tie probability=0.0288.</t>
+        </is>
+      </c>
+      <c r="AF15" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG15" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH15" s="24" t="n"/>
+      <c r="AI15" s="31" t="n"/>
+      <c r="AJ15" s="31" t="n"/>
+      <c r="AK15" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL15" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM15" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN15" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO15" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP15" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AQ15" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AR15" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AS15" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="AT15" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="AU15" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="AV15" s="24" t="n"/>
+      <c r="AW15" s="24" t="n"/>
+      <c r="AX15" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY15" s="24" t="n"/>
+      <c r="AZ15" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA15" s="24" t="inlineStr">
+        <is>
+          <t>587c95488a5eab49a474c082a9d83bc1218cd1ce498682f7305ccc207cdae6d9</t>
+        </is>
+      </c>
+      <c r="BB15" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC15" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD15" s="24" t="inlineStr">
+        <is>
+          <t>587c95488a5eab49a474c082a9d83bc1218cd1ce498682f7305ccc207cdae6d9</t>
+        </is>
+      </c>
+      <c r="BE15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG15" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:52.448253Z</t>
+        </is>
+      </c>
+      <c r="BI15" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ15" s="25" t="n"/>
+      <c r="BK15" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL15" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM15" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN15" s="28" t="n"/>
+      <c r="BO15" s="28" t="n"/>
+      <c r="BP15" s="25" t="n"/>
+      <c r="BQ15" s="27" t="n"/>
+      <c r="BR15" s="28" t="n"/>
+      <c r="BS15" s="28" t="n"/>
+      <c r="BT15" s="28" t="n"/>
+      <c r="BU15" s="25" t="n"/>
+      <c r="BV15" s="29" t="n"/>
+      <c r="BW15" s="24" t="n"/>
+      <c r="BX15" s="30" t="n"/>
+      <c r="BY15" s="27" t="n"/>
+      <c r="BZ15" s="24" t="n"/>
+      <c r="CA15" s="31" t="n"/>
+      <c r="CB15" s="24" t="n"/>
+      <c r="CC15" s="24" t="n"/>
+      <c r="CD15" s="24" t="n"/>
+      <c r="CE15" s="24" t="n"/>
+      <c r="CF15" s="24" t="n"/>
+      <c r="CG15" s="24" t="n"/>
+      <c r="CH15" s="24" t="n"/>
+      <c r="CI15" s="24" t="n"/>
+      <c r="CJ15" s="24" t="n"/>
+      <c r="CK15" s="24" t="n"/>
+      <c r="CL15" s="24" t="n"/>
+      <c r="CM15" s="24" t="n"/>
+      <c r="CN15" s="24" t="n"/>
+      <c r="CO15" s="24" t="n"/>
+      <c r="CP15" s="24" t="n"/>
+      <c r="CQ15" s="24" t="n"/>
+      <c r="CR15" s="24" t="n"/>
+      <c r="CS15" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>63e486e3516242c8</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:53.416116Z</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>69529</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J16" s="25" t="n"/>
+      <c r="K16" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L16" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M16" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N16" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O16" s="28" t="n">
+        <v>0.532673</v>
+      </c>
+      <c r="P16" s="28" t="n"/>
+      <c r="Q16" s="28" t="n">
+        <v>-0.026798</v>
+      </c>
+      <c r="R16" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="S16" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U16" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V16" s="24" t="n"/>
+      <c r="W16" s="26" t="n"/>
+      <c r="X16" s="26" t="n"/>
+      <c r="Y16" s="25" t="n"/>
+      <c r="Z16" s="26" t="n"/>
+      <c r="AA16" s="28" t="n"/>
+      <c r="AB16" s="28" t="n"/>
+      <c r="AC16" s="30" t="n"/>
+      <c r="AD16" s="24" t="n"/>
+      <c r="AE16" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5600 (market_slug=aec-npb-hci-ygo-2026-08-05). Tie probability=0.0336.</t>
+        </is>
+      </c>
+      <c r="AF16" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG16" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH16" s="24" t="n"/>
+      <c r="AI16" s="31" t="n"/>
+      <c r="AJ16" s="31" t="n"/>
+      <c r="AK16" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM16" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN16" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO16" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP16" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="AQ16" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="AR16" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="AS16" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="AT16" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="AU16" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="AV16" s="24" t="n"/>
+      <c r="AW16" s="24" t="n"/>
+      <c r="AX16" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY16" s="24" t="n"/>
+      <c r="AZ16" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA16" s="24" t="inlineStr">
+        <is>
+          <t>587c95488a5eab49a474c082a9d83bc1218cd1ce498682f7305ccc207cdae6d9</t>
+        </is>
+      </c>
+      <c r="BB16" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC16" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD16" s="24" t="inlineStr">
+        <is>
+          <t>587c95488a5eab49a474c082a9d83bc1218cd1ce498682f7305ccc207cdae6d9</t>
+        </is>
+      </c>
+      <c r="BE16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG16" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:53.416071Z</t>
+        </is>
+      </c>
+      <c r="BI16" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ16" s="25" t="n"/>
+      <c r="BK16" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL16" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM16" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN16" s="28" t="n"/>
+      <c r="BO16" s="28" t="n"/>
+      <c r="BP16" s="25" t="n"/>
+      <c r="BQ16" s="27" t="n"/>
+      <c r="BR16" s="28" t="n"/>
+      <c r="BS16" s="28" t="n"/>
+      <c r="BT16" s="28" t="n"/>
+      <c r="BU16" s="25" t="n"/>
+      <c r="BV16" s="29" t="n"/>
+      <c r="BW16" s="24" t="n"/>
+      <c r="BX16" s="30" t="n"/>
+      <c r="BY16" s="27" t="n"/>
+      <c r="BZ16" s="24" t="n"/>
+      <c r="CA16" s="31" t="n"/>
+      <c r="CB16" s="24" t="n"/>
+      <c r="CC16" s="24" t="n"/>
+      <c r="CD16" s="24" t="n"/>
+      <c r="CE16" s="24" t="n"/>
+      <c r="CF16" s="24" t="n"/>
+      <c r="CG16" s="24" t="n"/>
+      <c r="CH16" s="24" t="n"/>
+      <c r="CI16" s="24" t="n"/>
+      <c r="CJ16" s="24" t="n"/>
+      <c r="CK16" s="24" t="n"/>
+      <c r="CL16" s="24" t="n"/>
+      <c r="CM16" s="24" t="n"/>
+      <c r="CN16" s="24" t="n"/>
+      <c r="CO16" s="24" t="n"/>
+      <c r="CP16" s="24" t="n"/>
+      <c r="CQ16" s="24" t="n"/>
+      <c r="CR16" s="24" t="n"/>
+      <c r="CS16" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/npb.xlsx
+++ b/data/research/npb.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Picks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Picks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS16" headerRowCount="1">
-  <autoFilter ref="A1:CS16"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS22" headerRowCount="1">
+  <autoFilter ref="A1:CS22"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$16)</f>
+        <f>COUNTA('Picks'!$A$2:$A$22)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$16,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$22,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$16,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$22,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")+COUNTIFS('Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"win")+COUNTIFS('Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$16,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$22,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$22,"&gt;0",'Picks'!$V$2:$V$22,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$22,"&gt;0",'Picks'!$V$2:$V$22,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")/(COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"win")+COUNTIFS('Picks'!$BX$2:$BX$16,"&gt;0",'Picks'!$V$2:$V$16,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$22,"&gt;0",'Picks'!$V$2:$V$22,"win")/(COUNTIFS('Picks'!$BX$2:$BX$22,"&gt;0",'Picks'!$V$2:$V$22,"win")+COUNTIFS('Picks'!$BX$2:$BX$22,"&gt;0",'Picks'!$V$2:$V$22,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$16)/SUM('Picks'!$BX$2:$BX$16),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$22)/SUM('Picks'!$BX$2:$BX$22),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$16)</f>
+        <f>SUM('Picks'!$BY$2:$BY$22)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$16,"&lt;&gt;",'Picks'!$AB$2:$AB$16),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$22,"&lt;&gt;",'Picks'!$AB$2:$AB$22),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$16,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$16,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$22,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$22,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$16,'Picks'!$AM$2:$AM$16,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$22,'Picks'!$AM$2:$AM$22,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$22,$A14,'Picks'!$U$2:$U$22,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$22,$A14,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$22,$A14,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$22,'Picks'!$H$2:$H$22,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A14,'Picks'!$U$2:$U$16,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$22,'Picks'!$H$2:$H$22,$A14,'Picks'!$U$2:$U$22,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$22,$A15,'Picks'!$U$2:$U$22,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$22,$A15,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$22,$A15,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$22,'Picks'!$H$2:$H$22,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A15,'Picks'!$U$2:$U$16,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$22,'Picks'!$H$2:$H$22,$A15,'Picks'!$U$2:$U$22,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$22,$A16,'Picks'!$U$2:$U$22,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$22,$A16,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled",'Picks'!$V$2:$V$16,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$22,$A16,'Picks'!$U$2:$U$22,"settled",'Picks'!$V$2:$V$22,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$16,'Picks'!$H$2:$H$16,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$22,'Picks'!$H$2:$H$22,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$16,'Picks'!$H$2:$H$16,$A16,'Picks'!$U$2:$U$16,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$22,'Picks'!$H$2:$H$22,$A16,'Picks'!$U$2:$U$22,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS16"/>
+  <dimension ref="A1:CS22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -4219,18 +4219,32 @@
       </c>
       <c r="U11" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V11" s="24" t="n"/>
-      <c r="W11" s="26" t="n"/>
-      <c r="X11" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V11" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W11" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="X11" s="26" t="n">
+        <v>11</v>
+      </c>
       <c r="Y11" s="25" t="n"/>
       <c r="Z11" s="26" t="n"/>
       <c r="AA11" s="28" t="n"/>
       <c r="AB11" s="28" t="n"/>
-      <c r="AC11" s="30" t="n"/>
-      <c r="AD11" s="24" t="n"/>
+      <c r="AC11" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:18.583620Z</t>
+        </is>
+      </c>
       <c r="AE11" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.6000 (market_slug=aec-npb-ybo-hta-2026-08-05). Tie probability=0.0354.</t>
@@ -4243,7 +4257,7 @@
       </c>
       <c r="AG11" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH11" s="24" t="n"/>
@@ -4488,18 +4502,32 @@
       </c>
       <c r="U12" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V12" s="24" t="n"/>
-      <c r="W12" s="26" t="n"/>
-      <c r="X12" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V12" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W12" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" s="26" t="n">
+        <v>4</v>
+      </c>
       <c r="Y12" s="25" t="n"/>
       <c r="Z12" s="26" t="n"/>
       <c r="AA12" s="28" t="n"/>
       <c r="AB12" s="28" t="n"/>
-      <c r="AC12" s="30" t="n"/>
-      <c r="AD12" s="24" t="n"/>
+      <c r="AC12" s="30" t="n">
+        <v>1.0246</v>
+      </c>
+      <c r="AD12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:18.684954Z</t>
+        </is>
+      </c>
       <c r="AE12" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.5500 (market_slug=aec-npb-cdh-tys-2026-08-05). Tie probability=0.0272.</t>
@@ -4757,18 +4785,32 @@
       </c>
       <c r="U13" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V13" s="24" t="n"/>
-      <c r="W13" s="26" t="n"/>
-      <c r="X13" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V13" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W13" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" s="26" t="n">
+        <v>8</v>
+      </c>
       <c r="Y13" s="25" t="n"/>
       <c r="Z13" s="26" t="n"/>
       <c r="AA13" s="28" t="n"/>
       <c r="AB13" s="28" t="n"/>
-      <c r="AC13" s="30" t="n"/>
-      <c r="AD13" s="24" t="n"/>
+      <c r="AC13" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:18.770156Z</t>
+        </is>
+      </c>
       <c r="AE13" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.5300 (market_slug=aec-npb-clm-ssl-2026-08-05). Tie probability=0.0354.</t>
@@ -4781,7 +4823,7 @@
       </c>
       <c r="AG13" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH13" s="24" t="n"/>
@@ -5026,18 +5068,32 @@
       </c>
       <c r="U14" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V14" s="24" t="n"/>
-      <c r="W14" s="26" t="n"/>
-      <c r="X14" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V14" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W14" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" s="26" t="n">
+        <v>3</v>
+      </c>
       <c r="Y14" s="25" t="n"/>
       <c r="Z14" s="26" t="n"/>
       <c r="AA14" s="28" t="n"/>
       <c r="AB14" s="28" t="n"/>
-      <c r="AC14" s="30" t="n"/>
-      <c r="AD14" s="24" t="n"/>
+      <c r="AC14" s="30" t="n">
+        <v>0.5881999999999999</v>
+      </c>
+      <c r="AD14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:18.860547Z</t>
+        </is>
+      </c>
       <c r="AE14" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.6300 (market_slug=aec-npb-obr-trge-2026-08-05). Tie probability=0.0307.</t>
@@ -5295,18 +5351,32 @@
       </c>
       <c r="U15" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V15" s="24" t="n"/>
-      <c r="W15" s="26" t="n"/>
-      <c r="X15" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W15" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="X15" s="26" t="n">
+        <v>7</v>
+      </c>
       <c r="Y15" s="25" t="n"/>
       <c r="Z15" s="26" t="n"/>
       <c r="AA15" s="28" t="n"/>
       <c r="AB15" s="28" t="n"/>
-      <c r="AC15" s="30" t="n"/>
-      <c r="AD15" s="24" t="n"/>
+      <c r="AC15" s="30" t="n">
+        <v>0.8681</v>
+      </c>
+      <c r="AD15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:18.959265Z</t>
+        </is>
+      </c>
       <c r="AE15" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.5900 (market_slug=aec-npb-fsh-nhf-2026-08-05). Tie probability=0.0288.</t>
@@ -5564,18 +5634,32 @@
       </c>
       <c r="U16" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V16" s="24" t="n"/>
-      <c r="W16" s="26" t="n"/>
-      <c r="X16" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V16" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W16" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="X16" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y16" s="25" t="n"/>
       <c r="Z16" s="26" t="n"/>
       <c r="AA16" s="28" t="n"/>
       <c r="AB16" s="28" t="n"/>
-      <c r="AC16" s="30" t="n"/>
-      <c r="AD16" s="24" t="n"/>
+      <c r="AC16" s="30" t="n">
+        <v>0.7874</v>
+      </c>
+      <c r="AD16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:19.078808Z</t>
+        </is>
+      </c>
       <c r="AE16" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.5600 (market_slug=aec-npb-hci-ygo-2026-08-05). Tie probability=0.0336.</t>
@@ -5752,6 +5836,1620 @@
         </is>
       </c>
     </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>b6208e6608f643b2</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:04:08.876576Z</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>71688</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="H17" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J17" s="25" t="n"/>
+      <c r="K17" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L17" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="M17" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="N17" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="O17" s="28" t="n">
+        <v>0.671883</v>
+      </c>
+      <c r="P17" s="28" t="n"/>
+      <c r="Q17" s="28" t="n">
+        <v>0.06250799999999999</v>
+      </c>
+      <c r="R17" s="26" t="n">
+        <v>51</v>
+      </c>
+      <c r="S17" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U17" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V17" s="24" t="n"/>
+      <c r="W17" s="26" t="n"/>
+      <c r="X17" s="26" t="n"/>
+      <c r="Y17" s="25" t="n"/>
+      <c r="Z17" s="26" t="n"/>
+      <c r="AA17" s="28" t="n"/>
+      <c r="AB17" s="28" t="n"/>
+      <c r="AC17" s="30" t="n"/>
+      <c r="AD17" s="24" t="n"/>
+      <c r="AE17" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6100 (market_slug=aec-npb-ygo-tys-2026-08-07). Tie probability=0.0209.</t>
+        </is>
+      </c>
+      <c r="AF17" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG17" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH17" s="24" t="n"/>
+      <c r="AI17" s="31" t="n"/>
+      <c r="AJ17" s="31" t="n"/>
+      <c r="AK17" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL17" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM17" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN17" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO17" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP17" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AQ17" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AR17" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AS17" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="AT17" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="AU17" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="AV17" s="24" t="n"/>
+      <c r="AW17" s="24" t="n"/>
+      <c r="AX17" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY17" s="24" t="n"/>
+      <c r="AZ17" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA17" s="24" t="inlineStr">
+        <is>
+          <t>1397f2a2e62220577ae4a4ae8de10b8369816a7b15d915f063053eb9c759a04a</t>
+        </is>
+      </c>
+      <c r="BB17" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC17" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD17" s="24" t="inlineStr">
+        <is>
+          <t>1397f2a2e62220577ae4a4ae8de10b8369816a7b15d915f063053eb9c759a04a</t>
+        </is>
+      </c>
+      <c r="BE17" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF17" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG17" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:04:05.382616Z</t>
+        </is>
+      </c>
+      <c r="BI17" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ17" s="25" t="n"/>
+      <c r="BK17" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="BL17" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BM17" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="BN17" s="28" t="n"/>
+      <c r="BO17" s="28" t="n"/>
+      <c r="BP17" s="25" t="n"/>
+      <c r="BQ17" s="27" t="n"/>
+      <c r="BR17" s="28" t="n"/>
+      <c r="BS17" s="28" t="n"/>
+      <c r="BT17" s="28" t="n"/>
+      <c r="BU17" s="25" t="n"/>
+      <c r="BV17" s="29" t="n"/>
+      <c r="BW17" s="24" t="n"/>
+      <c r="BX17" s="30" t="n"/>
+      <c r="BY17" s="27" t="n"/>
+      <c r="BZ17" s="24" t="n"/>
+      <c r="CA17" s="31" t="n"/>
+      <c r="CB17" s="24" t="n"/>
+      <c r="CC17" s="24" t="n"/>
+      <c r="CD17" s="24" t="n"/>
+      <c r="CE17" s="24" t="n"/>
+      <c r="CF17" s="24" t="n"/>
+      <c r="CG17" s="24" t="n"/>
+      <c r="CH17" s="24" t="n"/>
+      <c r="CI17" s="24" t="n"/>
+      <c r="CJ17" s="24" t="n"/>
+      <c r="CK17" s="24" t="n"/>
+      <c r="CL17" s="24" t="n"/>
+      <c r="CM17" s="24" t="n"/>
+      <c r="CN17" s="24" t="n"/>
+      <c r="CO17" s="24" t="n"/>
+      <c r="CP17" s="24" t="n"/>
+      <c r="CQ17" s="24" t="n"/>
+      <c r="CR17" s="24" t="n"/>
+      <c r="CS17" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>a713a94747574b49</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:04:08.876576Z</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>71689</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="H18" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J18" s="25" t="n"/>
+      <c r="K18" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L18" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="M18" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="N18" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="O18" s="28" t="n">
+        <v>0.587646</v>
+      </c>
+      <c r="P18" s="28" t="n"/>
+      <c r="Q18" s="28" t="n">
+        <v>-0.08232100000000001</v>
+      </c>
+      <c r="R18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U18" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V18" s="24" t="n"/>
+      <c r="W18" s="26" t="n"/>
+      <c r="X18" s="26" t="n"/>
+      <c r="Y18" s="25" t="n"/>
+      <c r="Z18" s="26" t="n"/>
+      <c r="AA18" s="28" t="n"/>
+      <c r="AB18" s="28" t="n"/>
+      <c r="AC18" s="30" t="n"/>
+      <c r="AD18" s="24" t="n"/>
+      <c r="AE18" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6700 (market_slug=aec-npb-ybo-hci-2026-08-07). Tie probability=0.0287.</t>
+        </is>
+      </c>
+      <c r="AF18" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG18" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH18" s="24" t="n"/>
+      <c r="AI18" s="31" t="n"/>
+      <c r="AJ18" s="31" t="n"/>
+      <c r="AK18" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL18" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM18" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN18" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO18" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP18" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="AQ18" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="AR18" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="AS18" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AT18" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AU18" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AV18" s="24" t="n"/>
+      <c r="AW18" s="24" t="n"/>
+      <c r="AX18" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY18" s="24" t="n"/>
+      <c r="AZ18" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA18" s="24" t="inlineStr">
+        <is>
+          <t>1397f2a2e62220577ae4a4ae8de10b8369816a7b15d915f063053eb9c759a04a</t>
+        </is>
+      </c>
+      <c r="BB18" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC18" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD18" s="24" t="inlineStr">
+        <is>
+          <t>1397f2a2e62220577ae4a4ae8de10b8369816a7b15d915f063053eb9c759a04a</t>
+        </is>
+      </c>
+      <c r="BE18" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF18" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG18" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:04:06.385882Z</t>
+        </is>
+      </c>
+      <c r="BI18" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ18" s="25" t="n"/>
+      <c r="BK18" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="BL18" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="BM18" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="BN18" s="28" t="n"/>
+      <c r="BO18" s="28" t="n"/>
+      <c r="BP18" s="25" t="n"/>
+      <c r="BQ18" s="27" t="n"/>
+      <c r="BR18" s="28" t="n"/>
+      <c r="BS18" s="28" t="n"/>
+      <c r="BT18" s="28" t="n"/>
+      <c r="BU18" s="25" t="n"/>
+      <c r="BV18" s="29" t="n"/>
+      <c r="BW18" s="24" t="n"/>
+      <c r="BX18" s="30" t="n"/>
+      <c r="BY18" s="27" t="n"/>
+      <c r="BZ18" s="24" t="n"/>
+      <c r="CA18" s="31" t="n"/>
+      <c r="CB18" s="24" t="n"/>
+      <c r="CC18" s="24" t="n"/>
+      <c r="CD18" s="24" t="n"/>
+      <c r="CE18" s="24" t="n"/>
+      <c r="CF18" s="24" t="n"/>
+      <c r="CG18" s="24" t="n"/>
+      <c r="CH18" s="24" t="n"/>
+      <c r="CI18" s="24" t="n"/>
+      <c r="CJ18" s="24" t="n"/>
+      <c r="CK18" s="24" t="n"/>
+      <c r="CL18" s="24" t="n"/>
+      <c r="CM18" s="24" t="n"/>
+      <c r="CN18" s="24" t="n"/>
+      <c r="CO18" s="24" t="n"/>
+      <c r="CP18" s="24" t="n"/>
+      <c r="CQ18" s="24" t="n"/>
+      <c r="CR18" s="24" t="n"/>
+      <c r="CS18" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>80c41bce75c94f02</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:04:08.876576Z</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>71690</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J19" s="25" t="n"/>
+      <c r="K19" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L19" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="M19" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="N19" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="O19" s="28" t="n">
+        <v>0.577661</v>
+      </c>
+      <c r="P19" s="28" t="n"/>
+      <c r="Q19" s="28" t="n">
+        <v>-0.072689</v>
+      </c>
+      <c r="R19" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U19" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V19" s="24" t="n"/>
+      <c r="W19" s="26" t="n"/>
+      <c r="X19" s="26" t="n"/>
+      <c r="Y19" s="25" t="n"/>
+      <c r="Z19" s="26" t="n"/>
+      <c r="AA19" s="28" t="n"/>
+      <c r="AB19" s="28" t="n"/>
+      <c r="AC19" s="30" t="n"/>
+      <c r="AD19" s="24" t="n"/>
+      <c r="AE19" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6500 (market_slug=aec-npb-hta-cdh-2026-08-07). Tie probability=0.0296.</t>
+        </is>
+      </c>
+      <c r="AF19" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG19" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH19" s="24" t="n"/>
+      <c r="AI19" s="31" t="n"/>
+      <c r="AJ19" s="31" t="n"/>
+      <c r="AK19" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL19" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM19" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN19" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO19" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP19" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="AQ19" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="AR19" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="AS19" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AT19" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AU19" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AV19" s="24" t="n"/>
+      <c r="AW19" s="24" t="n"/>
+      <c r="AX19" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY19" s="24" t="n"/>
+      <c r="AZ19" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA19" s="24" t="inlineStr">
+        <is>
+          <t>1397f2a2e62220577ae4a4ae8de10b8369816a7b15d915f063053eb9c759a04a</t>
+        </is>
+      </c>
+      <c r="BB19" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC19" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD19" s="24" t="inlineStr">
+        <is>
+          <t>1397f2a2e62220577ae4a4ae8de10b8369816a7b15d915f063053eb9c759a04a</t>
+        </is>
+      </c>
+      <c r="BE19" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF19" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG19" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:04:06.951384Z</t>
+        </is>
+      </c>
+      <c r="BI19" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ19" s="25" t="n"/>
+      <c r="BK19" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="BL19" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="BM19" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="BN19" s="28" t="n"/>
+      <c r="BO19" s="28" t="n"/>
+      <c r="BP19" s="25" t="n"/>
+      <c r="BQ19" s="27" t="n"/>
+      <c r="BR19" s="28" t="n"/>
+      <c r="BS19" s="28" t="n"/>
+      <c r="BT19" s="28" t="n"/>
+      <c r="BU19" s="25" t="n"/>
+      <c r="BV19" s="29" t="n"/>
+      <c r="BW19" s="24" t="n"/>
+      <c r="BX19" s="30" t="n"/>
+      <c r="BY19" s="27" t="n"/>
+      <c r="BZ19" s="24" t="n"/>
+      <c r="CA19" s="31" t="n"/>
+      <c r="CB19" s="24" t="n"/>
+      <c r="CC19" s="24" t="n"/>
+      <c r="CD19" s="24" t="n"/>
+      <c r="CE19" s="24" t="n"/>
+      <c r="CF19" s="24" t="n"/>
+      <c r="CG19" s="24" t="n"/>
+      <c r="CH19" s="24" t="n"/>
+      <c r="CI19" s="24" t="n"/>
+      <c r="CJ19" s="24" t="n"/>
+      <c r="CK19" s="24" t="n"/>
+      <c r="CL19" s="24" t="n"/>
+      <c r="CM19" s="24" t="n"/>
+      <c r="CN19" s="24" t="n"/>
+      <c r="CO19" s="24" t="n"/>
+      <c r="CP19" s="24" t="n"/>
+      <c r="CQ19" s="24" t="n"/>
+      <c r="CR19" s="24" t="n"/>
+      <c r="CS19" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>8af9beec062f4eb8</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:04:08.876576Z</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>71691</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>Tohoku Rakuten Golden Eagles</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="H20" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J20" s="25" t="n"/>
+      <c r="K20" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L20" s="26" t="n">
+        <v>-257</v>
+      </c>
+      <c r="M20" s="27" t="n">
+        <v>1.389105</v>
+      </c>
+      <c r="N20" s="28" t="n">
+        <v>0.719888</v>
+      </c>
+      <c r="O20" s="28" t="n">
+        <v>0.648431</v>
+      </c>
+      <c r="P20" s="28" t="n"/>
+      <c r="Q20" s="28" t="n">
+        <v>-0.07145700000000001</v>
+      </c>
+      <c r="R20" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U20" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V20" s="24" t="n"/>
+      <c r="W20" s="26" t="n"/>
+      <c r="X20" s="26" t="n"/>
+      <c r="Y20" s="25" t="n"/>
+      <c r="Z20" s="26" t="n"/>
+      <c r="AA20" s="28" t="n"/>
+      <c r="AB20" s="28" t="n"/>
+      <c r="AC20" s="30" t="n"/>
+      <c r="AD20" s="24" t="n"/>
+      <c r="AE20" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.7200 (market_slug=aec-npb-nhf-trge-2026-08-07). Tie probability=0.0232.</t>
+        </is>
+      </c>
+      <c r="AF20" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG20" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH20" s="24" t="n"/>
+      <c r="AI20" s="31" t="n"/>
+      <c r="AJ20" s="31" t="n"/>
+      <c r="AK20" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL20" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM20" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN20" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO20" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP20" s="24" t="inlineStr">
+        <is>
+          <t>Tohoku Rakuten Golden Eagles</t>
+        </is>
+      </c>
+      <c r="AQ20" s="24" t="inlineStr">
+        <is>
+          <t>Tohoku Rakuten Golden Eagles</t>
+        </is>
+      </c>
+      <c r="AR20" s="24" t="inlineStr">
+        <is>
+          <t>Tohoku Rakuten Golden Eagles</t>
+        </is>
+      </c>
+      <c r="AS20" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AT20" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AU20" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AV20" s="24" t="n"/>
+      <c r="AW20" s="24" t="n"/>
+      <c r="AX20" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY20" s="24" t="n"/>
+      <c r="AZ20" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA20" s="24" t="inlineStr">
+        <is>
+          <t>1397f2a2e62220577ae4a4ae8de10b8369816a7b15d915f063053eb9c759a04a</t>
+        </is>
+      </c>
+      <c r="BB20" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC20" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD20" s="24" t="inlineStr">
+        <is>
+          <t>1397f2a2e62220577ae4a4ae8de10b8369816a7b15d915f063053eb9c759a04a</t>
+        </is>
+      </c>
+      <c r="BE20" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF20" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG20" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:04:07.658626Z</t>
+        </is>
+      </c>
+      <c r="BI20" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ20" s="25" t="n"/>
+      <c r="BK20" s="26" t="n">
+        <v>-257</v>
+      </c>
+      <c r="BL20" s="27" t="n">
+        <v>1.389105</v>
+      </c>
+      <c r="BM20" s="28" t="n">
+        <v>0.719888</v>
+      </c>
+      <c r="BN20" s="28" t="n"/>
+      <c r="BO20" s="28" t="n"/>
+      <c r="BP20" s="25" t="n"/>
+      <c r="BQ20" s="27" t="n"/>
+      <c r="BR20" s="28" t="n"/>
+      <c r="BS20" s="28" t="n"/>
+      <c r="BT20" s="28" t="n"/>
+      <c r="BU20" s="25" t="n"/>
+      <c r="BV20" s="29" t="n"/>
+      <c r="BW20" s="24" t="n"/>
+      <c r="BX20" s="30" t="n"/>
+      <c r="BY20" s="27" t="n"/>
+      <c r="BZ20" s="24" t="n"/>
+      <c r="CA20" s="31" t="n"/>
+      <c r="CB20" s="24" t="n"/>
+      <c r="CC20" s="24" t="n"/>
+      <c r="CD20" s="24" t="n"/>
+      <c r="CE20" s="24" t="n"/>
+      <c r="CF20" s="24" t="n"/>
+      <c r="CG20" s="24" t="n"/>
+      <c r="CH20" s="24" t="n"/>
+      <c r="CI20" s="24" t="n"/>
+      <c r="CJ20" s="24" t="n"/>
+      <c r="CK20" s="24" t="n"/>
+      <c r="CL20" s="24" t="n"/>
+      <c r="CM20" s="24" t="n"/>
+      <c r="CN20" s="24" t="n"/>
+      <c r="CO20" s="24" t="n"/>
+      <c r="CP20" s="24" t="n"/>
+      <c r="CQ20" s="24" t="n"/>
+      <c r="CR20" s="24" t="n"/>
+      <c r="CS20" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>53df51dcf4ef4440</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:04:08.876576Z</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>71692</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="H21" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J21" s="25" t="n"/>
+      <c r="K21" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L21" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M21" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N21" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O21" s="28" t="n">
+        <v>0.57184</v>
+      </c>
+      <c r="P21" s="28" t="n"/>
+      <c r="Q21" s="28" t="n">
+        <v>-0.02816</v>
+      </c>
+      <c r="R21" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="S21" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U21" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V21" s="24" t="n"/>
+      <c r="W21" s="26" t="n"/>
+      <c r="X21" s="26" t="n"/>
+      <c r="Y21" s="25" t="n"/>
+      <c r="Z21" s="26" t="n"/>
+      <c r="AA21" s="28" t="n"/>
+      <c r="AB21" s="28" t="n"/>
+      <c r="AC21" s="30" t="n"/>
+      <c r="AD21" s="24" t="n"/>
+      <c r="AE21" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6000 (market_slug=aec-npb-ssl-fsh-2026-08-07). Tie probability=0.0301.</t>
+        </is>
+      </c>
+      <c r="AF21" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG21" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH21" s="24" t="n"/>
+      <c r="AI21" s="31" t="n"/>
+      <c r="AJ21" s="31" t="n"/>
+      <c r="AK21" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL21" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM21" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN21" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO21" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP21" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="AQ21" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="AR21" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="AS21" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AT21" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AU21" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AV21" s="24" t="n"/>
+      <c r="AW21" s="24" t="n"/>
+      <c r="AX21" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY21" s="24" t="n"/>
+      <c r="AZ21" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA21" s="24" t="inlineStr">
+        <is>
+          <t>1397f2a2e62220577ae4a4ae8de10b8369816a7b15d915f063053eb9c759a04a</t>
+        </is>
+      </c>
+      <c r="BB21" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC21" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD21" s="24" t="inlineStr">
+        <is>
+          <t>1397f2a2e62220577ae4a4ae8de10b8369816a7b15d915f063053eb9c759a04a</t>
+        </is>
+      </c>
+      <c r="BE21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG21" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:04:08.234637Z</t>
+        </is>
+      </c>
+      <c r="BI21" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ21" s="25" t="n"/>
+      <c r="BK21" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL21" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM21" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN21" s="28" t="n"/>
+      <c r="BO21" s="28" t="n"/>
+      <c r="BP21" s="25" t="n"/>
+      <c r="BQ21" s="27" t="n"/>
+      <c r="BR21" s="28" t="n"/>
+      <c r="BS21" s="28" t="n"/>
+      <c r="BT21" s="28" t="n"/>
+      <c r="BU21" s="25" t="n"/>
+      <c r="BV21" s="29" t="n"/>
+      <c r="BW21" s="24" t="n"/>
+      <c r="BX21" s="30" t="n"/>
+      <c r="BY21" s="27" t="n"/>
+      <c r="BZ21" s="24" t="n"/>
+      <c r="CA21" s="31" t="n"/>
+      <c r="CB21" s="24" t="n"/>
+      <c r="CC21" s="24" t="n"/>
+      <c r="CD21" s="24" t="n"/>
+      <c r="CE21" s="24" t="n"/>
+      <c r="CF21" s="24" t="n"/>
+      <c r="CG21" s="24" t="n"/>
+      <c r="CH21" s="24" t="n"/>
+      <c r="CI21" s="24" t="n"/>
+      <c r="CJ21" s="24" t="n"/>
+      <c r="CK21" s="24" t="n"/>
+      <c r="CL21" s="24" t="n"/>
+      <c r="CM21" s="24" t="n"/>
+      <c r="CN21" s="24" t="n"/>
+      <c r="CO21" s="24" t="n"/>
+      <c r="CP21" s="24" t="n"/>
+      <c r="CQ21" s="24" t="n"/>
+      <c r="CR21" s="24" t="n"/>
+      <c r="CS21" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>09a39aaa7814454e</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:04:08.876576Z</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>71693</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>Orix Buffaloes</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
+        <is>
+          <t>Chiba Lotte Marines</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J22" s="25" t="n"/>
+      <c r="K22" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L22" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="M22" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="N22" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="O22" s="28" t="n">
+        <v>0.5519500000000001</v>
+      </c>
+      <c r="P22" s="28" t="n"/>
+      <c r="Q22" s="28" t="n">
+        <v>0.021434</v>
+      </c>
+      <c r="R22" s="26" t="n">
+        <v>31</v>
+      </c>
+      <c r="S22" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U22" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V22" s="24" t="n"/>
+      <c r="W22" s="26" t="n"/>
+      <c r="X22" s="26" t="n"/>
+      <c r="Y22" s="25" t="n"/>
+      <c r="Z22" s="26" t="n"/>
+      <c r="AA22" s="28" t="n"/>
+      <c r="AB22" s="28" t="n"/>
+      <c r="AC22" s="30" t="n"/>
+      <c r="AD22" s="24" t="n"/>
+      <c r="AE22" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5300 (market_slug=aec-npb-clm-obr-2026-08-07). Tie probability=0.0318.</t>
+        </is>
+      </c>
+      <c r="AF22" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG22" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH22" s="24" t="n"/>
+      <c r="AI22" s="31" t="n"/>
+      <c r="AJ22" s="31" t="n"/>
+      <c r="AK22" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL22" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM22" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN22" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO22" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP22" s="24" t="inlineStr">
+        <is>
+          <t>Orix Buffaloes</t>
+        </is>
+      </c>
+      <c r="AQ22" s="24" t="inlineStr">
+        <is>
+          <t>Orix Buffaloes</t>
+        </is>
+      </c>
+      <c r="AR22" s="24" t="inlineStr">
+        <is>
+          <t>Orix Buffaloes</t>
+        </is>
+      </c>
+      <c r="AS22" s="24" t="inlineStr">
+        <is>
+          <t>Chiba Lotte Marines</t>
+        </is>
+      </c>
+      <c r="AT22" s="24" t="inlineStr">
+        <is>
+          <t>Chiba Lotte Marines</t>
+        </is>
+      </c>
+      <c r="AU22" s="24" t="inlineStr">
+        <is>
+          <t>Chiba Lotte Marines</t>
+        </is>
+      </c>
+      <c r="AV22" s="24" t="n"/>
+      <c r="AW22" s="24" t="n"/>
+      <c r="AX22" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY22" s="24" t="n"/>
+      <c r="AZ22" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA22" s="24" t="inlineStr">
+        <is>
+          <t>1397f2a2e62220577ae4a4ae8de10b8369816a7b15d915f063053eb9c759a04a</t>
+        </is>
+      </c>
+      <c r="BB22" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC22" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD22" s="24" t="inlineStr">
+        <is>
+          <t>1397f2a2e62220577ae4a4ae8de10b8369816a7b15d915f063053eb9c759a04a</t>
+        </is>
+      </c>
+      <c r="BE22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG22" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:04:08.876525Z</t>
+        </is>
+      </c>
+      <c r="BI22" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ22" s="25" t="n"/>
+      <c r="BK22" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="BL22" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BM22" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="BN22" s="28" t="n"/>
+      <c r="BO22" s="28" t="n"/>
+      <c r="BP22" s="25" t="n"/>
+      <c r="BQ22" s="27" t="n"/>
+      <c r="BR22" s="28" t="n"/>
+      <c r="BS22" s="28" t="n"/>
+      <c r="BT22" s="28" t="n"/>
+      <c r="BU22" s="25" t="n"/>
+      <c r="BV22" s="29" t="n"/>
+      <c r="BW22" s="24" t="n"/>
+      <c r="BX22" s="30" t="n"/>
+      <c r="BY22" s="27" t="n"/>
+      <c r="BZ22" s="24" t="n"/>
+      <c r="CA22" s="31" t="n"/>
+      <c r="CB22" s="24" t="n"/>
+      <c r="CC22" s="24" t="n"/>
+      <c r="CD22" s="24" t="n"/>
+      <c r="CE22" s="24" t="n"/>
+      <c r="CF22" s="24" t="n"/>
+      <c r="CG22" s="24" t="n"/>
+      <c r="CH22" s="24" t="n"/>
+      <c r="CI22" s="24" t="n"/>
+      <c r="CJ22" s="24" t="n"/>
+      <c r="CK22" s="24" t="n"/>
+      <c r="CL22" s="24" t="n"/>
+      <c r="CM22" s="24" t="n"/>
+      <c r="CN22" s="24" t="n"/>
+      <c r="CO22" s="24" t="n"/>
+      <c r="CP22" s="24" t="n"/>
+      <c r="CQ22" s="24" t="n"/>
+      <c r="CR22" s="24" t="n"/>
+      <c r="CS22" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/npb.xlsx
+++ b/data/research/npb.xlsx
@@ -5917,18 +5917,32 @@
       </c>
       <c r="U17" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V17" s="24" t="n"/>
-      <c r="W17" s="26" t="n"/>
-      <c r="X17" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V17" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W17" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y17" s="25" t="n"/>
       <c r="Z17" s="26" t="n"/>
       <c r="AA17" s="28" t="n"/>
       <c r="AB17" s="28" t="n"/>
-      <c r="AC17" s="30" t="n"/>
-      <c r="AD17" s="24" t="n"/>
+      <c r="AC17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:21.798527Z</t>
+        </is>
+      </c>
       <c r="AE17" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.6100 (market_slug=aec-npb-ygo-tys-2026-08-07). Tie probability=0.0209.</t>
@@ -5941,7 +5955,7 @@
       </c>
       <c r="AG17" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH17" s="24" t="n"/>
@@ -6186,18 +6200,32 @@
       </c>
       <c r="U18" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V18" s="24" t="n"/>
-      <c r="W18" s="26" t="n"/>
-      <c r="X18" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V18" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W18" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y18" s="25" t="n"/>
       <c r="Z18" s="26" t="n"/>
       <c r="AA18" s="28" t="n"/>
       <c r="AB18" s="28" t="n"/>
-      <c r="AC18" s="30" t="n"/>
-      <c r="AD18" s="24" t="n"/>
+      <c r="AC18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:22.019890Z</t>
+        </is>
+      </c>
       <c r="AE18" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.6700 (market_slug=aec-npb-ybo-hci-2026-08-07). Tie probability=0.0287.</t>
@@ -6455,18 +6483,32 @@
       </c>
       <c r="U19" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V19" s="24" t="n"/>
-      <c r="W19" s="26" t="n"/>
-      <c r="X19" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V19" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W19" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X19" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y19" s="25" t="n"/>
       <c r="Z19" s="26" t="n"/>
       <c r="AA19" s="28" t="n"/>
       <c r="AB19" s="28" t="n"/>
-      <c r="AC19" s="30" t="n"/>
-      <c r="AD19" s="24" t="n"/>
+      <c r="AC19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:22.321727Z</t>
+        </is>
+      </c>
       <c r="AE19" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.6500 (market_slug=aec-npb-hta-cdh-2026-08-07). Tie probability=0.0296.</t>
@@ -6479,7 +6521,7 @@
       </c>
       <c r="AG19" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH19" s="24" t="n"/>
@@ -6724,18 +6766,32 @@
       </c>
       <c r="U20" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V20" s="24" t="n"/>
-      <c r="W20" s="26" t="n"/>
-      <c r="X20" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V20" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W20" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="X20" s="26" t="n">
+        <v>3</v>
+      </c>
       <c r="Y20" s="25" t="n"/>
       <c r="Z20" s="26" t="n"/>
       <c r="AA20" s="28" t="n"/>
       <c r="AB20" s="28" t="n"/>
-      <c r="AC20" s="30" t="n"/>
-      <c r="AD20" s="24" t="n"/>
+      <c r="AC20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:22.543840Z</t>
+        </is>
+      </c>
       <c r="AE20" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.7200 (market_slug=aec-npb-nhf-trge-2026-08-07). Tie probability=0.0232.</t>
@@ -6993,18 +7049,32 @@
       </c>
       <c r="U21" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V21" s="24" t="n"/>
-      <c r="W21" s="26" t="n"/>
-      <c r="X21" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V21" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W21" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="X21" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y21" s="25" t="n"/>
       <c r="Z21" s="26" t="n"/>
       <c r="AA21" s="28" t="n"/>
       <c r="AB21" s="28" t="n"/>
-      <c r="AC21" s="30" t="n"/>
-      <c r="AD21" s="24" t="n"/>
+      <c r="AC21" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:22.762636Z</t>
+        </is>
+      </c>
       <c r="AE21" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.6000 (market_slug=aec-npb-ssl-fsh-2026-08-07). Tie probability=0.0301.</t>
@@ -7262,18 +7332,32 @@
       </c>
       <c r="U22" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V22" s="24" t="n"/>
-      <c r="W22" s="26" t="n"/>
-      <c r="X22" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V22" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W22" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="X22" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y22" s="25" t="n"/>
       <c r="Z22" s="26" t="n"/>
       <c r="AA22" s="28" t="n"/>
       <c r="AB22" s="28" t="n"/>
-      <c r="AC22" s="30" t="n"/>
-      <c r="AD22" s="24" t="n"/>
+      <c r="AC22" s="30" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AD22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:22.989329Z</t>
+        </is>
+      </c>
       <c r="AE22" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.5300 (market_slug=aec-npb-clm-obr-2026-08-07). Tie probability=0.0318.</t>
@@ -7286,7 +7370,7 @@
       </c>
       <c r="AG22" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH22" s="24" t="n"/>

--- a/data/research/npb.xlsx
+++ b/data/research/npb.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Picks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Picks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS10" headerRowCount="1">
-  <autoFilter ref="A1:CS10"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS38" headerRowCount="1">
+  <autoFilter ref="A1:CS38"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$10)</f>
+        <f>COUNTA('Picks'!$A$2:$A$38)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$10,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$38,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$10,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$38,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")+COUNTIFS('Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"win")+COUNTIFS('Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$10,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$38,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$38,"&gt;0",'Picks'!$V$2:$V$38,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$38,"&gt;0",'Picks'!$V$2:$V$38,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")/(COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"win")+COUNTIFS('Picks'!$BX$2:$BX$10,"&gt;0",'Picks'!$V$2:$V$10,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$38,"&gt;0",'Picks'!$V$2:$V$38,"win")/(COUNTIFS('Picks'!$BX$2:$BX$38,"&gt;0",'Picks'!$V$2:$V$38,"win")+COUNTIFS('Picks'!$BX$2:$BX$38,"&gt;0",'Picks'!$V$2:$V$38,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$10)/SUM('Picks'!$BX$2:$BX$10),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$38)/SUM('Picks'!$BX$2:$BX$38),0)</f>
         <v/>
       </c>
     </row>
@@ -836,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$10)</f>
+        <f>SUM('Picks'!$BY$2:$BY$38)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$10,"&lt;&gt;",'Picks'!$AB$2:$AB$10),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$38,"&lt;&gt;",'Picks'!$AB$2:$AB$38),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$10,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$10,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$38,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$38,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$10,'Picks'!$AM$2:$AM$10,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$38,'Picks'!$AM$2:$AM$38,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A14,'Picks'!$U$2:$U$38,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A14,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A14,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -919,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$38,'Picks'!$H$2:$H$38,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A14,'Picks'!$U$2:$U$10,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$38,'Picks'!$H$2:$H$38,$A14,'Picks'!$U$2:$U$38,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A15,'Picks'!$U$2:$U$38,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A15,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A15,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -950,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$38,'Picks'!$H$2:$H$38,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A15,'Picks'!$U$2:$U$10,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$38,'Picks'!$H$2:$H$38,$A15,'Picks'!$U$2:$U$38,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A16,'Picks'!$U$2:$U$38,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A16,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled",'Picks'!$V$2:$V$10,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$38,$A16,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -981,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$10,'Picks'!$H$2:$H$10,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$38,'Picks'!$H$2:$H$38,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$10,'Picks'!$H$2:$H$10,$A16,'Picks'!$U$2:$U$10,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$38,'Picks'!$H$2:$H$38,$A16,'Picks'!$U$2:$U$38,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS10"/>
+  <dimension ref="A1:CS38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1859,8 +1859,12 @@
       <c r="BU2" s="25" t="n"/>
       <c r="BV2" s="29" t="n"/>
       <c r="BW2" s="24" t="n"/>
-      <c r="BX2" s="30" t="n"/>
-      <c r="BY2" s="27" t="n"/>
+      <c r="BX2" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY2" s="27" t="n">
+        <v>0.91</v>
+      </c>
       <c r="BZ2" s="24" t="n"/>
       <c r="CA2" s="31" t="n"/>
       <c r="CB2" s="24" t="n"/>
@@ -2138,8 +2142,12 @@
       <c r="BU3" s="25" t="n"/>
       <c r="BV3" s="29" t="n"/>
       <c r="BW3" s="24" t="n"/>
-      <c r="BX3" s="30" t="n"/>
-      <c r="BY3" s="27" t="n"/>
+      <c r="BX3" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY3" s="27" t="n">
+        <v>0.91</v>
+      </c>
       <c r="BZ3" s="24" t="n"/>
       <c r="CA3" s="31" t="n"/>
       <c r="CB3" s="24" t="n"/>
@@ -2417,8 +2425,12 @@
       <c r="BU4" s="25" t="n"/>
       <c r="BV4" s="29" t="n"/>
       <c r="BW4" s="24" t="n"/>
-      <c r="BX4" s="30" t="n"/>
-      <c r="BY4" s="27" t="n"/>
+      <c r="BX4" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY4" s="27" t="n">
+        <v>0.91</v>
+      </c>
       <c r="BZ4" s="24" t="n"/>
       <c r="CA4" s="31" t="n"/>
       <c r="CB4" s="24" t="n"/>
@@ -2696,8 +2708,12 @@
       <c r="BU5" s="25" t="n"/>
       <c r="BV5" s="29" t="n"/>
       <c r="BW5" s="24" t="n"/>
-      <c r="BX5" s="30" t="n"/>
-      <c r="BY5" s="27" t="n"/>
+      <c r="BX5" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY5" s="27" t="n">
+        <v>0.91</v>
+      </c>
       <c r="BZ5" s="24" t="n"/>
       <c r="CA5" s="31" t="n"/>
       <c r="CB5" s="24" t="n"/>
@@ -2804,18 +2820,32 @@
       </c>
       <c r="U6" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V6" s="24" t="n"/>
-      <c r="W6" s="26" t="n"/>
-      <c r="X6" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V6" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W6" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y6" s="25" t="n"/>
       <c r="Z6" s="26" t="n"/>
       <c r="AA6" s="28" t="n"/>
       <c r="AB6" s="28" t="n"/>
-      <c r="AC6" s="30" t="n"/>
-      <c r="AD6" s="24" t="n"/>
+      <c r="AC6" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD6" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:04:43.764923Z</t>
+        </is>
+      </c>
       <c r="AE6" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.6200 (market_slug=aec-npb-ybo-hta-2026-08-04). Tie probability=0.0344.</t>
@@ -2828,7 +2858,7 @@
       </c>
       <c r="AG6" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH6" s="24" t="n"/>
@@ -2965,8 +2995,12 @@
       <c r="BU6" s="25" t="n"/>
       <c r="BV6" s="29" t="n"/>
       <c r="BW6" s="24" t="n"/>
-      <c r="BX6" s="30" t="n"/>
-      <c r="BY6" s="27" t="n"/>
+      <c r="BX6" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY6" s="27" t="n">
+        <v>-1</v>
+      </c>
       <c r="BZ6" s="24" t="n"/>
       <c r="CA6" s="31" t="n"/>
       <c r="CB6" s="24" t="n"/>
@@ -3073,18 +3107,32 @@
       </c>
       <c r="U7" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V7" s="24" t="n"/>
-      <c r="W7" s="26" t="n"/>
-      <c r="X7" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V7" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W7" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X7" s="26" t="n">
+        <v>4</v>
+      </c>
       <c r="Y7" s="25" t="n"/>
       <c r="Z7" s="26" t="n"/>
       <c r="AA7" s="28" t="n"/>
       <c r="AB7" s="28" t="n"/>
-      <c r="AC7" s="30" t="n"/>
-      <c r="AD7" s="24" t="n"/>
+      <c r="AC7" s="30" t="n">
+        <v>0.6443</v>
+      </c>
+      <c r="AD7" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:04:43.845421Z</t>
+        </is>
+      </c>
       <c r="AE7" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.6600 (market_slug=aec-npb-cdh-tys-2026-08-04). Tie probability=0.0280.</t>
@@ -3234,8 +3282,12 @@
       <c r="BU7" s="25" t="n"/>
       <c r="BV7" s="29" t="n"/>
       <c r="BW7" s="24" t="n"/>
-      <c r="BX7" s="30" t="n"/>
-      <c r="BY7" s="27" t="n"/>
+      <c r="BX7" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY7" s="27" t="n">
+        <v>0.91</v>
+      </c>
       <c r="BZ7" s="24" t="n"/>
       <c r="CA7" s="31" t="n"/>
       <c r="CB7" s="24" t="n"/>
@@ -3342,18 +3394,32 @@
       </c>
       <c r="U8" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V8" s="24" t="n"/>
-      <c r="W8" s="26" t="n"/>
-      <c r="X8" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V8" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W8" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X8" s="26" t="n">
+        <v>4</v>
+      </c>
       <c r="Y8" s="25" t="n"/>
       <c r="Z8" s="26" t="n"/>
       <c r="AA8" s="28" t="n"/>
       <c r="AB8" s="28" t="n"/>
-      <c r="AC8" s="30" t="n"/>
-      <c r="AD8" s="24" t="n"/>
+      <c r="AC8" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD8" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:04:43.918073Z</t>
+        </is>
+      </c>
       <c r="AE8" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.4800 (market_slug=aec-npb-hci-ygo-2026-08-04). Tie probability=0.0325.</t>
@@ -3366,7 +3432,7 @@
       </c>
       <c r="AG8" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH8" s="24" t="n"/>
@@ -3503,8 +3569,12 @@
       <c r="BU8" s="25" t="n"/>
       <c r="BV8" s="29" t="n"/>
       <c r="BW8" s="24" t="n"/>
-      <c r="BX8" s="30" t="n"/>
-      <c r="BY8" s="27" t="n"/>
+      <c r="BX8" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY8" s="27" t="n">
+        <v>-1</v>
+      </c>
       <c r="BZ8" s="24" t="n"/>
       <c r="CA8" s="31" t="n"/>
       <c r="CB8" s="24" t="n"/>
@@ -3611,18 +3681,32 @@
       </c>
       <c r="U9" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V9" s="24" t="n"/>
-      <c r="W9" s="26" t="n"/>
-      <c r="X9" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V9" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W9" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X9" s="26" t="n">
+        <v>5</v>
+      </c>
       <c r="Y9" s="25" t="n"/>
       <c r="Z9" s="26" t="n"/>
       <c r="AA9" s="28" t="n"/>
       <c r="AB9" s="28" t="n"/>
-      <c r="AC9" s="30" t="n"/>
-      <c r="AD9" s="24" t="n"/>
+      <c r="AC9" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD9" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:04:43.989853Z</t>
+        </is>
+      </c>
       <c r="AE9" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.5700 (market_slug=aec-npb-clm-ssl-2026-08-04). Tie probability=0.0340.</t>
@@ -3635,7 +3719,7 @@
       </c>
       <c r="AG9" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH9" s="24" t="n"/>
@@ -3772,8 +3856,12 @@
       <c r="BU9" s="25" t="n"/>
       <c r="BV9" s="29" t="n"/>
       <c r="BW9" s="24" t="n"/>
-      <c r="BX9" s="30" t="n"/>
-      <c r="BY9" s="27" t="n"/>
+      <c r="BX9" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY9" s="27" t="n">
+        <v>-1</v>
+      </c>
       <c r="BZ9" s="24" t="n"/>
       <c r="CA9" s="31" t="n"/>
       <c r="CB9" s="24" t="n"/>
@@ -3880,18 +3968,32 @@
       </c>
       <c r="U10" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V10" s="24" t="n"/>
-      <c r="W10" s="26" t="n"/>
-      <c r="X10" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V10" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y10" s="25" t="n"/>
       <c r="Z10" s="26" t="n"/>
       <c r="AA10" s="28" t="n"/>
       <c r="AB10" s="28" t="n"/>
-      <c r="AC10" s="30" t="n"/>
-      <c r="AD10" s="24" t="n"/>
+      <c r="AC10" s="30" t="n">
+        <v>0.8013</v>
+      </c>
+      <c r="AD10" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T18:04:44.062623Z</t>
+        </is>
+      </c>
       <c r="AE10" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.6100 (market_slug=aec-npb-fsh-nhf-2026-08-04). Tie probability=0.0295.</t>
@@ -4041,8 +4143,12 @@
       <c r="BU10" s="25" t="n"/>
       <c r="BV10" s="29" t="n"/>
       <c r="BW10" s="24" t="n"/>
-      <c r="BX10" s="30" t="n"/>
-      <c r="BY10" s="27" t="n"/>
+      <c r="BX10" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY10" s="27" t="n">
+        <v>0.91</v>
+      </c>
       <c r="BZ10" s="24" t="n"/>
       <c r="CA10" s="31" t="n"/>
       <c r="CB10" s="24" t="n"/>
@@ -4068,6 +4174,7934 @@
         </is>
       </c>
     </row>
+    <row r="11" ht="36" customHeight="1">
+      <c r="A11" s="24" t="inlineStr">
+        <is>
+          <t>ba889f1490334b55</t>
+        </is>
+      </c>
+      <c r="B11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:53.416116Z</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T08:45:00Z</t>
+        </is>
+      </c>
+      <c r="D11" s="24" t="inlineStr">
+        <is>
+          <t>69524</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F11" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="G11" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="H11" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I11" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J11" s="25" t="n"/>
+      <c r="K11" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L11" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M11" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N11" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O11" s="28" t="n">
+        <v>0.512165</v>
+      </c>
+      <c r="P11" s="28" t="n"/>
+      <c r="Q11" s="28" t="n">
+        <v>-0.087835</v>
+      </c>
+      <c r="R11" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U11" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V11" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W11" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="X11" s="26" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y11" s="25" t="n"/>
+      <c r="Z11" s="26" t="n"/>
+      <c r="AA11" s="28" t="n"/>
+      <c r="AB11" s="28" t="n"/>
+      <c r="AC11" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:18.583620Z</t>
+        </is>
+      </c>
+      <c r="AE11" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6000 (market_slug=aec-npb-ybo-hta-2026-08-05). Tie probability=0.0354.</t>
+        </is>
+      </c>
+      <c r="AF11" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG11" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH11" s="24" t="n"/>
+      <c r="AI11" s="31" t="n"/>
+      <c r="AJ11" s="31" t="n"/>
+      <c r="AK11" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL11" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM11" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN11" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO11" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP11" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AQ11" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AR11" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AS11" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AT11" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AU11" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AV11" s="24" t="n"/>
+      <c r="AW11" s="24" t="n"/>
+      <c r="AX11" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY11" s="24" t="n"/>
+      <c r="AZ11" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA11" s="24" t="inlineStr">
+        <is>
+          <t>587c95488a5eab49a474c082a9d83bc1218cd1ce498682f7305ccc207cdae6d9</t>
+        </is>
+      </c>
+      <c r="BB11" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC11" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD11" s="24" t="inlineStr">
+        <is>
+          <t>587c95488a5eab49a474c082a9d83bc1218cd1ce498682f7305ccc207cdae6d9</t>
+        </is>
+      </c>
+      <c r="BE11" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF11" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG11" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH11" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:49.025090Z</t>
+        </is>
+      </c>
+      <c r="BI11" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ11" s="25" t="n"/>
+      <c r="BK11" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL11" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM11" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN11" s="28" t="n"/>
+      <c r="BO11" s="28" t="n"/>
+      <c r="BP11" s="25" t="n"/>
+      <c r="BQ11" s="27" t="n"/>
+      <c r="BR11" s="28" t="n"/>
+      <c r="BS11" s="28" t="n"/>
+      <c r="BT11" s="28" t="n"/>
+      <c r="BU11" s="25" t="n"/>
+      <c r="BV11" s="29" t="n"/>
+      <c r="BW11" s="24" t="n"/>
+      <c r="BX11" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY11" s="27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BZ11" s="24" t="n"/>
+      <c r="CA11" s="31" t="n"/>
+      <c r="CB11" s="24" t="n"/>
+      <c r="CC11" s="24" t="n"/>
+      <c r="CD11" s="24" t="n"/>
+      <c r="CE11" s="24" t="n"/>
+      <c r="CF11" s="24" t="n"/>
+      <c r="CG11" s="24" t="n"/>
+      <c r="CH11" s="24" t="n"/>
+      <c r="CI11" s="24" t="n"/>
+      <c r="CJ11" s="24" t="n"/>
+      <c r="CK11" s="24" t="n"/>
+      <c r="CL11" s="24" t="n"/>
+      <c r="CM11" s="24" t="n"/>
+      <c r="CN11" s="24" t="n"/>
+      <c r="CO11" s="24" t="n"/>
+      <c r="CP11" s="24" t="n"/>
+      <c r="CQ11" s="24" t="n"/>
+      <c r="CR11" s="24" t="n"/>
+      <c r="CS11" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="36" customHeight="1">
+      <c r="A12" s="24" t="inlineStr">
+        <is>
+          <t>4fee8ebfb11943f8</t>
+        </is>
+      </c>
+      <c r="B12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:53.416116Z</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>69525</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F12" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="G12" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="H12" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J12" s="25" t="n"/>
+      <c r="K12" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L12" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="M12" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="N12" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="O12" s="28" t="n">
+        <v>0.605094</v>
+      </c>
+      <c r="P12" s="28" t="n"/>
+      <c r="Q12" s="28" t="n">
+        <v>0.055544</v>
+      </c>
+      <c r="R12" s="26" t="n">
+        <v>48</v>
+      </c>
+      <c r="S12" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T12" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U12" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V12" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W12" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y12" s="25" t="n"/>
+      <c r="Z12" s="26" t="n"/>
+      <c r="AA12" s="28" t="n"/>
+      <c r="AB12" s="28" t="n"/>
+      <c r="AC12" s="30" t="n">
+        <v>1.0246</v>
+      </c>
+      <c r="AD12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:18.684954Z</t>
+        </is>
+      </c>
+      <c r="AE12" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5500 (market_slug=aec-npb-cdh-tys-2026-08-05). Tie probability=0.0272.</t>
+        </is>
+      </c>
+      <c r="AF12" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG12" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH12" s="24" t="n"/>
+      <c r="AI12" s="31" t="n"/>
+      <c r="AJ12" s="31" t="n"/>
+      <c r="AK12" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL12" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM12" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN12" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO12" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP12" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AQ12" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AR12" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AS12" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="AT12" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="AU12" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="AV12" s="24" t="n"/>
+      <c r="AW12" s="24" t="n"/>
+      <c r="AX12" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY12" s="24" t="n"/>
+      <c r="AZ12" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA12" s="24" t="inlineStr">
+        <is>
+          <t>587c95488a5eab49a474c082a9d83bc1218cd1ce498682f7305ccc207cdae6d9</t>
+        </is>
+      </c>
+      <c r="BB12" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC12" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD12" s="24" t="inlineStr">
+        <is>
+          <t>587c95488a5eab49a474c082a9d83bc1218cd1ce498682f7305ccc207cdae6d9</t>
+        </is>
+      </c>
+      <c r="BE12" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF12" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG12" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH12" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:49.865696Z</t>
+        </is>
+      </c>
+      <c r="BI12" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ12" s="25" t="n"/>
+      <c r="BK12" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="BL12" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="BM12" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="BN12" s="28" t="n"/>
+      <c r="BO12" s="28" t="n"/>
+      <c r="BP12" s="25" t="n"/>
+      <c r="BQ12" s="27" t="n"/>
+      <c r="BR12" s="28" t="n"/>
+      <c r="BS12" s="28" t="n"/>
+      <c r="BT12" s="28" t="n"/>
+      <c r="BU12" s="25" t="n"/>
+      <c r="BV12" s="29" t="n"/>
+      <c r="BW12" s="24" t="n"/>
+      <c r="BX12" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY12" s="27" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BZ12" s="24" t="n"/>
+      <c r="CA12" s="31" t="n"/>
+      <c r="CB12" s="24" t="n"/>
+      <c r="CC12" s="24" t="n"/>
+      <c r="CD12" s="24" t="n"/>
+      <c r="CE12" s="24" t="n"/>
+      <c r="CF12" s="24" t="n"/>
+      <c r="CG12" s="24" t="n"/>
+      <c r="CH12" s="24" t="n"/>
+      <c r="CI12" s="24" t="n"/>
+      <c r="CJ12" s="24" t="n"/>
+      <c r="CK12" s="24" t="n"/>
+      <c r="CL12" s="24" t="n"/>
+      <c r="CM12" s="24" t="n"/>
+      <c r="CN12" s="24" t="n"/>
+      <c r="CO12" s="24" t="n"/>
+      <c r="CP12" s="24" t="n"/>
+      <c r="CQ12" s="24" t="n"/>
+      <c r="CR12" s="24" t="n"/>
+      <c r="CS12" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="36" customHeight="1">
+      <c r="A13" s="24" t="inlineStr">
+        <is>
+          <t>6e9d79eeb8954b77</t>
+        </is>
+      </c>
+      <c r="B13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:53.416116Z</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>69526</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F13" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="G13" s="24" t="inlineStr">
+        <is>
+          <t>Chiba Lotte Marines</t>
+        </is>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I13" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J13" s="25" t="n"/>
+      <c r="K13" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L13" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="M13" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="N13" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="O13" s="28" t="n">
+        <v>0.511776</v>
+      </c>
+      <c r="P13" s="28" t="n"/>
+      <c r="Q13" s="28" t="n">
+        <v>-0.01874</v>
+      </c>
+      <c r="R13" s="26" t="n">
+        <v>11</v>
+      </c>
+      <c r="S13" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U13" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V13" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W13" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y13" s="25" t="n"/>
+      <c r="Z13" s="26" t="n"/>
+      <c r="AA13" s="28" t="n"/>
+      <c r="AB13" s="28" t="n"/>
+      <c r="AC13" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:18.770156Z</t>
+        </is>
+      </c>
+      <c r="AE13" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5300 (market_slug=aec-npb-clm-ssl-2026-08-05). Tie probability=0.0354.</t>
+        </is>
+      </c>
+      <c r="AF13" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG13" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH13" s="24" t="n"/>
+      <c r="AI13" s="31" t="n"/>
+      <c r="AJ13" s="31" t="n"/>
+      <c r="AK13" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL13" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM13" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN13" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO13" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP13" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AQ13" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AR13" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AS13" s="24" t="inlineStr">
+        <is>
+          <t>Chiba Lotte Marines</t>
+        </is>
+      </c>
+      <c r="AT13" s="24" t="inlineStr">
+        <is>
+          <t>Chiba Lotte Marines</t>
+        </is>
+      </c>
+      <c r="AU13" s="24" t="inlineStr">
+        <is>
+          <t>Chiba Lotte Marines</t>
+        </is>
+      </c>
+      <c r="AV13" s="24" t="n"/>
+      <c r="AW13" s="24" t="n"/>
+      <c r="AX13" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY13" s="24" t="n"/>
+      <c r="AZ13" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA13" s="24" t="inlineStr">
+        <is>
+          <t>587c95488a5eab49a474c082a9d83bc1218cd1ce498682f7305ccc207cdae6d9</t>
+        </is>
+      </c>
+      <c r="BB13" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC13" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD13" s="24" t="inlineStr">
+        <is>
+          <t>587c95488a5eab49a474c082a9d83bc1218cd1ce498682f7305ccc207cdae6d9</t>
+        </is>
+      </c>
+      <c r="BE13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF13" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG13" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH13" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:50.743012Z</t>
+        </is>
+      </c>
+      <c r="BI13" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ13" s="25" t="n"/>
+      <c r="BK13" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="BL13" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BM13" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="BN13" s="28" t="n"/>
+      <c r="BO13" s="28" t="n"/>
+      <c r="BP13" s="25" t="n"/>
+      <c r="BQ13" s="27" t="n"/>
+      <c r="BR13" s="28" t="n"/>
+      <c r="BS13" s="28" t="n"/>
+      <c r="BT13" s="28" t="n"/>
+      <c r="BU13" s="25" t="n"/>
+      <c r="BV13" s="29" t="n"/>
+      <c r="BW13" s="24" t="n"/>
+      <c r="BX13" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY13" s="27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BZ13" s="24" t="n"/>
+      <c r="CA13" s="31" t="n"/>
+      <c r="CB13" s="24" t="n"/>
+      <c r="CC13" s="24" t="n"/>
+      <c r="CD13" s="24" t="n"/>
+      <c r="CE13" s="24" t="n"/>
+      <c r="CF13" s="24" t="n"/>
+      <c r="CG13" s="24" t="n"/>
+      <c r="CH13" s="24" t="n"/>
+      <c r="CI13" s="24" t="n"/>
+      <c r="CJ13" s="24" t="n"/>
+      <c r="CK13" s="24" t="n"/>
+      <c r="CL13" s="24" t="n"/>
+      <c r="CM13" s="24" t="n"/>
+      <c r="CN13" s="24" t="n"/>
+      <c r="CO13" s="24" t="n"/>
+      <c r="CP13" s="24" t="n"/>
+      <c r="CQ13" s="24" t="n"/>
+      <c r="CR13" s="24" t="n"/>
+      <c r="CS13" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="36" customHeight="1">
+      <c r="A14" s="24" t="inlineStr">
+        <is>
+          <t>e390daaf0112448a</t>
+        </is>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:53.416116Z</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>69527</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F14" s="24" t="inlineStr">
+        <is>
+          <t>Tohoku Rakuten Golden Eagles</t>
+        </is>
+      </c>
+      <c r="G14" s="24" t="inlineStr">
+        <is>
+          <t>Orix Buffaloes</t>
+        </is>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J14" s="25" t="n"/>
+      <c r="K14" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L14" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="M14" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="N14" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="O14" s="28" t="n">
+        <v>0.565314</v>
+      </c>
+      <c r="P14" s="28" t="n"/>
+      <c r="Q14" s="28" t="n">
+        <v>-0.064316</v>
+      </c>
+      <c r="R14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U14" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V14" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W14" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y14" s="25" t="n"/>
+      <c r="Z14" s="26" t="n"/>
+      <c r="AA14" s="28" t="n"/>
+      <c r="AB14" s="28" t="n"/>
+      <c r="AC14" s="30" t="n">
+        <v>0.5881999999999999</v>
+      </c>
+      <c r="AD14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:18.860547Z</t>
+        </is>
+      </c>
+      <c r="AE14" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6300 (market_slug=aec-npb-obr-trge-2026-08-05). Tie probability=0.0307.</t>
+        </is>
+      </c>
+      <c r="AF14" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG14" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH14" s="24" t="n"/>
+      <c r="AI14" s="31" t="n"/>
+      <c r="AJ14" s="31" t="n"/>
+      <c r="AK14" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL14" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM14" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN14" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO14" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP14" s="24" t="inlineStr">
+        <is>
+          <t>Tohoku Rakuten Golden Eagles</t>
+        </is>
+      </c>
+      <c r="AQ14" s="24" t="inlineStr">
+        <is>
+          <t>Tohoku Rakuten Golden Eagles</t>
+        </is>
+      </c>
+      <c r="AR14" s="24" t="inlineStr">
+        <is>
+          <t>Tohoku Rakuten Golden Eagles</t>
+        </is>
+      </c>
+      <c r="AS14" s="24" t="inlineStr">
+        <is>
+          <t>Orix Buffaloes</t>
+        </is>
+      </c>
+      <c r="AT14" s="24" t="inlineStr">
+        <is>
+          <t>Orix Buffaloes</t>
+        </is>
+      </c>
+      <c r="AU14" s="24" t="inlineStr">
+        <is>
+          <t>Orix Buffaloes</t>
+        </is>
+      </c>
+      <c r="AV14" s="24" t="n"/>
+      <c r="AW14" s="24" t="n"/>
+      <c r="AX14" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY14" s="24" t="n"/>
+      <c r="AZ14" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA14" s="24" t="inlineStr">
+        <is>
+          <t>587c95488a5eab49a474c082a9d83bc1218cd1ce498682f7305ccc207cdae6d9</t>
+        </is>
+      </c>
+      <c r="BB14" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC14" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD14" s="24" t="inlineStr">
+        <is>
+          <t>587c95488a5eab49a474c082a9d83bc1218cd1ce498682f7305ccc207cdae6d9</t>
+        </is>
+      </c>
+      <c r="BE14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF14" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG14" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH14" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:51.558960Z</t>
+        </is>
+      </c>
+      <c r="BI14" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ14" s="25" t="n"/>
+      <c r="BK14" s="26" t="n">
+        <v>-170</v>
+      </c>
+      <c r="BL14" s="27" t="n">
+        <v>1.588235</v>
+      </c>
+      <c r="BM14" s="28" t="n">
+        <v>0.62963</v>
+      </c>
+      <c r="BN14" s="28" t="n"/>
+      <c r="BO14" s="28" t="n"/>
+      <c r="BP14" s="25" t="n"/>
+      <c r="BQ14" s="27" t="n"/>
+      <c r="BR14" s="28" t="n"/>
+      <c r="BS14" s="28" t="n"/>
+      <c r="BT14" s="28" t="n"/>
+      <c r="BU14" s="25" t="n"/>
+      <c r="BV14" s="29" t="n"/>
+      <c r="BW14" s="24" t="n"/>
+      <c r="BX14" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY14" s="27" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BZ14" s="24" t="n"/>
+      <c r="CA14" s="31" t="n"/>
+      <c r="CB14" s="24" t="n"/>
+      <c r="CC14" s="24" t="n"/>
+      <c r="CD14" s="24" t="n"/>
+      <c r="CE14" s="24" t="n"/>
+      <c r="CF14" s="24" t="n"/>
+      <c r="CG14" s="24" t="n"/>
+      <c r="CH14" s="24" t="n"/>
+      <c r="CI14" s="24" t="n"/>
+      <c r="CJ14" s="24" t="n"/>
+      <c r="CK14" s="24" t="n"/>
+      <c r="CL14" s="24" t="n"/>
+      <c r="CM14" s="24" t="n"/>
+      <c r="CN14" s="24" t="n"/>
+      <c r="CO14" s="24" t="n"/>
+      <c r="CP14" s="24" t="n"/>
+      <c r="CQ14" s="24" t="n"/>
+      <c r="CR14" s="24" t="n"/>
+      <c r="CS14" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="36" customHeight="1">
+      <c r="A15" s="24" t="inlineStr">
+        <is>
+          <t>7824cc7441d94f63</t>
+        </is>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:53.416116Z</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>69528</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F15" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="G15" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J15" s="25" t="n"/>
+      <c r="K15" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L15" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M15" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N15" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O15" s="28" t="n">
+        <v>0.587499</v>
+      </c>
+      <c r="P15" s="28" t="n"/>
+      <c r="Q15" s="28" t="n">
+        <v>-0.002665</v>
+      </c>
+      <c r="R15" s="26" t="n">
+        <v>19</v>
+      </c>
+      <c r="S15" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T15" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U15" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V15" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W15" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="X15" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y15" s="25" t="n"/>
+      <c r="Z15" s="26" t="n"/>
+      <c r="AA15" s="28" t="n"/>
+      <c r="AB15" s="28" t="n"/>
+      <c r="AC15" s="30" t="n">
+        <v>0.8681</v>
+      </c>
+      <c r="AD15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:18.959265Z</t>
+        </is>
+      </c>
+      <c r="AE15" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5900 (market_slug=aec-npb-fsh-nhf-2026-08-05). Tie probability=0.0288.</t>
+        </is>
+      </c>
+      <c r="AF15" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG15" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH15" s="24" t="n"/>
+      <c r="AI15" s="31" t="n"/>
+      <c r="AJ15" s="31" t="n"/>
+      <c r="AK15" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL15" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM15" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN15" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO15" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP15" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AQ15" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AR15" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AS15" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="AT15" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="AU15" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="AV15" s="24" t="n"/>
+      <c r="AW15" s="24" t="n"/>
+      <c r="AX15" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY15" s="24" t="n"/>
+      <c r="AZ15" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA15" s="24" t="inlineStr">
+        <is>
+          <t>587c95488a5eab49a474c082a9d83bc1218cd1ce498682f7305ccc207cdae6d9</t>
+        </is>
+      </c>
+      <c r="BB15" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC15" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD15" s="24" t="inlineStr">
+        <is>
+          <t>587c95488a5eab49a474c082a9d83bc1218cd1ce498682f7305ccc207cdae6d9</t>
+        </is>
+      </c>
+      <c r="BE15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF15" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG15" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH15" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:52.448253Z</t>
+        </is>
+      </c>
+      <c r="BI15" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ15" s="25" t="n"/>
+      <c r="BK15" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL15" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM15" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN15" s="28" t="n"/>
+      <c r="BO15" s="28" t="n"/>
+      <c r="BP15" s="25" t="n"/>
+      <c r="BQ15" s="27" t="n"/>
+      <c r="BR15" s="28" t="n"/>
+      <c r="BS15" s="28" t="n"/>
+      <c r="BT15" s="28" t="n"/>
+      <c r="BU15" s="25" t="n"/>
+      <c r="BV15" s="29" t="n"/>
+      <c r="BW15" s="24" t="n"/>
+      <c r="BX15" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY15" s="27" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BZ15" s="24" t="n"/>
+      <c r="CA15" s="31" t="n"/>
+      <c r="CB15" s="24" t="n"/>
+      <c r="CC15" s="24" t="n"/>
+      <c r="CD15" s="24" t="n"/>
+      <c r="CE15" s="24" t="n"/>
+      <c r="CF15" s="24" t="n"/>
+      <c r="CG15" s="24" t="n"/>
+      <c r="CH15" s="24" t="n"/>
+      <c r="CI15" s="24" t="n"/>
+      <c r="CJ15" s="24" t="n"/>
+      <c r="CK15" s="24" t="n"/>
+      <c r="CL15" s="24" t="n"/>
+      <c r="CM15" s="24" t="n"/>
+      <c r="CN15" s="24" t="n"/>
+      <c r="CO15" s="24" t="n"/>
+      <c r="CP15" s="24" t="n"/>
+      <c r="CQ15" s="24" t="n"/>
+      <c r="CR15" s="24" t="n"/>
+      <c r="CS15" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="24" t="inlineStr">
+        <is>
+          <t>63e486e3516242c8</t>
+        </is>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:53.416116Z</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>69529</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="G16" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J16" s="25" t="n"/>
+      <c r="K16" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L16" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M16" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N16" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O16" s="28" t="n">
+        <v>0.532673</v>
+      </c>
+      <c r="P16" s="28" t="n"/>
+      <c r="Q16" s="28" t="n">
+        <v>-0.026798</v>
+      </c>
+      <c r="R16" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="S16" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U16" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V16" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W16" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="X16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="25" t="n"/>
+      <c r="Z16" s="26" t="n"/>
+      <c r="AA16" s="28" t="n"/>
+      <c r="AB16" s="28" t="n"/>
+      <c r="AC16" s="30" t="n">
+        <v>0.7874</v>
+      </c>
+      <c r="AD16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T21:00:19.078808Z</t>
+        </is>
+      </c>
+      <c r="AE16" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5600 (market_slug=aec-npb-hci-ygo-2026-08-05). Tie probability=0.0336.</t>
+        </is>
+      </c>
+      <c r="AF16" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG16" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH16" s="24" t="n"/>
+      <c r="AI16" s="31" t="n"/>
+      <c r="AJ16" s="31" t="n"/>
+      <c r="AK16" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL16" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM16" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN16" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO16" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP16" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="AQ16" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="AR16" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="AS16" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="AT16" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="AU16" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="AV16" s="24" t="n"/>
+      <c r="AW16" s="24" t="n"/>
+      <c r="AX16" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY16" s="24" t="n"/>
+      <c r="AZ16" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA16" s="24" t="inlineStr">
+        <is>
+          <t>587c95488a5eab49a474c082a9d83bc1218cd1ce498682f7305ccc207cdae6d9</t>
+        </is>
+      </c>
+      <c r="BB16" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC16" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD16" s="24" t="inlineStr">
+        <is>
+          <t>587c95488a5eab49a474c082a9d83bc1218cd1ce498682f7305ccc207cdae6d9</t>
+        </is>
+      </c>
+      <c r="BE16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF16" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG16" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH16" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-05T04:36:53.416071Z</t>
+        </is>
+      </c>
+      <c r="BI16" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ16" s="25" t="n"/>
+      <c r="BK16" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL16" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM16" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN16" s="28" t="n"/>
+      <c r="BO16" s="28" t="n"/>
+      <c r="BP16" s="25" t="n"/>
+      <c r="BQ16" s="27" t="n"/>
+      <c r="BR16" s="28" t="n"/>
+      <c r="BS16" s="28" t="n"/>
+      <c r="BT16" s="28" t="n"/>
+      <c r="BU16" s="25" t="n"/>
+      <c r="BV16" s="29" t="n"/>
+      <c r="BW16" s="24" t="n"/>
+      <c r="BX16" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY16" s="27" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BZ16" s="24" t="n"/>
+      <c r="CA16" s="31" t="n"/>
+      <c r="CB16" s="24" t="n"/>
+      <c r="CC16" s="24" t="n"/>
+      <c r="CD16" s="24" t="n"/>
+      <c r="CE16" s="24" t="n"/>
+      <c r="CF16" s="24" t="n"/>
+      <c r="CG16" s="24" t="n"/>
+      <c r="CH16" s="24" t="n"/>
+      <c r="CI16" s="24" t="n"/>
+      <c r="CJ16" s="24" t="n"/>
+      <c r="CK16" s="24" t="n"/>
+      <c r="CL16" s="24" t="n"/>
+      <c r="CM16" s="24" t="n"/>
+      <c r="CN16" s="24" t="n"/>
+      <c r="CO16" s="24" t="n"/>
+      <c r="CP16" s="24" t="n"/>
+      <c r="CQ16" s="24" t="n"/>
+      <c r="CR16" s="24" t="n"/>
+      <c r="CS16" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="36" customHeight="1">
+      <c r="A17" s="24" t="inlineStr">
+        <is>
+          <t>b6208e6608f643b2</t>
+        </is>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:04:08.876576Z</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>71688</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F17" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="G17" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="H17" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J17" s="25" t="n"/>
+      <c r="K17" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L17" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="M17" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="N17" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="O17" s="28" t="n">
+        <v>0.671883</v>
+      </c>
+      <c r="P17" s="28" t="n"/>
+      <c r="Q17" s="28" t="n">
+        <v>0.06250799999999999</v>
+      </c>
+      <c r="R17" s="26" t="n">
+        <v>51</v>
+      </c>
+      <c r="S17" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U17" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V17" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W17" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="25" t="n"/>
+      <c r="Z17" s="26" t="n"/>
+      <c r="AA17" s="28" t="n"/>
+      <c r="AB17" s="28" t="n"/>
+      <c r="AC17" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:21.798527Z</t>
+        </is>
+      </c>
+      <c r="AE17" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6100 (market_slug=aec-npb-ygo-tys-2026-08-07). Tie probability=0.0209.</t>
+        </is>
+      </c>
+      <c r="AF17" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG17" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH17" s="24" t="n"/>
+      <c r="AI17" s="31" t="n"/>
+      <c r="AJ17" s="31" t="n"/>
+      <c r="AK17" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL17" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM17" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN17" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO17" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP17" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AQ17" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AR17" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AS17" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="AT17" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="AU17" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="AV17" s="24" t="n"/>
+      <c r="AW17" s="24" t="n"/>
+      <c r="AX17" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY17" s="24" t="n"/>
+      <c r="AZ17" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA17" s="24" t="inlineStr">
+        <is>
+          <t>1397f2a2e62220577ae4a4ae8de10b8369816a7b15d915f063053eb9c759a04a</t>
+        </is>
+      </c>
+      <c r="BB17" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC17" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD17" s="24" t="inlineStr">
+        <is>
+          <t>1397f2a2e62220577ae4a4ae8de10b8369816a7b15d915f063053eb9c759a04a</t>
+        </is>
+      </c>
+      <c r="BE17" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF17" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG17" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH17" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:04:05.382616Z</t>
+        </is>
+      </c>
+      <c r="BI17" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ17" s="25" t="n"/>
+      <c r="BK17" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="BL17" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BM17" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="BN17" s="28" t="n"/>
+      <c r="BO17" s="28" t="n"/>
+      <c r="BP17" s="25" t="n"/>
+      <c r="BQ17" s="27" t="n"/>
+      <c r="BR17" s="28" t="n"/>
+      <c r="BS17" s="28" t="n"/>
+      <c r="BT17" s="28" t="n"/>
+      <c r="BU17" s="25" t="n"/>
+      <c r="BV17" s="29" t="n"/>
+      <c r="BW17" s="24" t="n"/>
+      <c r="BX17" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY17" s="27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BZ17" s="24" t="n"/>
+      <c r="CA17" s="31" t="n"/>
+      <c r="CB17" s="24" t="n"/>
+      <c r="CC17" s="24" t="n"/>
+      <c r="CD17" s="24" t="n"/>
+      <c r="CE17" s="24" t="n"/>
+      <c r="CF17" s="24" t="n"/>
+      <c r="CG17" s="24" t="n"/>
+      <c r="CH17" s="24" t="n"/>
+      <c r="CI17" s="24" t="n"/>
+      <c r="CJ17" s="24" t="n"/>
+      <c r="CK17" s="24" t="n"/>
+      <c r="CL17" s="24" t="n"/>
+      <c r="CM17" s="24" t="n"/>
+      <c r="CN17" s="24" t="n"/>
+      <c r="CO17" s="24" t="n"/>
+      <c r="CP17" s="24" t="n"/>
+      <c r="CQ17" s="24" t="n"/>
+      <c r="CR17" s="24" t="n"/>
+      <c r="CS17" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1">
+      <c r="A18" s="24" t="inlineStr">
+        <is>
+          <t>a713a94747574b49</t>
+        </is>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:04:08.876576Z</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>71689</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F18" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="G18" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="H18" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J18" s="25" t="n"/>
+      <c r="K18" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L18" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="M18" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="N18" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="O18" s="28" t="n">
+        <v>0.587646</v>
+      </c>
+      <c r="P18" s="28" t="n"/>
+      <c r="Q18" s="28" t="n">
+        <v>-0.08232100000000001</v>
+      </c>
+      <c r="R18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U18" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V18" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W18" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y18" s="25" t="n"/>
+      <c r="Z18" s="26" t="n"/>
+      <c r="AA18" s="28" t="n"/>
+      <c r="AB18" s="28" t="n"/>
+      <c r="AC18" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:22.019890Z</t>
+        </is>
+      </c>
+      <c r="AE18" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6700 (market_slug=aec-npb-ybo-hci-2026-08-07). Tie probability=0.0287.</t>
+        </is>
+      </c>
+      <c r="AF18" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG18" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH18" s="24" t="n"/>
+      <c r="AI18" s="31" t="n"/>
+      <c r="AJ18" s="31" t="n"/>
+      <c r="AK18" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL18" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM18" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN18" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO18" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP18" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="AQ18" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="AR18" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="AS18" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AT18" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AU18" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AV18" s="24" t="n"/>
+      <c r="AW18" s="24" t="n"/>
+      <c r="AX18" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY18" s="24" t="n"/>
+      <c r="AZ18" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA18" s="24" t="inlineStr">
+        <is>
+          <t>1397f2a2e62220577ae4a4ae8de10b8369816a7b15d915f063053eb9c759a04a</t>
+        </is>
+      </c>
+      <c r="BB18" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC18" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD18" s="24" t="inlineStr">
+        <is>
+          <t>1397f2a2e62220577ae4a4ae8de10b8369816a7b15d915f063053eb9c759a04a</t>
+        </is>
+      </c>
+      <c r="BE18" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF18" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG18" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH18" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:04:06.385882Z</t>
+        </is>
+      </c>
+      <c r="BI18" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ18" s="25" t="n"/>
+      <c r="BK18" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="BL18" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="BM18" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="BN18" s="28" t="n"/>
+      <c r="BO18" s="28" t="n"/>
+      <c r="BP18" s="25" t="n"/>
+      <c r="BQ18" s="27" t="n"/>
+      <c r="BR18" s="28" t="n"/>
+      <c r="BS18" s="28" t="n"/>
+      <c r="BT18" s="28" t="n"/>
+      <c r="BU18" s="25" t="n"/>
+      <c r="BV18" s="29" t="n"/>
+      <c r="BW18" s="24" t="n"/>
+      <c r="BX18" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY18" s="27" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BZ18" s="24" t="n"/>
+      <c r="CA18" s="31" t="n"/>
+      <c r="CB18" s="24" t="n"/>
+      <c r="CC18" s="24" t="n"/>
+      <c r="CD18" s="24" t="n"/>
+      <c r="CE18" s="24" t="n"/>
+      <c r="CF18" s="24" t="n"/>
+      <c r="CG18" s="24" t="n"/>
+      <c r="CH18" s="24" t="n"/>
+      <c r="CI18" s="24" t="n"/>
+      <c r="CJ18" s="24" t="n"/>
+      <c r="CK18" s="24" t="n"/>
+      <c r="CL18" s="24" t="n"/>
+      <c r="CM18" s="24" t="n"/>
+      <c r="CN18" s="24" t="n"/>
+      <c r="CO18" s="24" t="n"/>
+      <c r="CP18" s="24" t="n"/>
+      <c r="CQ18" s="24" t="n"/>
+      <c r="CR18" s="24" t="n"/>
+      <c r="CS18" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1">
+      <c r="A19" s="24" t="inlineStr">
+        <is>
+          <t>80c41bce75c94f02</t>
+        </is>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:04:08.876576Z</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>71690</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F19" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="G19" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J19" s="25" t="n"/>
+      <c r="K19" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L19" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="M19" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="N19" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="O19" s="28" t="n">
+        <v>0.577661</v>
+      </c>
+      <c r="P19" s="28" t="n"/>
+      <c r="Q19" s="28" t="n">
+        <v>-0.072689</v>
+      </c>
+      <c r="R19" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U19" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V19" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W19" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X19" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y19" s="25" t="n"/>
+      <c r="Z19" s="26" t="n"/>
+      <c r="AA19" s="28" t="n"/>
+      <c r="AB19" s="28" t="n"/>
+      <c r="AC19" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:22.321727Z</t>
+        </is>
+      </c>
+      <c r="AE19" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6500 (market_slug=aec-npb-hta-cdh-2026-08-07). Tie probability=0.0296.</t>
+        </is>
+      </c>
+      <c r="AF19" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG19" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH19" s="24" t="n"/>
+      <c r="AI19" s="31" t="n"/>
+      <c r="AJ19" s="31" t="n"/>
+      <c r="AK19" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL19" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM19" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN19" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO19" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP19" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="AQ19" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="AR19" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="AS19" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AT19" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AU19" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AV19" s="24" t="n"/>
+      <c r="AW19" s="24" t="n"/>
+      <c r="AX19" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY19" s="24" t="n"/>
+      <c r="AZ19" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA19" s="24" t="inlineStr">
+        <is>
+          <t>1397f2a2e62220577ae4a4ae8de10b8369816a7b15d915f063053eb9c759a04a</t>
+        </is>
+      </c>
+      <c r="BB19" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC19" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD19" s="24" t="inlineStr">
+        <is>
+          <t>1397f2a2e62220577ae4a4ae8de10b8369816a7b15d915f063053eb9c759a04a</t>
+        </is>
+      </c>
+      <c r="BE19" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF19" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG19" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH19" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:04:06.951384Z</t>
+        </is>
+      </c>
+      <c r="BI19" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ19" s="25" t="n"/>
+      <c r="BK19" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="BL19" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="BM19" s="28" t="n">
+        <v>0.65035</v>
+      </c>
+      <c r="BN19" s="28" t="n"/>
+      <c r="BO19" s="28" t="n"/>
+      <c r="BP19" s="25" t="n"/>
+      <c r="BQ19" s="27" t="n"/>
+      <c r="BR19" s="28" t="n"/>
+      <c r="BS19" s="28" t="n"/>
+      <c r="BT19" s="28" t="n"/>
+      <c r="BU19" s="25" t="n"/>
+      <c r="BV19" s="29" t="n"/>
+      <c r="BW19" s="24" t="n"/>
+      <c r="BX19" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY19" s="27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BZ19" s="24" t="n"/>
+      <c r="CA19" s="31" t="n"/>
+      <c r="CB19" s="24" t="n"/>
+      <c r="CC19" s="24" t="n"/>
+      <c r="CD19" s="24" t="n"/>
+      <c r="CE19" s="24" t="n"/>
+      <c r="CF19" s="24" t="n"/>
+      <c r="CG19" s="24" t="n"/>
+      <c r="CH19" s="24" t="n"/>
+      <c r="CI19" s="24" t="n"/>
+      <c r="CJ19" s="24" t="n"/>
+      <c r="CK19" s="24" t="n"/>
+      <c r="CL19" s="24" t="n"/>
+      <c r="CM19" s="24" t="n"/>
+      <c r="CN19" s="24" t="n"/>
+      <c r="CO19" s="24" t="n"/>
+      <c r="CP19" s="24" t="n"/>
+      <c r="CQ19" s="24" t="n"/>
+      <c r="CR19" s="24" t="n"/>
+      <c r="CS19" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="24" t="inlineStr">
+        <is>
+          <t>8af9beec062f4eb8</t>
+        </is>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:04:08.876576Z</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>71691</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F20" s="24" t="inlineStr">
+        <is>
+          <t>Tohoku Rakuten Golden Eagles</t>
+        </is>
+      </c>
+      <c r="G20" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="H20" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J20" s="25" t="n"/>
+      <c r="K20" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L20" s="26" t="n">
+        <v>-257</v>
+      </c>
+      <c r="M20" s="27" t="n">
+        <v>1.389105</v>
+      </c>
+      <c r="N20" s="28" t="n">
+        <v>0.719888</v>
+      </c>
+      <c r="O20" s="28" t="n">
+        <v>0.648431</v>
+      </c>
+      <c r="P20" s="28" t="n"/>
+      <c r="Q20" s="28" t="n">
+        <v>-0.07145700000000001</v>
+      </c>
+      <c r="R20" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U20" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V20" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W20" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="X20" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y20" s="25" t="n"/>
+      <c r="Z20" s="26" t="n"/>
+      <c r="AA20" s="28" t="n"/>
+      <c r="AB20" s="28" t="n"/>
+      <c r="AC20" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:22.543840Z</t>
+        </is>
+      </c>
+      <c r="AE20" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.7200 (market_slug=aec-npb-nhf-trge-2026-08-07). Tie probability=0.0232.</t>
+        </is>
+      </c>
+      <c r="AF20" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG20" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH20" s="24" t="n"/>
+      <c r="AI20" s="31" t="n"/>
+      <c r="AJ20" s="31" t="n"/>
+      <c r="AK20" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL20" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM20" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN20" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO20" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP20" s="24" t="inlineStr">
+        <is>
+          <t>Tohoku Rakuten Golden Eagles</t>
+        </is>
+      </c>
+      <c r="AQ20" s="24" t="inlineStr">
+        <is>
+          <t>Tohoku Rakuten Golden Eagles</t>
+        </is>
+      </c>
+      <c r="AR20" s="24" t="inlineStr">
+        <is>
+          <t>Tohoku Rakuten Golden Eagles</t>
+        </is>
+      </c>
+      <c r="AS20" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AT20" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AU20" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AV20" s="24" t="n"/>
+      <c r="AW20" s="24" t="n"/>
+      <c r="AX20" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY20" s="24" t="n"/>
+      <c r="AZ20" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA20" s="24" t="inlineStr">
+        <is>
+          <t>1397f2a2e62220577ae4a4ae8de10b8369816a7b15d915f063053eb9c759a04a</t>
+        </is>
+      </c>
+      <c r="BB20" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC20" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD20" s="24" t="inlineStr">
+        <is>
+          <t>1397f2a2e62220577ae4a4ae8de10b8369816a7b15d915f063053eb9c759a04a</t>
+        </is>
+      </c>
+      <c r="BE20" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF20" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG20" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH20" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:04:07.658626Z</t>
+        </is>
+      </c>
+      <c r="BI20" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ20" s="25" t="n"/>
+      <c r="BK20" s="26" t="n">
+        <v>-257</v>
+      </c>
+      <c r="BL20" s="27" t="n">
+        <v>1.389105</v>
+      </c>
+      <c r="BM20" s="28" t="n">
+        <v>0.719888</v>
+      </c>
+      <c r="BN20" s="28" t="n"/>
+      <c r="BO20" s="28" t="n"/>
+      <c r="BP20" s="25" t="n"/>
+      <c r="BQ20" s="27" t="n"/>
+      <c r="BR20" s="28" t="n"/>
+      <c r="BS20" s="28" t="n"/>
+      <c r="BT20" s="28" t="n"/>
+      <c r="BU20" s="25" t="n"/>
+      <c r="BV20" s="29" t="n"/>
+      <c r="BW20" s="24" t="n"/>
+      <c r="BX20" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY20" s="27" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BZ20" s="24" t="n"/>
+      <c r="CA20" s="31" t="n"/>
+      <c r="CB20" s="24" t="n"/>
+      <c r="CC20" s="24" t="n"/>
+      <c r="CD20" s="24" t="n"/>
+      <c r="CE20" s="24" t="n"/>
+      <c r="CF20" s="24" t="n"/>
+      <c r="CG20" s="24" t="n"/>
+      <c r="CH20" s="24" t="n"/>
+      <c r="CI20" s="24" t="n"/>
+      <c r="CJ20" s="24" t="n"/>
+      <c r="CK20" s="24" t="n"/>
+      <c r="CL20" s="24" t="n"/>
+      <c r="CM20" s="24" t="n"/>
+      <c r="CN20" s="24" t="n"/>
+      <c r="CO20" s="24" t="n"/>
+      <c r="CP20" s="24" t="n"/>
+      <c r="CQ20" s="24" t="n"/>
+      <c r="CR20" s="24" t="n"/>
+      <c r="CS20" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="24" t="inlineStr">
+        <is>
+          <t>53df51dcf4ef4440</t>
+        </is>
+      </c>
+      <c r="B21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:04:08.876576Z</t>
+        </is>
+      </c>
+      <c r="C21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D21" s="24" t="inlineStr">
+        <is>
+          <t>71692</t>
+        </is>
+      </c>
+      <c r="E21" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F21" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="G21" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="H21" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I21" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J21" s="25" t="n"/>
+      <c r="K21" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L21" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M21" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N21" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O21" s="28" t="n">
+        <v>0.57184</v>
+      </c>
+      <c r="P21" s="28" t="n"/>
+      <c r="Q21" s="28" t="n">
+        <v>-0.02816</v>
+      </c>
+      <c r="R21" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="S21" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U21" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V21" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W21" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="X21" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y21" s="25" t="n"/>
+      <c r="Z21" s="26" t="n"/>
+      <c r="AA21" s="28" t="n"/>
+      <c r="AB21" s="28" t="n"/>
+      <c r="AC21" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:22.762636Z</t>
+        </is>
+      </c>
+      <c r="AE21" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6000 (market_slug=aec-npb-ssl-fsh-2026-08-07). Tie probability=0.0301.</t>
+        </is>
+      </c>
+      <c r="AF21" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG21" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH21" s="24" t="n"/>
+      <c r="AI21" s="31" t="n"/>
+      <c r="AJ21" s="31" t="n"/>
+      <c r="AK21" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL21" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM21" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN21" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO21" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP21" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="AQ21" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="AR21" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="AS21" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AT21" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AU21" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AV21" s="24" t="n"/>
+      <c r="AW21" s="24" t="n"/>
+      <c r="AX21" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY21" s="24" t="n"/>
+      <c r="AZ21" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA21" s="24" t="inlineStr">
+        <is>
+          <t>1397f2a2e62220577ae4a4ae8de10b8369816a7b15d915f063053eb9c759a04a</t>
+        </is>
+      </c>
+      <c r="BB21" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC21" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD21" s="24" t="inlineStr">
+        <is>
+          <t>1397f2a2e62220577ae4a4ae8de10b8369816a7b15d915f063053eb9c759a04a</t>
+        </is>
+      </c>
+      <c r="BE21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF21" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG21" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH21" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:04:08.234637Z</t>
+        </is>
+      </c>
+      <c r="BI21" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ21" s="25" t="n"/>
+      <c r="BK21" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL21" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM21" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN21" s="28" t="n"/>
+      <c r="BO21" s="28" t="n"/>
+      <c r="BP21" s="25" t="n"/>
+      <c r="BQ21" s="27" t="n"/>
+      <c r="BR21" s="28" t="n"/>
+      <c r="BS21" s="28" t="n"/>
+      <c r="BT21" s="28" t="n"/>
+      <c r="BU21" s="25" t="n"/>
+      <c r="BV21" s="29" t="n"/>
+      <c r="BW21" s="24" t="n"/>
+      <c r="BX21" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY21" s="27" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BZ21" s="24" t="n"/>
+      <c r="CA21" s="31" t="n"/>
+      <c r="CB21" s="24" t="n"/>
+      <c r="CC21" s="24" t="n"/>
+      <c r="CD21" s="24" t="n"/>
+      <c r="CE21" s="24" t="n"/>
+      <c r="CF21" s="24" t="n"/>
+      <c r="CG21" s="24" t="n"/>
+      <c r="CH21" s="24" t="n"/>
+      <c r="CI21" s="24" t="n"/>
+      <c r="CJ21" s="24" t="n"/>
+      <c r="CK21" s="24" t="n"/>
+      <c r="CL21" s="24" t="n"/>
+      <c r="CM21" s="24" t="n"/>
+      <c r="CN21" s="24" t="n"/>
+      <c r="CO21" s="24" t="n"/>
+      <c r="CP21" s="24" t="n"/>
+      <c r="CQ21" s="24" t="n"/>
+      <c r="CR21" s="24" t="n"/>
+      <c r="CS21" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>09a39aaa7814454e</t>
+        </is>
+      </c>
+      <c r="B22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:04:08.876576Z</t>
+        </is>
+      </c>
+      <c r="C22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>71693</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F22" s="24" t="inlineStr">
+        <is>
+          <t>Orix Buffaloes</t>
+        </is>
+      </c>
+      <c r="G22" s="24" t="inlineStr">
+        <is>
+          <t>Chiba Lotte Marines</t>
+        </is>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I22" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J22" s="25" t="n"/>
+      <c r="K22" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L22" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="M22" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="N22" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="O22" s="28" t="n">
+        <v>0.5519500000000001</v>
+      </c>
+      <c r="P22" s="28" t="n"/>
+      <c r="Q22" s="28" t="n">
+        <v>0.021434</v>
+      </c>
+      <c r="R22" s="26" t="n">
+        <v>31</v>
+      </c>
+      <c r="S22" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U22" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V22" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W22" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="X22" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y22" s="25" t="n"/>
+      <c r="Z22" s="26" t="n"/>
+      <c r="AA22" s="28" t="n"/>
+      <c r="AB22" s="28" t="n"/>
+      <c r="AC22" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T18:27:22.989329Z</t>
+        </is>
+      </c>
+      <c r="AE22" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5300 (market_slug=aec-npb-clm-obr-2026-08-07). Tie probability=0.0318.</t>
+        </is>
+      </c>
+      <c r="AF22" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG22" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH22" s="24" t="n"/>
+      <c r="AI22" s="31" t="n"/>
+      <c r="AJ22" s="31" t="n"/>
+      <c r="AK22" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL22" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM22" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN22" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO22" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP22" s="24" t="inlineStr">
+        <is>
+          <t>Orix Buffaloes</t>
+        </is>
+      </c>
+      <c r="AQ22" s="24" t="inlineStr">
+        <is>
+          <t>Orix Buffaloes</t>
+        </is>
+      </c>
+      <c r="AR22" s="24" t="inlineStr">
+        <is>
+          <t>Orix Buffaloes</t>
+        </is>
+      </c>
+      <c r="AS22" s="24" t="inlineStr">
+        <is>
+          <t>Chiba Lotte Marines</t>
+        </is>
+      </c>
+      <c r="AT22" s="24" t="inlineStr">
+        <is>
+          <t>Chiba Lotte Marines</t>
+        </is>
+      </c>
+      <c r="AU22" s="24" t="inlineStr">
+        <is>
+          <t>Chiba Lotte Marines</t>
+        </is>
+      </c>
+      <c r="AV22" s="24" t="n"/>
+      <c r="AW22" s="24" t="n"/>
+      <c r="AX22" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY22" s="24" t="n"/>
+      <c r="AZ22" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA22" s="24" t="inlineStr">
+        <is>
+          <t>1397f2a2e62220577ae4a4ae8de10b8369816a7b15d915f063053eb9c759a04a</t>
+        </is>
+      </c>
+      <c r="BB22" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC22" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD22" s="24" t="inlineStr">
+        <is>
+          <t>1397f2a2e62220577ae4a4ae8de10b8369816a7b15d915f063053eb9c759a04a</t>
+        </is>
+      </c>
+      <c r="BE22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF22" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG22" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH22" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-07T06:04:08.876525Z</t>
+        </is>
+      </c>
+      <c r="BI22" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ22" s="25" t="n"/>
+      <c r="BK22" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="BL22" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BM22" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="BN22" s="28" t="n"/>
+      <c r="BO22" s="28" t="n"/>
+      <c r="BP22" s="25" t="n"/>
+      <c r="BQ22" s="27" t="n"/>
+      <c r="BR22" s="28" t="n"/>
+      <c r="BS22" s="28" t="n"/>
+      <c r="BT22" s="28" t="n"/>
+      <c r="BU22" s="25" t="n"/>
+      <c r="BV22" s="29" t="n"/>
+      <c r="BW22" s="24" t="n"/>
+      <c r="BX22" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY22" s="27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BZ22" s="24" t="n"/>
+      <c r="CA22" s="31" t="n"/>
+      <c r="CB22" s="24" t="n"/>
+      <c r="CC22" s="24" t="n"/>
+      <c r="CD22" s="24" t="n"/>
+      <c r="CE22" s="24" t="n"/>
+      <c r="CF22" s="24" t="n"/>
+      <c r="CG22" s="24" t="n"/>
+      <c r="CH22" s="24" t="n"/>
+      <c r="CI22" s="24" t="n"/>
+      <c r="CJ22" s="24" t="n"/>
+      <c r="CK22" s="24" t="n"/>
+      <c r="CL22" s="24" t="n"/>
+      <c r="CM22" s="24" t="n"/>
+      <c r="CN22" s="24" t="n"/>
+      <c r="CO22" s="24" t="n"/>
+      <c r="CP22" s="24" t="n"/>
+      <c r="CQ22" s="24" t="n"/>
+      <c r="CR22" s="24" t="n"/>
+      <c r="CS22" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="24" t="inlineStr">
+        <is>
+          <t>e35e916b42364169</t>
+        </is>
+      </c>
+      <c r="B23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:06:50.014675Z</t>
+        </is>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>72694</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>Tohoku Rakuten Golden Eagles</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I23" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J23" s="25" t="n"/>
+      <c r="K23" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L23" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="M23" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="N23" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="O23" s="28" t="n">
+        <v>0.654702</v>
+      </c>
+      <c r="P23" s="28" t="n"/>
+      <c r="Q23" s="28" t="n">
+        <v>0.014414</v>
+      </c>
+      <c r="R23" s="26" t="n">
+        <v>27</v>
+      </c>
+      <c r="S23" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U23" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V23" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W23" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="X23" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="25" t="n"/>
+      <c r="Z23" s="26" t="n"/>
+      <c r="AA23" s="28" t="n"/>
+      <c r="AB23" s="28" t="n"/>
+      <c r="AC23" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T18:35:03.473196Z</t>
+        </is>
+      </c>
+      <c r="AE23" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6400 (market_slug=aec-npb-nhf-trge-2026-08-08). Tie probability=0.0225.</t>
+        </is>
+      </c>
+      <c r="AF23" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG23" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH23" s="24" t="n"/>
+      <c r="AI23" s="31" t="n"/>
+      <c r="AJ23" s="31" t="n"/>
+      <c r="AK23" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL23" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM23" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN23" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO23" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP23" s="24" t="inlineStr">
+        <is>
+          <t>Tohoku Rakuten Golden Eagles</t>
+        </is>
+      </c>
+      <c r="AQ23" s="24" t="inlineStr">
+        <is>
+          <t>Tohoku Rakuten Golden Eagles</t>
+        </is>
+      </c>
+      <c r="AR23" s="24" t="inlineStr">
+        <is>
+          <t>Tohoku Rakuten Golden Eagles</t>
+        </is>
+      </c>
+      <c r="AS23" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AT23" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AU23" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AV23" s="24" t="n"/>
+      <c r="AW23" s="24" t="n"/>
+      <c r="AX23" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY23" s="24" t="n"/>
+      <c r="AZ23" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA23" s="24" t="inlineStr">
+        <is>
+          <t>e9ab59688d3b514e2e6e6a6178916377e656c91d0946e4a0432922d92c29eca9</t>
+        </is>
+      </c>
+      <c r="BB23" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC23" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD23" s="24" t="inlineStr">
+        <is>
+          <t>e9ab59688d3b514e2e6e6a6178916377e656c91d0946e4a0432922d92c29eca9</t>
+        </is>
+      </c>
+      <c r="BE23" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF23" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG23" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH23" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:06:46.964710Z</t>
+        </is>
+      </c>
+      <c r="BI23" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ23" s="25" t="n"/>
+      <c r="BK23" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="BL23" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="BM23" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="BN23" s="28" t="n"/>
+      <c r="BO23" s="28" t="n"/>
+      <c r="BP23" s="25" t="n"/>
+      <c r="BQ23" s="27" t="n"/>
+      <c r="BR23" s="28" t="n"/>
+      <c r="BS23" s="28" t="n"/>
+      <c r="BT23" s="28" t="n"/>
+      <c r="BU23" s="25" t="n"/>
+      <c r="BV23" s="29" t="n"/>
+      <c r="BW23" s="24" t="n"/>
+      <c r="BX23" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY23" s="27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BZ23" s="24" t="n"/>
+      <c r="CA23" s="31" t="n"/>
+      <c r="CB23" s="24" t="n"/>
+      <c r="CC23" s="24" t="n"/>
+      <c r="CD23" s="24" t="n"/>
+      <c r="CE23" s="24" t="n"/>
+      <c r="CF23" s="24" t="n"/>
+      <c r="CG23" s="24" t="n"/>
+      <c r="CH23" s="24" t="n"/>
+      <c r="CI23" s="24" t="n"/>
+      <c r="CJ23" s="24" t="n"/>
+      <c r="CK23" s="24" t="n"/>
+      <c r="CL23" s="24" t="n"/>
+      <c r="CM23" s="24" t="n"/>
+      <c r="CN23" s="24" t="n"/>
+      <c r="CO23" s="24" t="n"/>
+      <c r="CP23" s="24" t="n"/>
+      <c r="CQ23" s="24" t="n"/>
+      <c r="CR23" s="24" t="n"/>
+      <c r="CS23" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>04d8165228a34d10</t>
+        </is>
+      </c>
+      <c r="B24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:06:50.014675Z</t>
+        </is>
+      </c>
+      <c r="C24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>72695</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I24" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J24" s="25" t="n"/>
+      <c r="K24" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L24" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M24" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N24" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O24" s="28" t="n">
+        <v>0.657907</v>
+      </c>
+      <c r="P24" s="28" t="n"/>
+      <c r="Q24" s="28" t="n">
+        <v>0.098436</v>
+      </c>
+      <c r="R24" s="26" t="n">
+        <v>69</v>
+      </c>
+      <c r="S24" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T24" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U24" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V24" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W24" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="X24" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y24" s="25" t="n"/>
+      <c r="Z24" s="26" t="n"/>
+      <c r="AA24" s="28" t="n"/>
+      <c r="AB24" s="28" t="n"/>
+      <c r="AC24" s="30" t="n">
+        <v>1.378</v>
+      </c>
+      <c r="AD24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T18:35:03.616191Z</t>
+        </is>
+      </c>
+      <c r="AE24" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5600 (market_slug=aec-npb-ygo-tys-2026-08-08). Tie probability=0.0222.</t>
+        </is>
+      </c>
+      <c r="AF24" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG24" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH24" s="24" t="n"/>
+      <c r="AI24" s="31" t="n"/>
+      <c r="AJ24" s="31" t="n"/>
+      <c r="AK24" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL24" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM24" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN24" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO24" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP24" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AQ24" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AR24" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AS24" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="AT24" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="AU24" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="AV24" s="24" t="n"/>
+      <c r="AW24" s="24" t="n"/>
+      <c r="AX24" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY24" s="24" t="n"/>
+      <c r="AZ24" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA24" s="24" t="inlineStr">
+        <is>
+          <t>e9ab59688d3b514e2e6e6a6178916377e656c91d0946e4a0432922d92c29eca9</t>
+        </is>
+      </c>
+      <c r="BB24" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC24" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD24" s="24" t="inlineStr">
+        <is>
+          <t>e9ab59688d3b514e2e6e6a6178916377e656c91d0946e4a0432922d92c29eca9</t>
+        </is>
+      </c>
+      <c r="BE24" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF24" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG24" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH24" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:06:47.516040Z</t>
+        </is>
+      </c>
+      <c r="BI24" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ24" s="25" t="n"/>
+      <c r="BK24" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL24" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM24" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN24" s="28" t="n"/>
+      <c r="BO24" s="28" t="n"/>
+      <c r="BP24" s="25" t="n"/>
+      <c r="BQ24" s="27" t="n"/>
+      <c r="BR24" s="28" t="n"/>
+      <c r="BS24" s="28" t="n"/>
+      <c r="BT24" s="28" t="n"/>
+      <c r="BU24" s="25" t="n"/>
+      <c r="BV24" s="29" t="n"/>
+      <c r="BW24" s="24" t="n"/>
+      <c r="BX24" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY24" s="27" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BZ24" s="24" t="n"/>
+      <c r="CA24" s="31" t="n"/>
+      <c r="CB24" s="24" t="n"/>
+      <c r="CC24" s="24" t="n"/>
+      <c r="CD24" s="24" t="n"/>
+      <c r="CE24" s="24" t="n"/>
+      <c r="CF24" s="24" t="n"/>
+      <c r="CG24" s="24" t="n"/>
+      <c r="CH24" s="24" t="n"/>
+      <c r="CI24" s="24" t="n"/>
+      <c r="CJ24" s="24" t="n"/>
+      <c r="CK24" s="24" t="n"/>
+      <c r="CL24" s="24" t="n"/>
+      <c r="CM24" s="24" t="n"/>
+      <c r="CN24" s="24" t="n"/>
+      <c r="CO24" s="24" t="n"/>
+      <c r="CP24" s="24" t="n"/>
+      <c r="CQ24" s="24" t="n"/>
+      <c r="CR24" s="24" t="n"/>
+      <c r="CS24" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="24" t="inlineStr">
+        <is>
+          <t>fa8b50ba53d04184</t>
+        </is>
+      </c>
+      <c r="B25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:06:50.014675Z</t>
+        </is>
+      </c>
+      <c r="C25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>72735</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I25" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J25" s="25" t="n"/>
+      <c r="K25" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L25" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="M25" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="N25" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="O25" s="28" t="n">
+        <v>0.585415</v>
+      </c>
+      <c r="P25" s="28" t="n"/>
+      <c r="Q25" s="28" t="n">
+        <v>0.035865</v>
+      </c>
+      <c r="R25" s="26" t="n">
+        <v>38</v>
+      </c>
+      <c r="S25" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U25" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V25" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W25" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X25" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y25" s="25" t="n"/>
+      <c r="Z25" s="26" t="n"/>
+      <c r="AA25" s="28" t="n"/>
+      <c r="AB25" s="28" t="n"/>
+      <c r="AC25" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T18:35:03.747969Z</t>
+        </is>
+      </c>
+      <c r="AE25" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5500 (market_slug=aec-npb-ssl-fsh-2026-08-08). Tie probability=0.0288.</t>
+        </is>
+      </c>
+      <c r="AF25" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG25" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH25" s="24" t="n"/>
+      <c r="AI25" s="31" t="n"/>
+      <c r="AJ25" s="31" t="n"/>
+      <c r="AK25" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL25" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM25" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN25" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO25" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP25" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="AQ25" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="AR25" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="AS25" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AT25" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AU25" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AV25" s="24" t="n"/>
+      <c r="AW25" s="24" t="n"/>
+      <c r="AX25" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY25" s="24" t="n"/>
+      <c r="AZ25" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA25" s="24" t="inlineStr">
+        <is>
+          <t>e9ab59688d3b514e2e6e6a6178916377e656c91d0946e4a0432922d92c29eca9</t>
+        </is>
+      </c>
+      <c r="BB25" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC25" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD25" s="24" t="inlineStr">
+        <is>
+          <t>e9ab59688d3b514e2e6e6a6178916377e656c91d0946e4a0432922d92c29eca9</t>
+        </is>
+      </c>
+      <c r="BE25" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF25" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG25" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH25" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:06:48.067662Z</t>
+        </is>
+      </c>
+      <c r="BI25" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ25" s="25" t="n"/>
+      <c r="BK25" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="BL25" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="BM25" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="BN25" s="28" t="n"/>
+      <c r="BO25" s="28" t="n"/>
+      <c r="BP25" s="25" t="n"/>
+      <c r="BQ25" s="27" t="n"/>
+      <c r="BR25" s="28" t="n"/>
+      <c r="BS25" s="28" t="n"/>
+      <c r="BT25" s="28" t="n"/>
+      <c r="BU25" s="25" t="n"/>
+      <c r="BV25" s="29" t="n"/>
+      <c r="BW25" s="24" t="n"/>
+      <c r="BX25" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY25" s="27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BZ25" s="24" t="n"/>
+      <c r="CA25" s="31" t="n"/>
+      <c r="CB25" s="24" t="n"/>
+      <c r="CC25" s="24" t="n"/>
+      <c r="CD25" s="24" t="n"/>
+      <c r="CE25" s="24" t="n"/>
+      <c r="CF25" s="24" t="n"/>
+      <c r="CG25" s="24" t="n"/>
+      <c r="CH25" s="24" t="n"/>
+      <c r="CI25" s="24" t="n"/>
+      <c r="CJ25" s="24" t="n"/>
+      <c r="CK25" s="24" t="n"/>
+      <c r="CL25" s="24" t="n"/>
+      <c r="CM25" s="24" t="n"/>
+      <c r="CN25" s="24" t="n"/>
+      <c r="CO25" s="24" t="n"/>
+      <c r="CP25" s="24" t="n"/>
+      <c r="CQ25" s="24" t="n"/>
+      <c r="CR25" s="24" t="n"/>
+      <c r="CS25" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="36" customHeight="1">
+      <c r="A26" s="24" t="inlineStr">
+        <is>
+          <t>2aa46eb0591e456a</t>
+        </is>
+      </c>
+      <c r="B26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:06:50.014675Z</t>
+        </is>
+      </c>
+      <c r="C26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>72736</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>Orix Buffaloes</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="inlineStr">
+        <is>
+          <t>Chiba Lotte Marines</t>
+        </is>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I26" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J26" s="25" t="n"/>
+      <c r="K26" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L26" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="M26" s="27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="N26" s="28" t="n">
+        <v>0.480769</v>
+      </c>
+      <c r="O26" s="28" t="n">
+        <v>0.5309430000000001</v>
+      </c>
+      <c r="P26" s="28" t="n"/>
+      <c r="Q26" s="28" t="n">
+        <v>0.050174</v>
+      </c>
+      <c r="R26" s="26" t="n">
+        <v>45</v>
+      </c>
+      <c r="S26" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U26" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V26" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W26" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X26" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y26" s="25" t="n"/>
+      <c r="Z26" s="26" t="n"/>
+      <c r="AA26" s="28" t="n"/>
+      <c r="AB26" s="28" t="n"/>
+      <c r="AC26" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T18:35:03.877371Z</t>
+        </is>
+      </c>
+      <c r="AE26" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.4800 (market_slug=aec-npb-clm-obr-2026-08-08). Tie probability=0.0336.</t>
+        </is>
+      </c>
+      <c r="AF26" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG26" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH26" s="24" t="n"/>
+      <c r="AI26" s="31" t="n"/>
+      <c r="AJ26" s="31" t="n"/>
+      <c r="AK26" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL26" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM26" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN26" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO26" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP26" s="24" t="inlineStr">
+        <is>
+          <t>Orix Buffaloes</t>
+        </is>
+      </c>
+      <c r="AQ26" s="24" t="inlineStr">
+        <is>
+          <t>Orix Buffaloes</t>
+        </is>
+      </c>
+      <c r="AR26" s="24" t="inlineStr">
+        <is>
+          <t>Orix Buffaloes</t>
+        </is>
+      </c>
+      <c r="AS26" s="24" t="inlineStr">
+        <is>
+          <t>Chiba Lotte Marines</t>
+        </is>
+      </c>
+      <c r="AT26" s="24" t="inlineStr">
+        <is>
+          <t>Chiba Lotte Marines</t>
+        </is>
+      </c>
+      <c r="AU26" s="24" t="inlineStr">
+        <is>
+          <t>Chiba Lotte Marines</t>
+        </is>
+      </c>
+      <c r="AV26" s="24" t="n"/>
+      <c r="AW26" s="24" t="n"/>
+      <c r="AX26" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY26" s="24" t="n"/>
+      <c r="AZ26" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA26" s="24" t="inlineStr">
+        <is>
+          <t>e9ab59688d3b514e2e6e6a6178916377e656c91d0946e4a0432922d92c29eca9</t>
+        </is>
+      </c>
+      <c r="BB26" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC26" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD26" s="24" t="inlineStr">
+        <is>
+          <t>e9ab59688d3b514e2e6e6a6178916377e656c91d0946e4a0432922d92c29eca9</t>
+        </is>
+      </c>
+      <c r="BE26" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF26" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG26" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH26" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:06:48.734721Z</t>
+        </is>
+      </c>
+      <c r="BI26" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ26" s="25" t="n"/>
+      <c r="BK26" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="BL26" s="27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM26" s="28" t="n">
+        <v>0.480769</v>
+      </c>
+      <c r="BN26" s="28" t="n"/>
+      <c r="BO26" s="28" t="n"/>
+      <c r="BP26" s="25" t="n"/>
+      <c r="BQ26" s="27" t="n"/>
+      <c r="BR26" s="28" t="n"/>
+      <c r="BS26" s="28" t="n"/>
+      <c r="BT26" s="28" t="n"/>
+      <c r="BU26" s="25" t="n"/>
+      <c r="BV26" s="29" t="n"/>
+      <c r="BW26" s="24" t="n"/>
+      <c r="BX26" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY26" s="27" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BZ26" s="24" t="n"/>
+      <c r="CA26" s="31" t="n"/>
+      <c r="CB26" s="24" t="n"/>
+      <c r="CC26" s="24" t="n"/>
+      <c r="CD26" s="24" t="n"/>
+      <c r="CE26" s="24" t="n"/>
+      <c r="CF26" s="24" t="n"/>
+      <c r="CG26" s="24" t="n"/>
+      <c r="CH26" s="24" t="n"/>
+      <c r="CI26" s="24" t="n"/>
+      <c r="CJ26" s="24" t="n"/>
+      <c r="CK26" s="24" t="n"/>
+      <c r="CL26" s="24" t="n"/>
+      <c r="CM26" s="24" t="n"/>
+      <c r="CN26" s="24" t="n"/>
+      <c r="CO26" s="24" t="n"/>
+      <c r="CP26" s="24" t="n"/>
+      <c r="CQ26" s="24" t="n"/>
+      <c r="CR26" s="24" t="n"/>
+      <c r="CS26" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="24" t="inlineStr">
+        <is>
+          <t>ea96d014d0a3498d</t>
+        </is>
+      </c>
+      <c r="B27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:06:50.014675Z</t>
+        </is>
+      </c>
+      <c r="C27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>72737</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="H27" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I27" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J27" s="25" t="n"/>
+      <c r="K27" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L27" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M27" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N27" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O27" s="28" t="n">
+        <v>0.564611</v>
+      </c>
+      <c r="P27" s="28" t="n"/>
+      <c r="Q27" s="28" t="n">
+        <v>0.00514</v>
+      </c>
+      <c r="R27" s="26" t="n">
+        <v>23</v>
+      </c>
+      <c r="S27" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U27" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V27" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W27" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="X27" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y27" s="25" t="n"/>
+      <c r="Z27" s="26" t="n"/>
+      <c r="AA27" s="28" t="n"/>
+      <c r="AB27" s="28" t="n"/>
+      <c r="AC27" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T18:35:04.027549Z</t>
+        </is>
+      </c>
+      <c r="AE27" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5600 (market_slug=aec-npb-hta-cdh-2026-08-08). Tie probability=0.0307.</t>
+        </is>
+      </c>
+      <c r="AF27" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG27" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH27" s="24" t="n"/>
+      <c r="AI27" s="31" t="n"/>
+      <c r="AJ27" s="31" t="n"/>
+      <c r="AK27" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL27" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM27" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN27" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO27" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP27" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="AQ27" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="AR27" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="AS27" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AT27" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AU27" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AV27" s="24" t="n"/>
+      <c r="AW27" s="24" t="n"/>
+      <c r="AX27" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY27" s="24" t="n"/>
+      <c r="AZ27" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA27" s="24" t="inlineStr">
+        <is>
+          <t>e9ab59688d3b514e2e6e6a6178916377e656c91d0946e4a0432922d92c29eca9</t>
+        </is>
+      </c>
+      <c r="BB27" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC27" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD27" s="24" t="inlineStr">
+        <is>
+          <t>e9ab59688d3b514e2e6e6a6178916377e656c91d0946e4a0432922d92c29eca9</t>
+        </is>
+      </c>
+      <c r="BE27" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF27" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG27" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH27" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:06:49.378255Z</t>
+        </is>
+      </c>
+      <c r="BI27" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ27" s="25" t="n"/>
+      <c r="BK27" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL27" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM27" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN27" s="28" t="n"/>
+      <c r="BO27" s="28" t="n"/>
+      <c r="BP27" s="25" t="n"/>
+      <c r="BQ27" s="27" t="n"/>
+      <c r="BR27" s="28" t="n"/>
+      <c r="BS27" s="28" t="n"/>
+      <c r="BT27" s="28" t="n"/>
+      <c r="BU27" s="25" t="n"/>
+      <c r="BV27" s="29" t="n"/>
+      <c r="BW27" s="24" t="n"/>
+      <c r="BX27" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY27" s="27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BZ27" s="24" t="n"/>
+      <c r="CA27" s="31" t="n"/>
+      <c r="CB27" s="24" t="n"/>
+      <c r="CC27" s="24" t="n"/>
+      <c r="CD27" s="24" t="n"/>
+      <c r="CE27" s="24" t="n"/>
+      <c r="CF27" s="24" t="n"/>
+      <c r="CG27" s="24" t="n"/>
+      <c r="CH27" s="24" t="n"/>
+      <c r="CI27" s="24" t="n"/>
+      <c r="CJ27" s="24" t="n"/>
+      <c r="CK27" s="24" t="n"/>
+      <c r="CL27" s="24" t="n"/>
+      <c r="CM27" s="24" t="n"/>
+      <c r="CN27" s="24" t="n"/>
+      <c r="CO27" s="24" t="n"/>
+      <c r="CP27" s="24" t="n"/>
+      <c r="CQ27" s="24" t="n"/>
+      <c r="CR27" s="24" t="n"/>
+      <c r="CS27" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>777fe6f89e3f44f7</t>
+        </is>
+      </c>
+      <c r="B28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:06:50.014675Z</t>
+        </is>
+      </c>
+      <c r="C28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>72738</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F28" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="G28" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="H28" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I28" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J28" s="25" t="n"/>
+      <c r="K28" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L28" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M28" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N28" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O28" s="28" t="n">
+        <v>0.596329</v>
+      </c>
+      <c r="P28" s="28" t="n"/>
+      <c r="Q28" s="28" t="n">
+        <v>-0.003671</v>
+      </c>
+      <c r="R28" s="26" t="n">
+        <v>18</v>
+      </c>
+      <c r="S28" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U28" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V28" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W28" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X28" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y28" s="25" t="n"/>
+      <c r="Z28" s="26" t="n"/>
+      <c r="AA28" s="28" t="n"/>
+      <c r="AB28" s="28" t="n"/>
+      <c r="AC28" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T18:35:04.159959Z</t>
+        </is>
+      </c>
+      <c r="AE28" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6000 (market_slug=aec-npb-ybo-hci-2026-08-08). Tie probability=0.0279.</t>
+        </is>
+      </c>
+      <c r="AF28" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG28" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH28" s="24" t="n"/>
+      <c r="AI28" s="31" t="n"/>
+      <c r="AJ28" s="31" t="n"/>
+      <c r="AK28" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL28" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM28" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN28" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO28" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP28" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="AQ28" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="AR28" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="AS28" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AT28" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AU28" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AV28" s="24" t="n"/>
+      <c r="AW28" s="24" t="n"/>
+      <c r="AX28" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY28" s="24" t="n"/>
+      <c r="AZ28" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA28" s="24" t="inlineStr">
+        <is>
+          <t>e9ab59688d3b514e2e6e6a6178916377e656c91d0946e4a0432922d92c29eca9</t>
+        </is>
+      </c>
+      <c r="BB28" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC28" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD28" s="24" t="inlineStr">
+        <is>
+          <t>e9ab59688d3b514e2e6e6a6178916377e656c91d0946e4a0432922d92c29eca9</t>
+        </is>
+      </c>
+      <c r="BE28" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF28" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG28" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH28" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-08T04:06:50.014626Z</t>
+        </is>
+      </c>
+      <c r="BI28" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ28" s="25" t="n"/>
+      <c r="BK28" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL28" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM28" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN28" s="28" t="n"/>
+      <c r="BO28" s="28" t="n"/>
+      <c r="BP28" s="25" t="n"/>
+      <c r="BQ28" s="27" t="n"/>
+      <c r="BR28" s="28" t="n"/>
+      <c r="BS28" s="28" t="n"/>
+      <c r="BT28" s="28" t="n"/>
+      <c r="BU28" s="25" t="n"/>
+      <c r="BV28" s="29" t="n"/>
+      <c r="BW28" s="24" t="n"/>
+      <c r="BX28" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY28" s="27" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BZ28" s="24" t="n"/>
+      <c r="CA28" s="31" t="n"/>
+      <c r="CB28" s="24" t="n"/>
+      <c r="CC28" s="24" t="n"/>
+      <c r="CD28" s="24" t="n"/>
+      <c r="CE28" s="24" t="n"/>
+      <c r="CF28" s="24" t="n"/>
+      <c r="CG28" s="24" t="n"/>
+      <c r="CH28" s="24" t="n"/>
+      <c r="CI28" s="24" t="n"/>
+      <c r="CJ28" s="24" t="n"/>
+      <c r="CK28" s="24" t="n"/>
+      <c r="CL28" s="24" t="n"/>
+      <c r="CM28" s="24" t="n"/>
+      <c r="CN28" s="24" t="n"/>
+      <c r="CO28" s="24" t="n"/>
+      <c r="CP28" s="24" t="n"/>
+      <c r="CQ28" s="24" t="n"/>
+      <c r="CR28" s="24" t="n"/>
+      <c r="CS28" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>1f70ae91533443d5</t>
+        </is>
+      </c>
+      <c r="B29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T05:17:45.141972Z</t>
+        </is>
+      </c>
+      <c r="C29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>73655</t>
+        </is>
+      </c>
+      <c r="E29" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F29" s="24" t="inlineStr">
+        <is>
+          <t>Orix Buffaloes</t>
+        </is>
+      </c>
+      <c r="G29" s="24" t="inlineStr">
+        <is>
+          <t>Chiba Lotte Marines</t>
+        </is>
+      </c>
+      <c r="H29" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I29" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J29" s="25" t="n"/>
+      <c r="K29" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L29" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="M29" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="N29" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="O29" s="28" t="n">
+        <v>0.547003</v>
+      </c>
+      <c r="P29" s="28" t="n"/>
+      <c r="Q29" s="28" t="n">
+        <v>0.056807</v>
+      </c>
+      <c r="R29" s="26" t="n">
+        <v>48</v>
+      </c>
+      <c r="S29" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U29" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V29" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W29" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="X29" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y29" s="25" t="n"/>
+      <c r="Z29" s="26" t="n"/>
+      <c r="AA29" s="28" t="n"/>
+      <c r="AB29" s="28" t="n"/>
+      <c r="AC29" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T20:26:16.355091Z</t>
+        </is>
+      </c>
+      <c r="AE29" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.4900 (market_slug=aec-npb-clm-obr-2026-08-09). Tie probability=0.0322.</t>
+        </is>
+      </c>
+      <c r="AF29" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG29" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH29" s="24" t="n"/>
+      <c r="AI29" s="31" t="n"/>
+      <c r="AJ29" s="31" t="n"/>
+      <c r="AK29" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL29" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM29" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN29" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO29" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP29" s="24" t="inlineStr">
+        <is>
+          <t>Orix Buffaloes</t>
+        </is>
+      </c>
+      <c r="AQ29" s="24" t="inlineStr">
+        <is>
+          <t>Orix Buffaloes</t>
+        </is>
+      </c>
+      <c r="AR29" s="24" t="inlineStr">
+        <is>
+          <t>Orix Buffaloes</t>
+        </is>
+      </c>
+      <c r="AS29" s="24" t="inlineStr">
+        <is>
+          <t>Chiba Lotte Marines</t>
+        </is>
+      </c>
+      <c r="AT29" s="24" t="inlineStr">
+        <is>
+          <t>Chiba Lotte Marines</t>
+        </is>
+      </c>
+      <c r="AU29" s="24" t="inlineStr">
+        <is>
+          <t>Chiba Lotte Marines</t>
+        </is>
+      </c>
+      <c r="AV29" s="24" t="n"/>
+      <c r="AW29" s="24" t="n"/>
+      <c r="AX29" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY29" s="24" t="n"/>
+      <c r="AZ29" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA29" s="24" t="inlineStr">
+        <is>
+          <t>1b7c2815d24b862bd8c1893baa5e4f65c12122708fa3c5aac2d6bac9c376d736</t>
+        </is>
+      </c>
+      <c r="BB29" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC29" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD29" s="24" t="inlineStr">
+        <is>
+          <t>1b7c2815d24b862bd8c1893baa5e4f65c12122708fa3c5aac2d6bac9c376d736</t>
+        </is>
+      </c>
+      <c r="BE29" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF29" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG29" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH29" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T05:17:43.172262Z</t>
+        </is>
+      </c>
+      <c r="BI29" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ29" s="25" t="n"/>
+      <c r="BK29" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="BL29" s="27" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BM29" s="28" t="n">
+        <v>0.490196</v>
+      </c>
+      <c r="BN29" s="28" t="n"/>
+      <c r="BO29" s="28" t="n"/>
+      <c r="BP29" s="25" t="n"/>
+      <c r="BQ29" s="27" t="n"/>
+      <c r="BR29" s="28" t="n"/>
+      <c r="BS29" s="28" t="n"/>
+      <c r="BT29" s="28" t="n"/>
+      <c r="BU29" s="25" t="n"/>
+      <c r="BV29" s="29" t="n"/>
+      <c r="BW29" s="24" t="n"/>
+      <c r="BX29" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY29" s="27" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BZ29" s="24" t="n"/>
+      <c r="CA29" s="31" t="n"/>
+      <c r="CB29" s="24" t="n"/>
+      <c r="CC29" s="24" t="n"/>
+      <c r="CD29" s="24" t="n"/>
+      <c r="CE29" s="24" t="n"/>
+      <c r="CF29" s="24" t="n"/>
+      <c r="CG29" s="24" t="n"/>
+      <c r="CH29" s="24" t="n"/>
+      <c r="CI29" s="24" t="n"/>
+      <c r="CJ29" s="24" t="n"/>
+      <c r="CK29" s="24" t="n"/>
+      <c r="CL29" s="24" t="n"/>
+      <c r="CM29" s="24" t="n"/>
+      <c r="CN29" s="24" t="n"/>
+      <c r="CO29" s="24" t="n"/>
+      <c r="CP29" s="24" t="n"/>
+      <c r="CQ29" s="24" t="n"/>
+      <c r="CR29" s="24" t="n"/>
+      <c r="CS29" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>dde9695350e144cd</t>
+        </is>
+      </c>
+      <c r="B30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T05:17:45.141972Z</t>
+        </is>
+      </c>
+      <c r="C30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T08:00:00Z</t>
+        </is>
+      </c>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>73656</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F30" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="G30" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="H30" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I30" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J30" s="25" t="n"/>
+      <c r="K30" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L30" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="M30" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="N30" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="O30" s="28" t="n">
+        <v>0.571416</v>
+      </c>
+      <c r="P30" s="28" t="n"/>
+      <c r="Q30" s="28" t="n">
+        <v>-0.018748</v>
+      </c>
+      <c r="R30" s="26" t="n">
+        <v>11</v>
+      </c>
+      <c r="S30" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U30" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V30" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W30" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="X30" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="25" t="n"/>
+      <c r="Z30" s="26" t="n"/>
+      <c r="AA30" s="28" t="n"/>
+      <c r="AB30" s="28" t="n"/>
+      <c r="AC30" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T20:26:16.493332Z</t>
+        </is>
+      </c>
+      <c r="AE30" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5900 (market_slug=aec-npb-ssl-fsh-2026-08-09). Tie probability=0.0300.</t>
+        </is>
+      </c>
+      <c r="AF30" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG30" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH30" s="24" t="n"/>
+      <c r="AI30" s="31" t="n"/>
+      <c r="AJ30" s="31" t="n"/>
+      <c r="AK30" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL30" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM30" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN30" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO30" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP30" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="AQ30" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="AR30" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="AS30" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AT30" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AU30" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AV30" s="24" t="n"/>
+      <c r="AW30" s="24" t="n"/>
+      <c r="AX30" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY30" s="24" t="n"/>
+      <c r="AZ30" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA30" s="24" t="inlineStr">
+        <is>
+          <t>1b7c2815d24b862bd8c1893baa5e4f65c12122708fa3c5aac2d6bac9c376d736</t>
+        </is>
+      </c>
+      <c r="BB30" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC30" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD30" s="24" t="inlineStr">
+        <is>
+          <t>1b7c2815d24b862bd8c1893baa5e4f65c12122708fa3c5aac2d6bac9c376d736</t>
+        </is>
+      </c>
+      <c r="BE30" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF30" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG30" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH30" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T05:17:43.809915Z</t>
+        </is>
+      </c>
+      <c r="BI30" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ30" s="25" t="n"/>
+      <c r="BK30" s="26" t="n">
+        <v>-144</v>
+      </c>
+      <c r="BL30" s="27" t="n">
+        <v>1.694444</v>
+      </c>
+      <c r="BM30" s="28" t="n">
+        <v>0.590164</v>
+      </c>
+      <c r="BN30" s="28" t="n"/>
+      <c r="BO30" s="28" t="n"/>
+      <c r="BP30" s="25" t="n"/>
+      <c r="BQ30" s="27" t="n"/>
+      <c r="BR30" s="28" t="n"/>
+      <c r="BS30" s="28" t="n"/>
+      <c r="BT30" s="28" t="n"/>
+      <c r="BU30" s="25" t="n"/>
+      <c r="BV30" s="29" t="n"/>
+      <c r="BW30" s="24" t="n"/>
+      <c r="BX30" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY30" s="27" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BZ30" s="24" t="n"/>
+      <c r="CA30" s="31" t="n"/>
+      <c r="CB30" s="24" t="n"/>
+      <c r="CC30" s="24" t="n"/>
+      <c r="CD30" s="24" t="n"/>
+      <c r="CE30" s="24" t="n"/>
+      <c r="CF30" s="24" t="n"/>
+      <c r="CG30" s="24" t="n"/>
+      <c r="CH30" s="24" t="n"/>
+      <c r="CI30" s="24" t="n"/>
+      <c r="CJ30" s="24" t="n"/>
+      <c r="CK30" s="24" t="n"/>
+      <c r="CL30" s="24" t="n"/>
+      <c r="CM30" s="24" t="n"/>
+      <c r="CN30" s="24" t="n"/>
+      <c r="CO30" s="24" t="n"/>
+      <c r="CP30" s="24" t="n"/>
+      <c r="CQ30" s="24" t="n"/>
+      <c r="CR30" s="24" t="n"/>
+      <c r="CS30" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>0ce75ac6e6a748fb</t>
+        </is>
+      </c>
+      <c r="B31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T05:17:45.141972Z</t>
+        </is>
+      </c>
+      <c r="C31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>73664</t>
+        </is>
+      </c>
+      <c r="E31" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F31" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="G31" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="H31" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I31" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J31" s="25" t="n"/>
+      <c r="K31" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L31" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="M31" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="N31" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="O31" s="28" t="n">
+        <v>0.604738</v>
+      </c>
+      <c r="P31" s="28" t="n"/>
+      <c r="Q31" s="28" t="n">
+        <v>-0.004637</v>
+      </c>
+      <c r="R31" s="26" t="n">
+        <v>18</v>
+      </c>
+      <c r="S31" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U31" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V31" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W31" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y31" s="25" t="n"/>
+      <c r="Z31" s="26" t="n"/>
+      <c r="AA31" s="28" t="n"/>
+      <c r="AB31" s="28" t="n"/>
+      <c r="AC31" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T20:26:16.627025Z</t>
+        </is>
+      </c>
+      <c r="AE31" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6100 (market_slug=aec-npb-ybo-hci-2026-08-09). Tie probability=0.0271.</t>
+        </is>
+      </c>
+      <c r="AF31" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG31" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH31" s="24" t="n"/>
+      <c r="AI31" s="31" t="n"/>
+      <c r="AJ31" s="31" t="n"/>
+      <c r="AK31" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL31" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM31" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN31" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO31" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP31" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="AQ31" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="AR31" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="AS31" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AT31" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AU31" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AV31" s="24" t="n"/>
+      <c r="AW31" s="24" t="n"/>
+      <c r="AX31" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY31" s="24" t="n"/>
+      <c r="AZ31" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA31" s="24" t="inlineStr">
+        <is>
+          <t>1b7c2815d24b862bd8c1893baa5e4f65c12122708fa3c5aac2d6bac9c376d736</t>
+        </is>
+      </c>
+      <c r="BB31" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC31" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD31" s="24" t="inlineStr">
+        <is>
+          <t>1b7c2815d24b862bd8c1893baa5e4f65c12122708fa3c5aac2d6bac9c376d736</t>
+        </is>
+      </c>
+      <c r="BE31" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF31" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG31" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH31" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T05:17:44.416064Z</t>
+        </is>
+      </c>
+      <c r="BI31" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ31" s="25" t="n"/>
+      <c r="BK31" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="BL31" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BM31" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="BN31" s="28" t="n"/>
+      <c r="BO31" s="28" t="n"/>
+      <c r="BP31" s="25" t="n"/>
+      <c r="BQ31" s="27" t="n"/>
+      <c r="BR31" s="28" t="n"/>
+      <c r="BS31" s="28" t="n"/>
+      <c r="BT31" s="28" t="n"/>
+      <c r="BU31" s="25" t="n"/>
+      <c r="BV31" s="29" t="n"/>
+      <c r="BW31" s="24" t="n"/>
+      <c r="BX31" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY31" s="27" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BZ31" s="24" t="n"/>
+      <c r="CA31" s="31" t="n"/>
+      <c r="CB31" s="24" t="n"/>
+      <c r="CC31" s="24" t="n"/>
+      <c r="CD31" s="24" t="n"/>
+      <c r="CE31" s="24" t="n"/>
+      <c r="CF31" s="24" t="n"/>
+      <c r="CG31" s="24" t="n"/>
+      <c r="CH31" s="24" t="n"/>
+      <c r="CI31" s="24" t="n"/>
+      <c r="CJ31" s="24" t="n"/>
+      <c r="CK31" s="24" t="n"/>
+      <c r="CL31" s="24" t="n"/>
+      <c r="CM31" s="24" t="n"/>
+      <c r="CN31" s="24" t="n"/>
+      <c r="CO31" s="24" t="n"/>
+      <c r="CP31" s="24" t="n"/>
+      <c r="CQ31" s="24" t="n"/>
+      <c r="CR31" s="24" t="n"/>
+      <c r="CS31" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>edc48d2b878540d9</t>
+        </is>
+      </c>
+      <c r="B32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T05:17:45.141972Z</t>
+        </is>
+      </c>
+      <c r="C32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>73665</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F32" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="G32" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="H32" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I32" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J32" s="25" t="n"/>
+      <c r="K32" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L32" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="M32" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="N32" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="O32" s="28" t="n">
+        <v>0.540616</v>
+      </c>
+      <c r="P32" s="28" t="n"/>
+      <c r="Q32" s="28" t="n">
+        <v>-0.079156</v>
+      </c>
+      <c r="R32" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U32" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V32" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W32" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y32" s="25" t="n"/>
+      <c r="Z32" s="26" t="n"/>
+      <c r="AA32" s="28" t="n"/>
+      <c r="AB32" s="28" t="n"/>
+      <c r="AC32" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T20:26:16.763277Z</t>
+        </is>
+      </c>
+      <c r="AE32" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6200 (market_slug=aec-npb-hta-cdh-2026-08-09). Tie probability=0.0327.</t>
+        </is>
+      </c>
+      <c r="AF32" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG32" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH32" s="24" t="n"/>
+      <c r="AI32" s="31" t="n"/>
+      <c r="AJ32" s="31" t="n"/>
+      <c r="AK32" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL32" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM32" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN32" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO32" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_WINNER_OVERVALUED</t>
+        </is>
+      </c>
+      <c r="AP32" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="AQ32" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="AR32" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="AS32" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AT32" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AU32" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AV32" s="24" t="n"/>
+      <c r="AW32" s="24" t="n"/>
+      <c r="AX32" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY32" s="24" t="n"/>
+      <c r="AZ32" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA32" s="24" t="inlineStr">
+        <is>
+          <t>1b7c2815d24b862bd8c1893baa5e4f65c12122708fa3c5aac2d6bac9c376d736</t>
+        </is>
+      </c>
+      <c r="BB32" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC32" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD32" s="24" t="inlineStr">
+        <is>
+          <t>1b7c2815d24b862bd8c1893baa5e4f65c12122708fa3c5aac2d6bac9c376d736</t>
+        </is>
+      </c>
+      <c r="BE32" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF32" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG32" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH32" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T05:17:45.141880Z</t>
+        </is>
+      </c>
+      <c r="BI32" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ32" s="25" t="n"/>
+      <c r="BK32" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="BL32" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="BM32" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="BN32" s="28" t="n"/>
+      <c r="BO32" s="28" t="n"/>
+      <c r="BP32" s="25" t="n"/>
+      <c r="BQ32" s="27" t="n"/>
+      <c r="BR32" s="28" t="n"/>
+      <c r="BS32" s="28" t="n"/>
+      <c r="BT32" s="28" t="n"/>
+      <c r="BU32" s="25" t="n"/>
+      <c r="BV32" s="29" t="n"/>
+      <c r="BW32" s="24" t="n"/>
+      <c r="BX32" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="BY32" s="27" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BZ32" s="24" t="n"/>
+      <c r="CA32" s="31" t="n"/>
+      <c r="CB32" s="24" t="n"/>
+      <c r="CC32" s="24" t="n"/>
+      <c r="CD32" s="24" t="n"/>
+      <c r="CE32" s="24" t="n"/>
+      <c r="CF32" s="24" t="n"/>
+      <c r="CG32" s="24" t="n"/>
+      <c r="CH32" s="24" t="n"/>
+      <c r="CI32" s="24" t="n"/>
+      <c r="CJ32" s="24" t="n"/>
+      <c r="CK32" s="24" t="n"/>
+      <c r="CL32" s="24" t="n"/>
+      <c r="CM32" s="24" t="n"/>
+      <c r="CN32" s="24" t="n"/>
+      <c r="CO32" s="24" t="n"/>
+      <c r="CP32" s="24" t="n"/>
+      <c r="CQ32" s="24" t="n"/>
+      <c r="CR32" s="24" t="n"/>
+      <c r="CS32" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>2de7ef6136274bf0</t>
+        </is>
+      </c>
+      <c r="B33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:21:35.145090Z</t>
+        </is>
+      </c>
+      <c r="C33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D33" s="24" t="inlineStr">
+        <is>
+          <t>76184</t>
+        </is>
+      </c>
+      <c r="E33" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F33" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="G33" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="H33" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I33" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J33" s="25" t="n"/>
+      <c r="K33" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L33" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="M33" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="N33" s="28" t="n">
+        <v>0.440529</v>
+      </c>
+      <c r="O33" s="28" t="n">
+        <v>0.515505</v>
+      </c>
+      <c r="P33" s="28" t="n"/>
+      <c r="Q33" s="28" t="n">
+        <v>0.074976</v>
+      </c>
+      <c r="R33" s="26" t="n">
+        <v>57</v>
+      </c>
+      <c r="S33" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U33" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V33" s="24" t="n"/>
+      <c r="W33" s="26" t="n"/>
+      <c r="X33" s="26" t="n"/>
+      <c r="Y33" s="25" t="n"/>
+      <c r="Z33" s="26" t="n"/>
+      <c r="AA33" s="28" t="n"/>
+      <c r="AB33" s="28" t="n"/>
+      <c r="AC33" s="30" t="n"/>
+      <c r="AD33" s="24" t="n"/>
+      <c r="AE33" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.4400 (market_slug=aec-npb-ygo-hta-2026-08-12). Tie probability=0.0348.</t>
+        </is>
+      </c>
+      <c r="AF33" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG33" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH33" s="24" t="n"/>
+      <c r="AI33" s="31" t="n"/>
+      <c r="AJ33" s="31" t="n"/>
+      <c r="AK33" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL33" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM33" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN33" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO33" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP33" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AQ33" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AR33" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AS33" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="AT33" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="AU33" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="AV33" s="24" t="n"/>
+      <c r="AW33" s="24" t="n"/>
+      <c r="AX33" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY33" s="24" t="n"/>
+      <c r="AZ33" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA33" s="24" t="inlineStr">
+        <is>
+          <t>05ce5c163469a19fa69948e39f5a5c074f3e14d31fa465677897d80bd6c4e801</t>
+        </is>
+      </c>
+      <c r="BB33" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC33" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD33" s="24" t="inlineStr">
+        <is>
+          <t>05ce5c163469a19fa69948e39f5a5c074f3e14d31fa465677897d80bd6c4e801</t>
+        </is>
+      </c>
+      <c r="BE33" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF33" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG33" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:21:31.890109Z</t>
+        </is>
+      </c>
+      <c r="BI33" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ33" s="25" t="n"/>
+      <c r="BK33" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="BL33" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BM33" s="28" t="n">
+        <v>0.440529</v>
+      </c>
+      <c r="BN33" s="28" t="n"/>
+      <c r="BO33" s="28" t="n"/>
+      <c r="BP33" s="25" t="n"/>
+      <c r="BQ33" s="27" t="n"/>
+      <c r="BR33" s="28" t="n"/>
+      <c r="BS33" s="28" t="n"/>
+      <c r="BT33" s="28" t="n"/>
+      <c r="BU33" s="25" t="n"/>
+      <c r="BV33" s="29" t="n"/>
+      <c r="BW33" s="24" t="n"/>
+      <c r="BX33" s="30" t="n"/>
+      <c r="BY33" s="27" t="n"/>
+      <c r="BZ33" s="24" t="n"/>
+      <c r="CA33" s="31" t="n"/>
+      <c r="CB33" s="24" t="n"/>
+      <c r="CC33" s="24" t="n"/>
+      <c r="CD33" s="24" t="n"/>
+      <c r="CE33" s="24" t="n"/>
+      <c r="CF33" s="24" t="n"/>
+      <c r="CG33" s="24" t="n"/>
+      <c r="CH33" s="24" t="n"/>
+      <c r="CI33" s="24" t="n"/>
+      <c r="CJ33" s="24" t="n"/>
+      <c r="CK33" s="24" t="n"/>
+      <c r="CL33" s="24" t="n"/>
+      <c r="CM33" s="24" t="n"/>
+      <c r="CN33" s="24" t="n"/>
+      <c r="CO33" s="24" t="n"/>
+      <c r="CP33" s="24" t="n"/>
+      <c r="CQ33" s="24" t="n"/>
+      <c r="CR33" s="24" t="n"/>
+      <c r="CS33" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>acbde3c2abd54fbb</t>
+        </is>
+      </c>
+      <c r="B34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:21:35.145090Z</t>
+        </is>
+      </c>
+      <c r="C34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D34" s="24" t="inlineStr">
+        <is>
+          <t>76185</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F34" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="G34" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="H34" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I34" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J34" s="25" t="n"/>
+      <c r="K34" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L34" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="M34" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="N34" s="28" t="n">
+        <v>0.440529</v>
+      </c>
+      <c r="O34" s="28" t="n">
+        <v>0.53288</v>
+      </c>
+      <c r="P34" s="28" t="n"/>
+      <c r="Q34" s="28" t="n">
+        <v>0.092351</v>
+      </c>
+      <c r="R34" s="26" t="n">
+        <v>66</v>
+      </c>
+      <c r="S34" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T34" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U34" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V34" s="24" t="n"/>
+      <c r="W34" s="26" t="n"/>
+      <c r="X34" s="26" t="n"/>
+      <c r="Y34" s="25" t="n"/>
+      <c r="Z34" s="26" t="n"/>
+      <c r="AA34" s="28" t="n"/>
+      <c r="AB34" s="28" t="n"/>
+      <c r="AC34" s="30" t="n"/>
+      <c r="AD34" s="24" t="n"/>
+      <c r="AE34" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.4400 (market_slug=aec-npb-cdh-ybo-2026-08-12). Tie probability=0.0333.</t>
+        </is>
+      </c>
+      <c r="AF34" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG34" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH34" s="24" t="n"/>
+      <c r="AI34" s="31" t="n"/>
+      <c r="AJ34" s="31" t="n"/>
+      <c r="AK34" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL34" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM34" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN34" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO34" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP34" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AQ34" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AR34" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AS34" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="AT34" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="AU34" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="AV34" s="24" t="n"/>
+      <c r="AW34" s="24" t="n"/>
+      <c r="AX34" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY34" s="24" t="n"/>
+      <c r="AZ34" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA34" s="24" t="inlineStr">
+        <is>
+          <t>05ce5c163469a19fa69948e39f5a5c074f3e14d31fa465677897d80bd6c4e801</t>
+        </is>
+      </c>
+      <c r="BB34" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC34" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD34" s="24" t="inlineStr">
+        <is>
+          <t>05ce5c163469a19fa69948e39f5a5c074f3e14d31fa465677897d80bd6c4e801</t>
+        </is>
+      </c>
+      <c r="BE34" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF34" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG34" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:21:32.791156Z</t>
+        </is>
+      </c>
+      <c r="BI34" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ34" s="25" t="n"/>
+      <c r="BK34" s="26" t="n">
+        <v>127</v>
+      </c>
+      <c r="BL34" s="27" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BM34" s="28" t="n">
+        <v>0.440529</v>
+      </c>
+      <c r="BN34" s="28" t="n"/>
+      <c r="BO34" s="28" t="n"/>
+      <c r="BP34" s="25" t="n"/>
+      <c r="BQ34" s="27" t="n"/>
+      <c r="BR34" s="28" t="n"/>
+      <c r="BS34" s="28" t="n"/>
+      <c r="BT34" s="28" t="n"/>
+      <c r="BU34" s="25" t="n"/>
+      <c r="BV34" s="29" t="n"/>
+      <c r="BW34" s="24" t="n"/>
+      <c r="BX34" s="30" t="n"/>
+      <c r="BY34" s="27" t="n"/>
+      <c r="BZ34" s="24" t="n"/>
+      <c r="CA34" s="31" t="n"/>
+      <c r="CB34" s="24" t="n"/>
+      <c r="CC34" s="24" t="n"/>
+      <c r="CD34" s="24" t="n"/>
+      <c r="CE34" s="24" t="n"/>
+      <c r="CF34" s="24" t="n"/>
+      <c r="CG34" s="24" t="n"/>
+      <c r="CH34" s="24" t="n"/>
+      <c r="CI34" s="24" t="n"/>
+      <c r="CJ34" s="24" t="n"/>
+      <c r="CK34" s="24" t="n"/>
+      <c r="CL34" s="24" t="n"/>
+      <c r="CM34" s="24" t="n"/>
+      <c r="CN34" s="24" t="n"/>
+      <c r="CO34" s="24" t="n"/>
+      <c r="CP34" s="24" t="n"/>
+      <c r="CQ34" s="24" t="n"/>
+      <c r="CR34" s="24" t="n"/>
+      <c r="CS34" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>1a182660a149408e</t>
+        </is>
+      </c>
+      <c r="B35" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:21:35.145090Z</t>
+        </is>
+      </c>
+      <c r="C35" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D35" s="24" t="inlineStr">
+        <is>
+          <t>76186</t>
+        </is>
+      </c>
+      <c r="E35" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F35" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="G35" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="H35" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I35" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J35" s="25" t="n"/>
+      <c r="K35" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L35" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="M35" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="N35" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="O35" s="28" t="n">
+        <v>0.567846</v>
+      </c>
+      <c r="P35" s="28" t="n"/>
+      <c r="Q35" s="28" t="n">
+        <v>-0.102121</v>
+      </c>
+      <c r="R35" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T35" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U35" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V35" s="24" t="n"/>
+      <c r="W35" s="26" t="n"/>
+      <c r="X35" s="26" t="n"/>
+      <c r="Y35" s="25" t="n"/>
+      <c r="Z35" s="26" t="n"/>
+      <c r="AA35" s="28" t="n"/>
+      <c r="AB35" s="28" t="n"/>
+      <c r="AC35" s="30" t="n"/>
+      <c r="AD35" s="24" t="n"/>
+      <c r="AE35" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6700 (market_slug=aec-npb-nhf-ssl-2026-08-12). Tie probability=0.0303.</t>
+        </is>
+      </c>
+      <c r="AF35" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG35" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH35" s="24" t="n"/>
+      <c r="AI35" s="31" t="n"/>
+      <c r="AJ35" s="31" t="n"/>
+      <c r="AK35" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL35" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM35" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN35" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO35" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP35" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AQ35" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AR35" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AS35" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AT35" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AU35" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AV35" s="24" t="n"/>
+      <c r="AW35" s="24" t="n"/>
+      <c r="AX35" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY35" s="24" t="n"/>
+      <c r="AZ35" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA35" s="24" t="inlineStr">
+        <is>
+          <t>05ce5c163469a19fa69948e39f5a5c074f3e14d31fa465677897d80bd6c4e801</t>
+        </is>
+      </c>
+      <c r="BB35" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC35" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD35" s="24" t="inlineStr">
+        <is>
+          <t>05ce5c163469a19fa69948e39f5a5c074f3e14d31fa465677897d80bd6c4e801</t>
+        </is>
+      </c>
+      <c r="BE35" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF35" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG35" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH35" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:21:33.487442Z</t>
+        </is>
+      </c>
+      <c r="BI35" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ35" s="25" t="n"/>
+      <c r="BK35" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="BL35" s="27" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="BM35" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="BN35" s="28" t="n"/>
+      <c r="BO35" s="28" t="n"/>
+      <c r="BP35" s="25" t="n"/>
+      <c r="BQ35" s="27" t="n"/>
+      <c r="BR35" s="28" t="n"/>
+      <c r="BS35" s="28" t="n"/>
+      <c r="BT35" s="28" t="n"/>
+      <c r="BU35" s="25" t="n"/>
+      <c r="BV35" s="29" t="n"/>
+      <c r="BW35" s="24" t="n"/>
+      <c r="BX35" s="30" t="n"/>
+      <c r="BY35" s="27" t="n"/>
+      <c r="BZ35" s="24" t="n"/>
+      <c r="CA35" s="31" t="n"/>
+      <c r="CB35" s="24" t="n"/>
+      <c r="CC35" s="24" t="n"/>
+      <c r="CD35" s="24" t="n"/>
+      <c r="CE35" s="24" t="n"/>
+      <c r="CF35" s="24" t="n"/>
+      <c r="CG35" s="24" t="n"/>
+      <c r="CH35" s="24" t="n"/>
+      <c r="CI35" s="24" t="n"/>
+      <c r="CJ35" s="24" t="n"/>
+      <c r="CK35" s="24" t="n"/>
+      <c r="CL35" s="24" t="n"/>
+      <c r="CM35" s="24" t="n"/>
+      <c r="CN35" s="24" t="n"/>
+      <c r="CO35" s="24" t="n"/>
+      <c r="CP35" s="24" t="n"/>
+      <c r="CQ35" s="24" t="n"/>
+      <c r="CR35" s="24" t="n"/>
+      <c r="CS35" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>a9555c4be9244fb0</t>
+        </is>
+      </c>
+      <c r="B36" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:21:35.145090Z</t>
+        </is>
+      </c>
+      <c r="C36" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D36" s="24" t="inlineStr">
+        <is>
+          <t>76187</t>
+        </is>
+      </c>
+      <c r="E36" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F36" s="24" t="inlineStr">
+        <is>
+          <t>Orix Buffaloes</t>
+        </is>
+      </c>
+      <c r="G36" s="24" t="inlineStr">
+        <is>
+          <t>Tohoku Rakuten Golden Eagles</t>
+        </is>
+      </c>
+      <c r="H36" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I36" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J36" s="25" t="n"/>
+      <c r="K36" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L36" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="M36" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="N36" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="O36" s="28" t="n">
+        <v>0.514003</v>
+      </c>
+      <c r="P36" s="28" t="n"/>
+      <c r="Q36" s="28" t="n">
+        <v>-0.016513</v>
+      </c>
+      <c r="R36" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="S36" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U36" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V36" s="24" t="n"/>
+      <c r="W36" s="26" t="n"/>
+      <c r="X36" s="26" t="n"/>
+      <c r="Y36" s="25" t="n"/>
+      <c r="Z36" s="26" t="n"/>
+      <c r="AA36" s="28" t="n"/>
+      <c r="AB36" s="28" t="n"/>
+      <c r="AC36" s="30" t="n"/>
+      <c r="AD36" s="24" t="n"/>
+      <c r="AE36" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5300 (market_slug=aec-npb-trge-obr-2026-08-12). Tie probability=0.0349.</t>
+        </is>
+      </c>
+      <c r="AF36" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG36" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH36" s="24" t="n"/>
+      <c r="AI36" s="31" t="n"/>
+      <c r="AJ36" s="31" t="n"/>
+      <c r="AK36" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL36" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM36" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN36" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO36" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP36" s="24" t="inlineStr">
+        <is>
+          <t>Orix Buffaloes</t>
+        </is>
+      </c>
+      <c r="AQ36" s="24" t="inlineStr">
+        <is>
+          <t>Orix Buffaloes</t>
+        </is>
+      </c>
+      <c r="AR36" s="24" t="inlineStr">
+        <is>
+          <t>Orix Buffaloes</t>
+        </is>
+      </c>
+      <c r="AS36" s="24" t="inlineStr">
+        <is>
+          <t>Tohoku Rakuten Golden Eagles</t>
+        </is>
+      </c>
+      <c r="AT36" s="24" t="inlineStr">
+        <is>
+          <t>Tohoku Rakuten Golden Eagles</t>
+        </is>
+      </c>
+      <c r="AU36" s="24" t="inlineStr">
+        <is>
+          <t>Tohoku Rakuten Golden Eagles</t>
+        </is>
+      </c>
+      <c r="AV36" s="24" t="n"/>
+      <c r="AW36" s="24" t="n"/>
+      <c r="AX36" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY36" s="24" t="n"/>
+      <c r="AZ36" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA36" s="24" t="inlineStr">
+        <is>
+          <t>05ce5c163469a19fa69948e39f5a5c074f3e14d31fa465677897d80bd6c4e801</t>
+        </is>
+      </c>
+      <c r="BB36" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC36" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD36" s="24" t="inlineStr">
+        <is>
+          <t>05ce5c163469a19fa69948e39f5a5c074f3e14d31fa465677897d80bd6c4e801</t>
+        </is>
+      </c>
+      <c r="BE36" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF36" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG36" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH36" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:21:33.970591Z</t>
+        </is>
+      </c>
+      <c r="BI36" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ36" s="25" t="n"/>
+      <c r="BK36" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="BL36" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BM36" s="28" t="n">
+        <v>0.530516</v>
+      </c>
+      <c r="BN36" s="28" t="n"/>
+      <c r="BO36" s="28" t="n"/>
+      <c r="BP36" s="25" t="n"/>
+      <c r="BQ36" s="27" t="n"/>
+      <c r="BR36" s="28" t="n"/>
+      <c r="BS36" s="28" t="n"/>
+      <c r="BT36" s="28" t="n"/>
+      <c r="BU36" s="25" t="n"/>
+      <c r="BV36" s="29" t="n"/>
+      <c r="BW36" s="24" t="n"/>
+      <c r="BX36" s="30" t="n"/>
+      <c r="BY36" s="27" t="n"/>
+      <c r="BZ36" s="24" t="n"/>
+      <c r="CA36" s="31" t="n"/>
+      <c r="CB36" s="24" t="n"/>
+      <c r="CC36" s="24" t="n"/>
+      <c r="CD36" s="24" t="n"/>
+      <c r="CE36" s="24" t="n"/>
+      <c r="CF36" s="24" t="n"/>
+      <c r="CG36" s="24" t="n"/>
+      <c r="CH36" s="24" t="n"/>
+      <c r="CI36" s="24" t="n"/>
+      <c r="CJ36" s="24" t="n"/>
+      <c r="CK36" s="24" t="n"/>
+      <c r="CL36" s="24" t="n"/>
+      <c r="CM36" s="24" t="n"/>
+      <c r="CN36" s="24" t="n"/>
+      <c r="CO36" s="24" t="n"/>
+      <c r="CP36" s="24" t="n"/>
+      <c r="CQ36" s="24" t="n"/>
+      <c r="CR36" s="24" t="n"/>
+      <c r="CS36" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>22d15b195e984d0a</t>
+        </is>
+      </c>
+      <c r="B37" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:21:35.145090Z</t>
+        </is>
+      </c>
+      <c r="C37" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D37" s="24" t="inlineStr">
+        <is>
+          <t>76188</t>
+        </is>
+      </c>
+      <c r="E37" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F37" s="24" t="inlineStr">
+        <is>
+          <t>Chiba Lotte Marines</t>
+        </is>
+      </c>
+      <c r="G37" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="H37" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I37" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J37" s="25" t="n"/>
+      <c r="K37" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L37" s="26" t="n">
+        <v>-257</v>
+      </c>
+      <c r="M37" s="27" t="n">
+        <v>1.389105</v>
+      </c>
+      <c r="N37" s="28" t="n">
+        <v>0.719888</v>
+      </c>
+      <c r="O37" s="28" t="n">
+        <v>0.654962</v>
+      </c>
+      <c r="P37" s="28" t="n"/>
+      <c r="Q37" s="28" t="n">
+        <v>-0.064926</v>
+      </c>
+      <c r="R37" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T37" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U37" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V37" s="24" t="n"/>
+      <c r="W37" s="26" t="n"/>
+      <c r="X37" s="26" t="n"/>
+      <c r="Y37" s="25" t="n"/>
+      <c r="Z37" s="26" t="n"/>
+      <c r="AA37" s="28" t="n"/>
+      <c r="AB37" s="28" t="n"/>
+      <c r="AC37" s="30" t="n"/>
+      <c r="AD37" s="24" t="n"/>
+      <c r="AE37" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.7200 (market_slug=aec-npb-fsh-clm-2026-08-12). Tie probability=0.0224.</t>
+        </is>
+      </c>
+      <c r="AF37" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG37" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH37" s="24" t="n"/>
+      <c r="AI37" s="31" t="n"/>
+      <c r="AJ37" s="31" t="n"/>
+      <c r="AK37" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL37" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM37" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN37" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO37" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP37" s="24" t="inlineStr">
+        <is>
+          <t>Chiba Lotte Marines</t>
+        </is>
+      </c>
+      <c r="AQ37" s="24" t="inlineStr">
+        <is>
+          <t>Chiba Lotte Marines</t>
+        </is>
+      </c>
+      <c r="AR37" s="24" t="inlineStr">
+        <is>
+          <t>Chiba Lotte Marines</t>
+        </is>
+      </c>
+      <c r="AS37" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="AT37" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="AU37" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="AV37" s="24" t="n"/>
+      <c r="AW37" s="24" t="n"/>
+      <c r="AX37" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY37" s="24" t="n"/>
+      <c r="AZ37" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA37" s="24" t="inlineStr">
+        <is>
+          <t>05ce5c163469a19fa69948e39f5a5c074f3e14d31fa465677897d80bd6c4e801</t>
+        </is>
+      </c>
+      <c r="BB37" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC37" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD37" s="24" t="inlineStr">
+        <is>
+          <t>05ce5c163469a19fa69948e39f5a5c074f3e14d31fa465677897d80bd6c4e801</t>
+        </is>
+      </c>
+      <c r="BE37" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF37" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG37" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH37" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:21:34.674761Z</t>
+        </is>
+      </c>
+      <c r="BI37" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ37" s="25" t="n"/>
+      <c r="BK37" s="26" t="n">
+        <v>-257</v>
+      </c>
+      <c r="BL37" s="27" t="n">
+        <v>1.389105</v>
+      </c>
+      <c r="BM37" s="28" t="n">
+        <v>0.719888</v>
+      </c>
+      <c r="BN37" s="28" t="n"/>
+      <c r="BO37" s="28" t="n"/>
+      <c r="BP37" s="25" t="n"/>
+      <c r="BQ37" s="27" t="n"/>
+      <c r="BR37" s="28" t="n"/>
+      <c r="BS37" s="28" t="n"/>
+      <c r="BT37" s="28" t="n"/>
+      <c r="BU37" s="25" t="n"/>
+      <c r="BV37" s="29" t="n"/>
+      <c r="BW37" s="24" t="n"/>
+      <c r="BX37" s="30" t="n"/>
+      <c r="BY37" s="27" t="n"/>
+      <c r="BZ37" s="24" t="n"/>
+      <c r="CA37" s="31" t="n"/>
+      <c r="CB37" s="24" t="n"/>
+      <c r="CC37" s="24" t="n"/>
+      <c r="CD37" s="24" t="n"/>
+      <c r="CE37" s="24" t="n"/>
+      <c r="CF37" s="24" t="n"/>
+      <c r="CG37" s="24" t="n"/>
+      <c r="CH37" s="24" t="n"/>
+      <c r="CI37" s="24" t="n"/>
+      <c r="CJ37" s="24" t="n"/>
+      <c r="CK37" s="24" t="n"/>
+      <c r="CL37" s="24" t="n"/>
+      <c r="CM37" s="24" t="n"/>
+      <c r="CN37" s="24" t="n"/>
+      <c r="CO37" s="24" t="n"/>
+      <c r="CP37" s="24" t="n"/>
+      <c r="CQ37" s="24" t="n"/>
+      <c r="CR37" s="24" t="n"/>
+      <c r="CS37" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="24" t="inlineStr">
+        <is>
+          <t>a2967370bb244f6f</t>
+        </is>
+      </c>
+      <c r="B38" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:21:35.145090Z</t>
+        </is>
+      </c>
+      <c r="C38" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D38" s="24" t="inlineStr">
+        <is>
+          <t>76189</t>
+        </is>
+      </c>
+      <c r="E38" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F38" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="G38" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="H38" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I38" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J38" s="25" t="n"/>
+      <c r="K38" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L38" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="M38" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="N38" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="O38" s="28" t="n">
+        <v>0.516541</v>
+      </c>
+      <c r="P38" s="28" t="n"/>
+      <c r="Q38" s="28" t="n">
+        <v>-0.04293</v>
+      </c>
+      <c r="R38" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U38" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V38" s="24" t="n"/>
+      <c r="W38" s="26" t="n"/>
+      <c r="X38" s="26" t="n"/>
+      <c r="Y38" s="25" t="n"/>
+      <c r="Z38" s="26" t="n"/>
+      <c r="AA38" s="28" t="n"/>
+      <c r="AB38" s="28" t="n"/>
+      <c r="AC38" s="30" t="n"/>
+      <c r="AD38" s="24" t="n"/>
+      <c r="AE38" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5600 (market_slug=aec-npb-tys-hci-2026-08-12). Tie probability=0.0347.</t>
+        </is>
+      </c>
+      <c r="AF38" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG38" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH38" s="24" t="n"/>
+      <c r="AI38" s="31" t="n"/>
+      <c r="AJ38" s="31" t="n"/>
+      <c r="AK38" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL38" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM38" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN38" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO38" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP38" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="AQ38" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="AR38" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="AS38" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AT38" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AU38" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AV38" s="24" t="n"/>
+      <c r="AW38" s="24" t="n"/>
+      <c r="AX38" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY38" s="24" t="n"/>
+      <c r="AZ38" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA38" s="24" t="inlineStr">
+        <is>
+          <t>05ce5c163469a19fa69948e39f5a5c074f3e14d31fa465677897d80bd6c4e801</t>
+        </is>
+      </c>
+      <c r="BB38" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC38" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD38" s="24" t="inlineStr">
+        <is>
+          <t>05ce5c163469a19fa69948e39f5a5c074f3e14d31fa465677897d80bd6c4e801</t>
+        </is>
+      </c>
+      <c r="BE38" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF38" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG38" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH38" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:21:35.145050Z</t>
+        </is>
+      </c>
+      <c r="BI38" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ38" s="25" t="n"/>
+      <c r="BK38" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="BL38" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BM38" s="28" t="n">
+        <v>0.5594710000000001</v>
+      </c>
+      <c r="BN38" s="28" t="n"/>
+      <c r="BO38" s="28" t="n"/>
+      <c r="BP38" s="25" t="n"/>
+      <c r="BQ38" s="27" t="n"/>
+      <c r="BR38" s="28" t="n"/>
+      <c r="BS38" s="28" t="n"/>
+      <c r="BT38" s="28" t="n"/>
+      <c r="BU38" s="25" t="n"/>
+      <c r="BV38" s="29" t="n"/>
+      <c r="BW38" s="24" t="n"/>
+      <c r="BX38" s="30" t="n"/>
+      <c r="BY38" s="27" t="n"/>
+      <c r="BZ38" s="24" t="n"/>
+      <c r="CA38" s="31" t="n"/>
+      <c r="CB38" s="24" t="n"/>
+      <c r="CC38" s="24" t="n"/>
+      <c r="CD38" s="24" t="n"/>
+      <c r="CE38" s="24" t="n"/>
+      <c r="CF38" s="24" t="n"/>
+      <c r="CG38" s="24" t="n"/>
+      <c r="CH38" s="24" t="n"/>
+      <c r="CI38" s="24" t="n"/>
+      <c r="CJ38" s="24" t="n"/>
+      <c r="CK38" s="24" t="n"/>
+      <c r="CL38" s="24" t="n"/>
+      <c r="CM38" s="24" t="n"/>
+      <c r="CN38" s="24" t="n"/>
+      <c r="CO38" s="24" t="n"/>
+      <c r="CP38" s="24" t="n"/>
+      <c r="CQ38" s="24" t="n"/>
+      <c r="CR38" s="24" t="n"/>
+      <c r="CS38" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/research/npb.xlsx
+++ b/data/research/npb.xlsx
@@ -21,10 +21,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.0###"/>
-    <numFmt numFmtId="165" formatCode="0.000000"/>
-    <numFmt numFmtId="166" formatCode="0.0000"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.0###"/>
+    <numFmt numFmtId="167" formatCode="0.000000"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -136,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -150,10 +150,10 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -169,10 +169,10 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -184,10 +184,10 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -202,13 +202,13 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="10" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -217,11 +217,38 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -300,8 +327,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS38" headerRowCount="1">
-  <autoFilter ref="A1:CS38"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS44" headerRowCount="1">
+  <autoFilter ref="A1:CS44"/>
   <tableColumns count="97">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -756,19 +783,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$38)</f>
+        <f>COUNTA('Picks'!$A$2:$A$44)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$38,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$44,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$38,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$44,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"win")+COUNTIFS('Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$44,"settled",'Picks'!$V$2:$V$44,"win")+COUNTIFS('Picks'!$U$2:$U$44,"settled",'Picks'!$V$2:$V$44,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -796,19 +823,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$38,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$44,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$38,"&gt;0",'Picks'!$V$2:$V$38,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$38,"&gt;0",'Picks'!$V$2:$V$38,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$44,"&gt;0",'Picks'!$V$2:$V$44,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$44,"&gt;0",'Picks'!$V$2:$V$44,"loss")</f>
         <v/>
       </c>
-      <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$38,"&gt;0",'Picks'!$V$2:$V$38,"win")/(COUNTIFS('Picks'!$BX$2:$BX$38,"&gt;0",'Picks'!$V$2:$V$38,"win")+COUNTIFS('Picks'!$BX$2:$BX$38,"&gt;0",'Picks'!$V$2:$V$38,"loss")),0)</f>
+      <c r="E7" s="32">
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$44,"&gt;0",'Picks'!$V$2:$V$44,"win")/(COUNTIFS('Picks'!$BX$2:$BX$44,"&gt;0",'Picks'!$V$2:$V$44,"win")+COUNTIFS('Picks'!$BX$2:$BX$44,"&gt;0",'Picks'!$V$2:$V$44,"loss")),0)</f>
         <v/>
       </c>
-      <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$38)/SUM('Picks'!$BX$2:$BX$38),0)</f>
+      <c r="G7" s="32">
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$44)/SUM('Picks'!$BX$2:$BX$44),0)</f>
         <v/>
       </c>
     </row>
@@ -835,20 +862,20 @@
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$38)</f>
+      <c r="A10" s="33">
+        <f>SUM('Picks'!$BY$2:$BY$44)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$38,"&lt;&gt;",'Picks'!$AB$2:$AB$38),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$44,"&lt;&gt;",'Picks'!$AB$2:$AB$44),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$38,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$38,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$44,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$44,"settled")</f>
         <v/>
       </c>
-      <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$38,'Picks'!$AM$2:$AM$38,"QUALIFIED_SHADOW_CALL")</f>
+      <c r="G10" s="33">
+        <f>SUMIFS('Picks'!$AC$2:$AC$44,'Picks'!$AM$2:$AM$44,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -903,27 +930,27 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$38,$A14,'Picks'!$U$2:$U$38,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$44,$A14,'Picks'!$U$2:$U$44,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$38,$A14,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$44,$A14,'Picks'!$U$2:$U$44,"settled",'Picks'!$V$2:$V$44,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$38,$A14,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$44,$A14,'Picks'!$U$2:$U$44,"settled",'Picks'!$V$2:$V$44,"loss")</f>
         <v/>
       </c>
-      <c r="E14" s="14">
+      <c r="E14" s="34">
         <f>IFERROR(C14/(C14+D14),0)</f>
         <v/>
       </c>
-      <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$38,'Picks'!$H$2:$H$38,$A14)</f>
+      <c r="F14" s="35">
+        <f>SUMIFS('Picks'!$BY$2:$BY$44,'Picks'!$H$2:$H$44,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$38,'Picks'!$H$2:$H$38,$A14,'Picks'!$U$2:$U$38,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$44,'Picks'!$H$2:$H$44,$A14,'Picks'!$U$2:$U$44,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -934,27 +961,27 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$38,$A15,'Picks'!$U$2:$U$38,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$44,$A15,'Picks'!$U$2:$U$44,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$38,$A15,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$44,$A15,'Picks'!$U$2:$U$44,"settled",'Picks'!$V$2:$V$44,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$38,$A15,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$44,$A15,'Picks'!$U$2:$U$44,"settled",'Picks'!$V$2:$V$44,"loss")</f>
         <v/>
       </c>
-      <c r="E15" s="19">
+      <c r="E15" s="36">
         <f>IFERROR(C15/(C15+D15),0)</f>
         <v/>
       </c>
-      <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$38,'Picks'!$H$2:$H$38,$A15)</f>
+      <c r="F15" s="37">
+        <f>SUMIFS('Picks'!$BY$2:$BY$44,'Picks'!$H$2:$H$44,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$38,'Picks'!$H$2:$H$38,$A15,'Picks'!$U$2:$U$38,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$44,'Picks'!$H$2:$H$44,$A15,'Picks'!$U$2:$U$44,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -965,27 +992,27 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$38,$A16,'Picks'!$U$2:$U$38,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$44,$A16,'Picks'!$U$2:$U$44,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$38,$A16,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$44,$A16,'Picks'!$U$2:$U$44,"settled",'Picks'!$V$2:$V$44,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$38,$A16,'Picks'!$U$2:$U$38,"settled",'Picks'!$V$2:$V$38,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$44,$A16,'Picks'!$U$2:$U$44,"settled",'Picks'!$V$2:$V$44,"loss")</f>
         <v/>
       </c>
-      <c r="E16" s="14">
+      <c r="E16" s="34">
         <f>IFERROR(C16/(C16+D16),0)</f>
         <v/>
       </c>
-      <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$38,'Picks'!$H$2:$H$38,$A16)</f>
+      <c r="F16" s="35">
+        <f>SUMIFS('Picks'!$BY$2:$BY$44,'Picks'!$H$2:$H$44,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$38,'Picks'!$H$2:$H$38,$A16,'Picks'!$U$2:$U$38,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$44,'Picks'!$H$2:$H$44,$A16,'Picks'!$U$2:$U$44,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1014,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS38"/>
+  <dimension ref="A1:CS44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1649,7 +1676,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J2" s="25" t="n"/>
+      <c r="J2" s="38" t="n"/>
       <c r="K2" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -1658,7 +1685,7 @@
       <c r="L2" s="26" t="n">
         <v>-156</v>
       </c>
-      <c r="M2" s="27" t="n">
+      <c r="M2" s="39" t="n">
         <v>1.641026</v>
       </c>
       <c r="N2" s="28" t="n">
@@ -1698,11 +1725,11 @@
       <c r="X2" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="Y2" s="25" t="n"/>
+      <c r="Y2" s="38" t="n"/>
       <c r="Z2" s="26" t="n"/>
       <c r="AA2" s="28" t="n"/>
       <c r="AB2" s="28" t="n"/>
-      <c r="AC2" s="30" t="n">
+      <c r="AC2" s="40" t="n">
         <v>0.8013</v>
       </c>
       <c r="AD2" s="24" t="inlineStr">
@@ -1839,11 +1866,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ2" s="25" t="n"/>
+      <c r="BJ2" s="38" t="n"/>
       <c r="BK2" s="26" t="n">
         <v>-156</v>
       </c>
-      <c r="BL2" s="27" t="n">
+      <c r="BL2" s="39" t="n">
         <v>1.641026</v>
       </c>
       <c r="BM2" s="28" t="n">
@@ -1851,18 +1878,18 @@
       </c>
       <c r="BN2" s="28" t="n"/>
       <c r="BO2" s="28" t="n"/>
-      <c r="BP2" s="25" t="n"/>
-      <c r="BQ2" s="27" t="n"/>
+      <c r="BP2" s="38" t="n"/>
+      <c r="BQ2" s="39" t="n"/>
       <c r="BR2" s="28" t="n"/>
       <c r="BS2" s="28" t="n"/>
       <c r="BT2" s="28" t="n"/>
-      <c r="BU2" s="25" t="n"/>
+      <c r="BU2" s="38" t="n"/>
       <c r="BV2" s="29" t="n"/>
       <c r="BW2" s="24" t="n"/>
-      <c r="BX2" s="30" t="n">
+      <c r="BX2" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY2" s="27" t="n">
+      <c r="BY2" s="39" t="n">
         <v>0.91</v>
       </c>
       <c r="BZ2" s="24" t="n"/>
@@ -1932,7 +1959,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J3" s="25" t="n"/>
+      <c r="J3" s="38" t="n"/>
       <c r="K3" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -1941,7 +1968,7 @@
       <c r="L3" s="26" t="n">
         <v>-156</v>
       </c>
-      <c r="M3" s="27" t="n">
+      <c r="M3" s="39" t="n">
         <v>1.641026</v>
       </c>
       <c r="N3" s="28" t="n">
@@ -1981,11 +2008,11 @@
       <c r="X3" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="Y3" s="25" t="n"/>
+      <c r="Y3" s="38" t="n"/>
       <c r="Z3" s="26" t="n"/>
       <c r="AA3" s="28" t="n"/>
       <c r="AB3" s="28" t="n"/>
-      <c r="AC3" s="30" t="n">
+      <c r="AC3" s="40" t="n">
         <v>0.8013</v>
       </c>
       <c r="AD3" s="24" t="inlineStr">
@@ -2122,11 +2149,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ3" s="25" t="n"/>
+      <c r="BJ3" s="38" t="n"/>
       <c r="BK3" s="26" t="n">
         <v>-156</v>
       </c>
-      <c r="BL3" s="27" t="n">
+      <c r="BL3" s="39" t="n">
         <v>1.641026</v>
       </c>
       <c r="BM3" s="28" t="n">
@@ -2134,18 +2161,18 @@
       </c>
       <c r="BN3" s="28" t="n"/>
       <c r="BO3" s="28" t="n"/>
-      <c r="BP3" s="25" t="n"/>
-      <c r="BQ3" s="27" t="n"/>
+      <c r="BP3" s="38" t="n"/>
+      <c r="BQ3" s="39" t="n"/>
       <c r="BR3" s="28" t="n"/>
       <c r="BS3" s="28" t="n"/>
       <c r="BT3" s="28" t="n"/>
-      <c r="BU3" s="25" t="n"/>
+      <c r="BU3" s="38" t="n"/>
       <c r="BV3" s="29" t="n"/>
       <c r="BW3" s="24" t="n"/>
-      <c r="BX3" s="30" t="n">
+      <c r="BX3" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY3" s="27" t="n">
+      <c r="BY3" s="39" t="n">
         <v>0.91</v>
       </c>
       <c r="BZ3" s="24" t="n"/>
@@ -2215,7 +2242,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J4" s="25" t="n"/>
+      <c r="J4" s="38" t="n"/>
       <c r="K4" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2224,7 +2251,7 @@
       <c r="L4" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="M4" s="27" t="n">
+      <c r="M4" s="39" t="n">
         <v>1.925926</v>
       </c>
       <c r="N4" s="28" t="n">
@@ -2264,11 +2291,11 @@
       <c r="X4" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y4" s="25" t="n"/>
+      <c r="Y4" s="38" t="n"/>
       <c r="Z4" s="26" t="n"/>
       <c r="AA4" s="28" t="n"/>
       <c r="AB4" s="28" t="n"/>
-      <c r="AC4" s="30" t="n">
+      <c r="AC4" s="40" t="n">
         <v>0.9258999999999999</v>
       </c>
       <c r="AD4" s="24" t="inlineStr">
@@ -2405,11 +2432,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ4" s="25" t="n"/>
+      <c r="BJ4" s="38" t="n"/>
       <c r="BK4" s="26" t="n">
         <v>-108</v>
       </c>
-      <c r="BL4" s="27" t="n">
+      <c r="BL4" s="39" t="n">
         <v>1.925926</v>
       </c>
       <c r="BM4" s="28" t="n">
@@ -2417,18 +2444,18 @@
       </c>
       <c r="BN4" s="28" t="n"/>
       <c r="BO4" s="28" t="n"/>
-      <c r="BP4" s="25" t="n"/>
-      <c r="BQ4" s="27" t="n"/>
+      <c r="BP4" s="38" t="n"/>
+      <c r="BQ4" s="39" t="n"/>
       <c r="BR4" s="28" t="n"/>
       <c r="BS4" s="28" t="n"/>
       <c r="BT4" s="28" t="n"/>
-      <c r="BU4" s="25" t="n"/>
+      <c r="BU4" s="38" t="n"/>
       <c r="BV4" s="29" t="n"/>
       <c r="BW4" s="24" t="n"/>
-      <c r="BX4" s="30" t="n">
+      <c r="BX4" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY4" s="27" t="n">
+      <c r="BY4" s="39" t="n">
         <v>0.91</v>
       </c>
       <c r="BZ4" s="24" t="n"/>
@@ -2498,7 +2525,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J5" s="25" t="n"/>
+      <c r="J5" s="38" t="n"/>
       <c r="K5" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2507,7 +2534,7 @@
       <c r="L5" s="26" t="n">
         <v>-122</v>
       </c>
-      <c r="M5" s="27" t="n">
+      <c r="M5" s="39" t="n">
         <v>1.819672</v>
       </c>
       <c r="N5" s="28" t="n">
@@ -2547,11 +2574,11 @@
       <c r="X5" s="26" t="n">
         <v>9</v>
       </c>
-      <c r="Y5" s="25" t="n"/>
+      <c r="Y5" s="38" t="n"/>
       <c r="Z5" s="26" t="n"/>
       <c r="AA5" s="28" t="n"/>
       <c r="AB5" s="28" t="n"/>
-      <c r="AC5" s="30" t="n">
+      <c r="AC5" s="40" t="n">
         <v>0.8197</v>
       </c>
       <c r="AD5" s="24" t="inlineStr">
@@ -2688,11 +2715,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ5" s="25" t="n"/>
+      <c r="BJ5" s="38" t="n"/>
       <c r="BK5" s="26" t="n">
         <v>-122</v>
       </c>
-      <c r="BL5" s="27" t="n">
+      <c r="BL5" s="39" t="n">
         <v>1.819672</v>
       </c>
       <c r="BM5" s="28" t="n">
@@ -2700,18 +2727,18 @@
       </c>
       <c r="BN5" s="28" t="n"/>
       <c r="BO5" s="28" t="n"/>
-      <c r="BP5" s="25" t="n"/>
-      <c r="BQ5" s="27" t="n"/>
+      <c r="BP5" s="38" t="n"/>
+      <c r="BQ5" s="39" t="n"/>
       <c r="BR5" s="28" t="n"/>
       <c r="BS5" s="28" t="n"/>
       <c r="BT5" s="28" t="n"/>
-      <c r="BU5" s="25" t="n"/>
+      <c r="BU5" s="38" t="n"/>
       <c r="BV5" s="29" t="n"/>
       <c r="BW5" s="24" t="n"/>
-      <c r="BX5" s="30" t="n">
+      <c r="BX5" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY5" s="27" t="n">
+      <c r="BY5" s="39" t="n">
         <v>0.91</v>
       </c>
       <c r="BZ5" s="24" t="n"/>
@@ -2785,7 +2812,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J6" s="25" t="n"/>
+      <c r="J6" s="38" t="n"/>
       <c r="K6" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -2794,7 +2821,7 @@
       <c r="L6" s="26" t="n">
         <v>-163</v>
       </c>
-      <c r="M6" s="27" t="n">
+      <c r="M6" s="39" t="n">
         <v>1.613497</v>
       </c>
       <c r="N6" s="28" t="n">
@@ -2834,11 +2861,11 @@
       <c r="X6" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y6" s="25" t="n"/>
+      <c r="Y6" s="38" t="n"/>
       <c r="Z6" s="26" t="n"/>
       <c r="AA6" s="28" t="n"/>
       <c r="AB6" s="28" t="n"/>
-      <c r="AC6" s="30" t="n">
+      <c r="AC6" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD6" s="24" t="inlineStr">
@@ -2975,11 +3002,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ6" s="25" t="n"/>
+      <c r="BJ6" s="38" t="n"/>
       <c r="BK6" s="26" t="n">
         <v>-163</v>
       </c>
-      <c r="BL6" s="27" t="n">
+      <c r="BL6" s="39" t="n">
         <v>1.613497</v>
       </c>
       <c r="BM6" s="28" t="n">
@@ -2987,18 +3014,18 @@
       </c>
       <c r="BN6" s="28" t="n"/>
       <c r="BO6" s="28" t="n"/>
-      <c r="BP6" s="25" t="n"/>
-      <c r="BQ6" s="27" t="n"/>
+      <c r="BP6" s="38" t="n"/>
+      <c r="BQ6" s="39" t="n"/>
       <c r="BR6" s="28" t="n"/>
       <c r="BS6" s="28" t="n"/>
       <c r="BT6" s="28" t="n"/>
-      <c r="BU6" s="25" t="n"/>
+      <c r="BU6" s="38" t="n"/>
       <c r="BV6" s="29" t="n"/>
       <c r="BW6" s="24" t="n"/>
-      <c r="BX6" s="30" t="n">
+      <c r="BX6" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY6" s="27" t="n">
+      <c r="BY6" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ6" s="24" t="n"/>
@@ -3072,7 +3099,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J7" s="25" t="n"/>
+      <c r="J7" s="38" t="n"/>
       <c r="K7" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3081,7 +3108,7 @@
       <c r="L7" s="26" t="n">
         <v>-194</v>
       </c>
-      <c r="M7" s="27" t="n">
+      <c r="M7" s="39" t="n">
         <v>1.515464</v>
       </c>
       <c r="N7" s="28" t="n">
@@ -3121,11 +3148,11 @@
       <c r="X7" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y7" s="25" t="n"/>
+      <c r="Y7" s="38" t="n"/>
       <c r="Z7" s="26" t="n"/>
       <c r="AA7" s="28" t="n"/>
       <c r="AB7" s="28" t="n"/>
-      <c r="AC7" s="30" t="n">
+      <c r="AC7" s="40" t="n">
         <v>0.6443</v>
       </c>
       <c r="AD7" s="24" t="inlineStr">
@@ -3262,11 +3289,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ7" s="25" t="n"/>
+      <c r="BJ7" s="38" t="n"/>
       <c r="BK7" s="26" t="n">
         <v>-194</v>
       </c>
-      <c r="BL7" s="27" t="n">
+      <c r="BL7" s="39" t="n">
         <v>1.515464</v>
       </c>
       <c r="BM7" s="28" t="n">
@@ -3274,18 +3301,18 @@
       </c>
       <c r="BN7" s="28" t="n"/>
       <c r="BO7" s="28" t="n"/>
-      <c r="BP7" s="25" t="n"/>
-      <c r="BQ7" s="27" t="n"/>
+      <c r="BP7" s="38" t="n"/>
+      <c r="BQ7" s="39" t="n"/>
       <c r="BR7" s="28" t="n"/>
       <c r="BS7" s="28" t="n"/>
       <c r="BT7" s="28" t="n"/>
-      <c r="BU7" s="25" t="n"/>
+      <c r="BU7" s="38" t="n"/>
       <c r="BV7" s="29" t="n"/>
       <c r="BW7" s="24" t="n"/>
-      <c r="BX7" s="30" t="n">
+      <c r="BX7" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY7" s="27" t="n">
+      <c r="BY7" s="39" t="n">
         <v>0.91</v>
       </c>
       <c r="BZ7" s="24" t="n"/>
@@ -3359,7 +3386,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J8" s="25" t="n"/>
+      <c r="J8" s="38" t="n"/>
       <c r="K8" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3368,7 +3395,7 @@
       <c r="L8" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="M8" s="27" t="n">
+      <c r="M8" s="39" t="n">
         <v>2.08</v>
       </c>
       <c r="N8" s="28" t="n">
@@ -3408,11 +3435,11 @@
       <c r="X8" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y8" s="25" t="n"/>
+      <c r="Y8" s="38" t="n"/>
       <c r="Z8" s="26" t="n"/>
       <c r="AA8" s="28" t="n"/>
       <c r="AB8" s="28" t="n"/>
-      <c r="AC8" s="30" t="n">
+      <c r="AC8" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD8" s="24" t="inlineStr">
@@ -3549,11 +3576,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ8" s="25" t="n"/>
+      <c r="BJ8" s="38" t="n"/>
       <c r="BK8" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="BL8" s="27" t="n">
+      <c r="BL8" s="39" t="n">
         <v>2.08</v>
       </c>
       <c r="BM8" s="28" t="n">
@@ -3561,18 +3588,18 @@
       </c>
       <c r="BN8" s="28" t="n"/>
       <c r="BO8" s="28" t="n"/>
-      <c r="BP8" s="25" t="n"/>
-      <c r="BQ8" s="27" t="n"/>
+      <c r="BP8" s="38" t="n"/>
+      <c r="BQ8" s="39" t="n"/>
       <c r="BR8" s="28" t="n"/>
       <c r="BS8" s="28" t="n"/>
       <c r="BT8" s="28" t="n"/>
-      <c r="BU8" s="25" t="n"/>
+      <c r="BU8" s="38" t="n"/>
       <c r="BV8" s="29" t="n"/>
       <c r="BW8" s="24" t="n"/>
-      <c r="BX8" s="30" t="n">
+      <c r="BX8" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY8" s="27" t="n">
+      <c r="BY8" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ8" s="24" t="n"/>
@@ -3646,7 +3673,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J9" s="25" t="n"/>
+      <c r="J9" s="38" t="n"/>
       <c r="K9" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3655,7 +3682,7 @@
       <c r="L9" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="M9" s="27" t="n">
+      <c r="M9" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="N9" s="28" t="n">
@@ -3695,11 +3722,11 @@
       <c r="X9" s="26" t="n">
         <v>5</v>
       </c>
-      <c r="Y9" s="25" t="n"/>
+      <c r="Y9" s="38" t="n"/>
       <c r="Z9" s="26" t="n"/>
       <c r="AA9" s="28" t="n"/>
       <c r="AB9" s="28" t="n"/>
-      <c r="AC9" s="30" t="n">
+      <c r="AC9" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD9" s="24" t="inlineStr">
@@ -3836,11 +3863,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ9" s="25" t="n"/>
+      <c r="BJ9" s="38" t="n"/>
       <c r="BK9" s="26" t="n">
         <v>-133</v>
       </c>
-      <c r="BL9" s="27" t="n">
+      <c r="BL9" s="39" t="n">
         <v>1.75188</v>
       </c>
       <c r="BM9" s="28" t="n">
@@ -3848,18 +3875,18 @@
       </c>
       <c r="BN9" s="28" t="n"/>
       <c r="BO9" s="28" t="n"/>
-      <c r="BP9" s="25" t="n"/>
-      <c r="BQ9" s="27" t="n"/>
+      <c r="BP9" s="38" t="n"/>
+      <c r="BQ9" s="39" t="n"/>
       <c r="BR9" s="28" t="n"/>
       <c r="BS9" s="28" t="n"/>
       <c r="BT9" s="28" t="n"/>
-      <c r="BU9" s="25" t="n"/>
+      <c r="BU9" s="38" t="n"/>
       <c r="BV9" s="29" t="n"/>
       <c r="BW9" s="24" t="n"/>
-      <c r="BX9" s="30" t="n">
+      <c r="BX9" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY9" s="27" t="n">
+      <c r="BY9" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ9" s="24" t="n"/>
@@ -3933,7 +3960,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J10" s="25" t="n"/>
+      <c r="J10" s="38" t="n"/>
       <c r="K10" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -3942,7 +3969,7 @@
       <c r="L10" s="26" t="n">
         <v>-156</v>
       </c>
-      <c r="M10" s="27" t="n">
+      <c r="M10" s="39" t="n">
         <v>1.641026</v>
       </c>
       <c r="N10" s="28" t="n">
@@ -3982,11 +4009,11 @@
       <c r="X10" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y10" s="25" t="n"/>
+      <c r="Y10" s="38" t="n"/>
       <c r="Z10" s="26" t="n"/>
       <c r="AA10" s="28" t="n"/>
       <c r="AB10" s="28" t="n"/>
-      <c r="AC10" s="30" t="n">
+      <c r="AC10" s="40" t="n">
         <v>0.8013</v>
       </c>
       <c r="AD10" s="24" t="inlineStr">
@@ -4123,11 +4150,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ10" s="25" t="n"/>
+      <c r="BJ10" s="38" t="n"/>
       <c r="BK10" s="26" t="n">
         <v>-156</v>
       </c>
-      <c r="BL10" s="27" t="n">
+      <c r="BL10" s="39" t="n">
         <v>1.641026</v>
       </c>
       <c r="BM10" s="28" t="n">
@@ -4135,18 +4162,18 @@
       </c>
       <c r="BN10" s="28" t="n"/>
       <c r="BO10" s="28" t="n"/>
-      <c r="BP10" s="25" t="n"/>
-      <c r="BQ10" s="27" t="n"/>
+      <c r="BP10" s="38" t="n"/>
+      <c r="BQ10" s="39" t="n"/>
       <c r="BR10" s="28" t="n"/>
       <c r="BS10" s="28" t="n"/>
       <c r="BT10" s="28" t="n"/>
-      <c r="BU10" s="25" t="n"/>
+      <c r="BU10" s="38" t="n"/>
       <c r="BV10" s="29" t="n"/>
       <c r="BW10" s="24" t="n"/>
-      <c r="BX10" s="30" t="n">
+      <c r="BX10" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY10" s="27" t="n">
+      <c r="BY10" s="39" t="n">
         <v>0.91</v>
       </c>
       <c r="BZ10" s="24" t="n"/>
@@ -4220,7 +4247,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J11" s="25" t="n"/>
+      <c r="J11" s="38" t="n"/>
       <c r="K11" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4229,7 +4256,7 @@
       <c r="L11" s="26" t="n">
         <v>-150</v>
       </c>
-      <c r="M11" s="27" t="n">
+      <c r="M11" s="39" t="n">
         <v>1.666667</v>
       </c>
       <c r="N11" s="28" t="n">
@@ -4269,11 +4296,11 @@
       <c r="X11" s="26" t="n">
         <v>11</v>
       </c>
-      <c r="Y11" s="25" t="n"/>
+      <c r="Y11" s="38" t="n"/>
       <c r="Z11" s="26" t="n"/>
       <c r="AA11" s="28" t="n"/>
       <c r="AB11" s="28" t="n"/>
-      <c r="AC11" s="30" t="n">
+      <c r="AC11" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD11" s="24" t="inlineStr">
@@ -4410,11 +4437,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ11" s="25" t="n"/>
+      <c r="BJ11" s="38" t="n"/>
       <c r="BK11" s="26" t="n">
         <v>-150</v>
       </c>
-      <c r="BL11" s="27" t="n">
+      <c r="BL11" s="39" t="n">
         <v>1.666667</v>
       </c>
       <c r="BM11" s="28" t="n">
@@ -4422,18 +4449,18 @@
       </c>
       <c r="BN11" s="28" t="n"/>
       <c r="BO11" s="28" t="n"/>
-      <c r="BP11" s="25" t="n"/>
-      <c r="BQ11" s="27" t="n"/>
+      <c r="BP11" s="38" t="n"/>
+      <c r="BQ11" s="39" t="n"/>
       <c r="BR11" s="28" t="n"/>
       <c r="BS11" s="28" t="n"/>
       <c r="BT11" s="28" t="n"/>
-      <c r="BU11" s="25" t="n"/>
+      <c r="BU11" s="38" t="n"/>
       <c r="BV11" s="29" t="n"/>
       <c r="BW11" s="24" t="n"/>
-      <c r="BX11" s="30" t="n">
+      <c r="BX11" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY11" s="27" t="n">
+      <c r="BY11" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ11" s="24" t="n"/>
@@ -4507,7 +4534,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J12" s="25" t="n"/>
+      <c r="J12" s="38" t="n"/>
       <c r="K12" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4516,7 +4543,7 @@
       <c r="L12" s="26" t="n">
         <v>-122</v>
       </c>
-      <c r="M12" s="27" t="n">
+      <c r="M12" s="39" t="n">
         <v>1.819672</v>
       </c>
       <c r="N12" s="28" t="n">
@@ -4556,11 +4583,11 @@
       <c r="X12" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y12" s="25" t="n"/>
+      <c r="Y12" s="38" t="n"/>
       <c r="Z12" s="26" t="n"/>
       <c r="AA12" s="28" t="n"/>
       <c r="AB12" s="28" t="n"/>
-      <c r="AC12" s="30" t="n">
+      <c r="AC12" s="40" t="n">
         <v>1.0246</v>
       </c>
       <c r="AD12" s="24" t="inlineStr">
@@ -4697,11 +4724,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ12" s="25" t="n"/>
+      <c r="BJ12" s="38" t="n"/>
       <c r="BK12" s="26" t="n">
         <v>-122</v>
       </c>
-      <c r="BL12" s="27" t="n">
+      <c r="BL12" s="39" t="n">
         <v>1.819672</v>
       </c>
       <c r="BM12" s="28" t="n">
@@ -4709,18 +4736,18 @@
       </c>
       <c r="BN12" s="28" t="n"/>
       <c r="BO12" s="28" t="n"/>
-      <c r="BP12" s="25" t="n"/>
-      <c r="BQ12" s="27" t="n"/>
+      <c r="BP12" s="38" t="n"/>
+      <c r="BQ12" s="39" t="n"/>
       <c r="BR12" s="28" t="n"/>
       <c r="BS12" s="28" t="n"/>
       <c r="BT12" s="28" t="n"/>
-      <c r="BU12" s="25" t="n"/>
+      <c r="BU12" s="38" t="n"/>
       <c r="BV12" s="29" t="n"/>
       <c r="BW12" s="24" t="n"/>
-      <c r="BX12" s="30" t="n">
+      <c r="BX12" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY12" s="27" t="n">
+      <c r="BY12" s="39" t="n">
         <v>0.91</v>
       </c>
       <c r="BZ12" s="24" t="n"/>
@@ -4794,7 +4821,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J13" s="25" t="n"/>
+      <c r="J13" s="38" t="n"/>
       <c r="K13" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -4803,7 +4830,7 @@
       <c r="L13" s="26" t="n">
         <v>-113</v>
       </c>
-      <c r="M13" s="27" t="n">
+      <c r="M13" s="39" t="n">
         <v>1.884956</v>
       </c>
       <c r="N13" s="28" t="n">
@@ -4843,11 +4870,11 @@
       <c r="X13" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="Y13" s="25" t="n"/>
+      <c r="Y13" s="38" t="n"/>
       <c r="Z13" s="26" t="n"/>
       <c r="AA13" s="28" t="n"/>
       <c r="AB13" s="28" t="n"/>
-      <c r="AC13" s="30" t="n">
+      <c r="AC13" s="40" t="n">
         <v>-1</v>
       </c>
       <c r="AD13" s="24" t="inlineStr">
@@ -4984,11 +5011,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ13" s="25" t="n"/>
+      <c r="BJ13" s="38" t="n"/>
       <c r="BK13" s="26" t="n">
         <v>-113</v>
       </c>
-      <c r="BL13" s="27" t="n">
+      <c r="BL13" s="39" t="n">
         <v>1.884956</v>
       </c>
       <c r="BM13" s="28" t="n">
@@ -4996,18 +5023,18 @@
       </c>
       <c r="BN13" s="28" t="n"/>
       <c r="BO13" s="28" t="n"/>
-      <c r="BP13" s="25" t="n"/>
-      <c r="BQ13" s="27" t="n"/>
+      <c r="BP13" s="38" t="n"/>
+      <c r="BQ13" s="39" t="n"/>
       <c r="BR13" s="28" t="n"/>
       <c r="BS13" s="28" t="n"/>
       <c r="BT13" s="28" t="n"/>
-      <c r="BU13" s="25" t="n"/>
+      <c r="BU13" s="38" t="n"/>
       <c r="BV13" s="29" t="n"/>
       <c r="BW13" s="24" t="n"/>
-      <c r="BX13" s="30" t="n">
+      <c r="BX13" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY13" s="27" t="n">
+      <c r="BY13" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ13" s="24" t="n"/>
@@ -5081,7 +5108,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J14" s="25" t="n"/>
+      <c r="J14" s="38" t="n"/>
       <c r="K14" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5090,7 +5117,7 @@
       <c r="L14" s="26" t="n">
         <v>-170</v>
       </c>
-      <c r="M14" s="27" t="n">
+      <c r="M14" s="39" t="n">
         <v>1.588235</v>
       </c>
       <c r="N14" s="28" t="n">
@@ -5130,11 +5157,11 @@
       <c r="X14" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="Y14" s="25" t="n"/>
+      <c r="Y14" s="38" t="n"/>
       <c r="Z14" s="26" t="n"/>
       <c r="AA14" s="28" t="n"/>
       <c r="AB14" s="28" t="n"/>
-      <c r="AC14" s="30" t="n">
+      <c r="AC14" s="40" t="n">
         <v>0.5881999999999999</v>
       </c>
       <c r="AD14" s="24" t="inlineStr">
@@ -5271,11 +5298,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ14" s="25" t="n"/>
+      <c r="BJ14" s="38" t="n"/>
       <c r="BK14" s="26" t="n">
         <v>-170</v>
       </c>
-      <c r="BL14" s="27" t="n">
+      <c r="BL14" s="39" t="n">
         <v>1.588235</v>
       </c>
       <c r="BM14" s="28" t="n">
@@ -5283,18 +5310,18 @@
       </c>
       <c r="BN14" s="28" t="n"/>
       <c r="BO14" s="28" t="n"/>
-      <c r="BP14" s="25" t="n"/>
-      <c r="BQ14" s="27" t="n"/>
+      <c r="BP14" s="38" t="n"/>
+      <c r="BQ14" s="39" t="n"/>
       <c r="BR14" s="28" t="n"/>
       <c r="BS14" s="28" t="n"/>
       <c r="BT14" s="28" t="n"/>
-      <c r="BU14" s="25" t="n"/>
+      <c r="BU14" s="38" t="n"/>
       <c r="BV14" s="29" t="n"/>
       <c r="BW14" s="24" t="n"/>
-      <c r="BX14" s="30" t="n">
+      <c r="BX14" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY14" s="27" t="n">
+      <c r="BY14" s="39" t="n">
         <v>0.91</v>
       </c>
       <c r="BZ14" s="24" t="n"/>
@@ -5368,7 +5395,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J15" s="25" t="n"/>
+      <c r="J15" s="38" t="n"/>
       <c r="K15" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5377,7 +5404,7 @@
       <c r="L15" s="26" t="n">
         <v>-144</v>
       </c>
-      <c r="M15" s="27" t="n">
+      <c r="M15" s="39" t="n">
         <v>1.694444</v>
       </c>
       <c r="N15" s="28" t="n">
@@ -5417,11 +5444,11 @@
       <c r="X15" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="Y15" s="25" t="n"/>
+      <c r="Y15" s="38" t="n"/>
       <c r="Z15" s="26" t="n"/>
       <c r="AA15" s="28" t="n"/>
       <c r="AB15" s="28" t="n"/>
-      <c r="AC15" s="30" t="n">
+      <c r="AC15" s="40" t="n">
         <v>0.8681</v>
       </c>
       <c r="AD15" s="24" t="inlineStr">
@@ -5558,11 +5585,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ15" s="25" t="n"/>
+      <c r="BJ15" s="38" t="n"/>
       <c r="BK15" s="26" t="n">
         <v>-144</v>
       </c>
-      <c r="BL15" s="27" t="n">
+      <c r="BL15" s="39" t="n">
         <v>1.694444</v>
       </c>
       <c r="BM15" s="28" t="n">
@@ -5570,18 +5597,18 @@
       </c>
       <c r="BN15" s="28" t="n"/>
       <c r="BO15" s="28" t="n"/>
-      <c r="BP15" s="25" t="n"/>
-      <c r="BQ15" s="27" t="n"/>
+      <c r="BP15" s="38" t="n"/>
+      <c r="BQ15" s="39" t="n"/>
       <c r="BR15" s="28" t="n"/>
       <c r="BS15" s="28" t="n"/>
       <c r="BT15" s="28" t="n"/>
-      <c r="BU15" s="25" t="n"/>
+      <c r="BU15" s="38" t="n"/>
       <c r="BV15" s="29" t="n"/>
       <c r="BW15" s="24" t="n"/>
-      <c r="BX15" s="30" t="n">
+      <c r="BX15" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY15" s="27" t="n">
+      <c r="BY15" s="39" t="n">
         <v>0.91</v>
       </c>
       <c r="BZ15" s="24" t="n"/>
@@ -5655,7 +5682,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J16" s="25" t="n"/>
+      <c r="J16" s="38" t="n"/>
       <c r="K16" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5664,7 +5691,7 @@
       <c r="L16" s="26" t="n">
         <v>-127</v>
       </c>
-      <c r="M16" s="27" t="n">
+      <c r="M16" s="39" t="n">
         <v>1.787402</v>
       </c>
       <c r="N16" s="28" t="n">
@@ -5704,11 +5731,11 @@
       <c r="X16" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="Y16" s="25" t="n"/>
+      <c r="Y16" s="38" t="n"/>
       <c r="Z16" s="26" t="n"/>
       <c r="AA16" s="28" t="n"/>
       <c r="AB16" s="28" t="n"/>
-      <c r="AC16" s="30" t="n">
+      <c r="AC16" s="40" t="n">
         <v>0.7874</v>
       </c>
       <c r="AD16" s="24" t="inlineStr">
@@ -5845,11 +5872,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ16" s="25" t="n"/>
+      <c r="BJ16" s="38" t="n"/>
       <c r="BK16" s="26" t="n">
         <v>-127</v>
       </c>
-      <c r="BL16" s="27" t="n">
+      <c r="BL16" s="39" t="n">
         <v>1.787402</v>
       </c>
       <c r="BM16" s="28" t="n">
@@ -5857,18 +5884,18 @@
       </c>
       <c r="BN16" s="28" t="n"/>
       <c r="BO16" s="28" t="n"/>
-      <c r="BP16" s="25" t="n"/>
-      <c r="BQ16" s="27" t="n"/>
+      <c r="BP16" s="38" t="n"/>
+      <c r="BQ16" s="39" t="n"/>
       <c r="BR16" s="28" t="n"/>
       <c r="BS16" s="28" t="n"/>
       <c r="BT16" s="28" t="n"/>
-      <c r="BU16" s="25" t="n"/>
+      <c r="BU16" s="38" t="n"/>
       <c r="BV16" s="29" t="n"/>
       <c r="BW16" s="24" t="n"/>
-      <c r="BX16" s="30" t="n">
+      <c r="BX16" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY16" s="27" t="n">
+      <c r="BY16" s="39" t="n">
         <v>0.91</v>
       </c>
       <c r="BZ16" s="24" t="n"/>
@@ -5942,7 +5969,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J17" s="25" t="n"/>
+      <c r="J17" s="38" t="n"/>
       <c r="K17" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -5951,7 +5978,7 @@
       <c r="L17" s="26" t="n">
         <v>-156</v>
       </c>
-      <c r="M17" s="27" t="n">
+      <c r="M17" s="39" t="n">
         <v>1.641026</v>
       </c>
       <c r="N17" s="28" t="n">
@@ -5968,7 +5995,7 @@
         <v>51</v>
       </c>
       <c r="S17" s="29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="T17" s="24" t="inlineStr">
         <is>
@@ -5991,12 +6018,12 @@
       <c r="X17" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="Y17" s="25" t="n"/>
+      <c r="Y17" s="38" t="n"/>
       <c r="Z17" s="26" t="n"/>
       <c r="AA17" s="28" t="n"/>
       <c r="AB17" s="28" t="n"/>
-      <c r="AC17" s="30" t="n">
-        <v>0</v>
+      <c r="AC17" s="40" t="n">
+        <v>-1.75</v>
       </c>
       <c r="AD17" s="24" t="inlineStr">
         <is>
@@ -6020,7 +6047,11 @@
       </c>
       <c r="AH17" s="24" t="n"/>
       <c r="AI17" s="31" t="n"/>
-      <c r="AJ17" s="31" t="n"/>
+      <c r="AJ17" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK17" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -6132,11 +6163,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ17" s="25" t="n"/>
+      <c r="BJ17" s="38" t="n"/>
       <c r="BK17" s="26" t="n">
         <v>-156</v>
       </c>
-      <c r="BL17" s="27" t="n">
+      <c r="BL17" s="39" t="n">
         <v>1.641026</v>
       </c>
       <c r="BM17" s="28" t="n">
@@ -6144,18 +6175,18 @@
       </c>
       <c r="BN17" s="28" t="n"/>
       <c r="BO17" s="28" t="n"/>
-      <c r="BP17" s="25" t="n"/>
-      <c r="BQ17" s="27" t="n"/>
+      <c r="BP17" s="38" t="n"/>
+      <c r="BQ17" s="39" t="n"/>
       <c r="BR17" s="28" t="n"/>
       <c r="BS17" s="28" t="n"/>
       <c r="BT17" s="28" t="n"/>
-      <c r="BU17" s="25" t="n"/>
+      <c r="BU17" s="38" t="n"/>
       <c r="BV17" s="29" t="n"/>
       <c r="BW17" s="24" t="n"/>
-      <c r="BX17" s="30" t="n">
+      <c r="BX17" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY17" s="27" t="n">
+      <c r="BY17" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ17" s="24" t="n"/>
@@ -6229,7 +6260,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J18" s="25" t="n"/>
+      <c r="J18" s="38" t="n"/>
       <c r="K18" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -6238,7 +6269,7 @@
       <c r="L18" s="26" t="n">
         <v>-203</v>
       </c>
-      <c r="M18" s="27" t="n">
+      <c r="M18" s="39" t="n">
         <v>1.492611</v>
       </c>
       <c r="N18" s="28" t="n">
@@ -6255,7 +6286,7 @@
         <v>0</v>
       </c>
       <c r="S18" s="29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T18" s="24" t="inlineStr">
         <is>
@@ -6278,12 +6309,12 @@
       <c r="X18" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y18" s="25" t="n"/>
+      <c r="Y18" s="38" t="n"/>
       <c r="Z18" s="26" t="n"/>
       <c r="AA18" s="28" t="n"/>
       <c r="AB18" s="28" t="n"/>
-      <c r="AC18" s="30" t="n">
-        <v>0</v>
+      <c r="AC18" s="40" t="n">
+        <v>0.6158</v>
       </c>
       <c r="AD18" s="24" t="inlineStr">
         <is>
@@ -6307,7 +6338,11 @@
       </c>
       <c r="AH18" s="24" t="n"/>
       <c r="AI18" s="31" t="n"/>
-      <c r="AJ18" s="31" t="n"/>
+      <c r="AJ18" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK18" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -6419,11 +6454,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ18" s="25" t="n"/>
+      <c r="BJ18" s="38" t="n"/>
       <c r="BK18" s="26" t="n">
         <v>-203</v>
       </c>
-      <c r="BL18" s="27" t="n">
+      <c r="BL18" s="39" t="n">
         <v>1.492611</v>
       </c>
       <c r="BM18" s="28" t="n">
@@ -6431,18 +6466,18 @@
       </c>
       <c r="BN18" s="28" t="n"/>
       <c r="BO18" s="28" t="n"/>
-      <c r="BP18" s="25" t="n"/>
-      <c r="BQ18" s="27" t="n"/>
+      <c r="BP18" s="38" t="n"/>
+      <c r="BQ18" s="39" t="n"/>
       <c r="BR18" s="28" t="n"/>
       <c r="BS18" s="28" t="n"/>
       <c r="BT18" s="28" t="n"/>
-      <c r="BU18" s="25" t="n"/>
+      <c r="BU18" s="38" t="n"/>
       <c r="BV18" s="29" t="n"/>
       <c r="BW18" s="24" t="n"/>
-      <c r="BX18" s="30" t="n">
+      <c r="BX18" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY18" s="27" t="n">
+      <c r="BY18" s="39" t="n">
         <v>0.91</v>
       </c>
       <c r="BZ18" s="24" t="n"/>
@@ -6516,7 +6551,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J19" s="25" t="n"/>
+      <c r="J19" s="38" t="n"/>
       <c r="K19" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -6525,7 +6560,7 @@
       <c r="L19" s="26" t="n">
         <v>-186</v>
       </c>
-      <c r="M19" s="27" t="n">
+      <c r="M19" s="39" t="n">
         <v>1.537634</v>
       </c>
       <c r="N19" s="28" t="n">
@@ -6542,7 +6577,7 @@
         <v>0</v>
       </c>
       <c r="S19" s="29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T19" s="24" t="inlineStr">
         <is>
@@ -6565,12 +6600,12 @@
       <c r="X19" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y19" s="25" t="n"/>
+      <c r="Y19" s="38" t="n"/>
       <c r="Z19" s="26" t="n"/>
       <c r="AA19" s="28" t="n"/>
       <c r="AB19" s="28" t="n"/>
-      <c r="AC19" s="30" t="n">
-        <v>0</v>
+      <c r="AC19" s="40" t="n">
+        <v>-1.25</v>
       </c>
       <c r="AD19" s="24" t="inlineStr">
         <is>
@@ -6594,7 +6629,11 @@
       </c>
       <c r="AH19" s="24" t="n"/>
       <c r="AI19" s="31" t="n"/>
-      <c r="AJ19" s="31" t="n"/>
+      <c r="AJ19" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK19" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -6706,11 +6745,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ19" s="25" t="n"/>
+      <c r="BJ19" s="38" t="n"/>
       <c r="BK19" s="26" t="n">
         <v>-186</v>
       </c>
-      <c r="BL19" s="27" t="n">
+      <c r="BL19" s="39" t="n">
         <v>1.537634</v>
       </c>
       <c r="BM19" s="28" t="n">
@@ -6718,18 +6757,18 @@
       </c>
       <c r="BN19" s="28" t="n"/>
       <c r="BO19" s="28" t="n"/>
-      <c r="BP19" s="25" t="n"/>
-      <c r="BQ19" s="27" t="n"/>
+      <c r="BP19" s="38" t="n"/>
+      <c r="BQ19" s="39" t="n"/>
       <c r="BR19" s="28" t="n"/>
       <c r="BS19" s="28" t="n"/>
       <c r="BT19" s="28" t="n"/>
-      <c r="BU19" s="25" t="n"/>
+      <c r="BU19" s="38" t="n"/>
       <c r="BV19" s="29" t="n"/>
       <c r="BW19" s="24" t="n"/>
-      <c r="BX19" s="30" t="n">
+      <c r="BX19" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY19" s="27" t="n">
+      <c r="BY19" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ19" s="24" t="n"/>
@@ -6803,7 +6842,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J20" s="25" t="n"/>
+      <c r="J20" s="38" t="n"/>
       <c r="K20" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -6812,7 +6851,7 @@
       <c r="L20" s="26" t="n">
         <v>-257</v>
       </c>
-      <c r="M20" s="27" t="n">
+      <c r="M20" s="39" t="n">
         <v>1.389105</v>
       </c>
       <c r="N20" s="28" t="n">
@@ -6829,7 +6868,7 @@
         <v>0</v>
       </c>
       <c r="S20" s="29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="T20" s="24" t="inlineStr">
         <is>
@@ -6852,12 +6891,12 @@
       <c r="X20" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="Y20" s="25" t="n"/>
+      <c r="Y20" s="38" t="n"/>
       <c r="Z20" s="26" t="n"/>
       <c r="AA20" s="28" t="n"/>
       <c r="AB20" s="28" t="n"/>
-      <c r="AC20" s="30" t="n">
-        <v>0</v>
+      <c r="AC20" s="40" t="n">
+        <v>0.6808999999999999</v>
       </c>
       <c r="AD20" s="24" t="inlineStr">
         <is>
@@ -6881,7 +6920,11 @@
       </c>
       <c r="AH20" s="24" t="n"/>
       <c r="AI20" s="31" t="n"/>
-      <c r="AJ20" s="31" t="n"/>
+      <c r="AJ20" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK20" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -6993,11 +7036,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ20" s="25" t="n"/>
+      <c r="BJ20" s="38" t="n"/>
       <c r="BK20" s="26" t="n">
         <v>-257</v>
       </c>
-      <c r="BL20" s="27" t="n">
+      <c r="BL20" s="39" t="n">
         <v>1.389105</v>
       </c>
       <c r="BM20" s="28" t="n">
@@ -7005,18 +7048,18 @@
       </c>
       <c r="BN20" s="28" t="n"/>
       <c r="BO20" s="28" t="n"/>
-      <c r="BP20" s="25" t="n"/>
-      <c r="BQ20" s="27" t="n"/>
+      <c r="BP20" s="38" t="n"/>
+      <c r="BQ20" s="39" t="n"/>
       <c r="BR20" s="28" t="n"/>
       <c r="BS20" s="28" t="n"/>
       <c r="BT20" s="28" t="n"/>
-      <c r="BU20" s="25" t="n"/>
+      <c r="BU20" s="38" t="n"/>
       <c r="BV20" s="29" t="n"/>
       <c r="BW20" s="24" t="n"/>
-      <c r="BX20" s="30" t="n">
+      <c r="BX20" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY20" s="27" t="n">
+      <c r="BY20" s="39" t="n">
         <v>0.91</v>
       </c>
       <c r="BZ20" s="24" t="n"/>
@@ -7090,7 +7133,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J21" s="25" t="n"/>
+      <c r="J21" s="38" t="n"/>
       <c r="K21" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -7099,7 +7142,7 @@
       <c r="L21" s="26" t="n">
         <v>-150</v>
       </c>
-      <c r="M21" s="27" t="n">
+      <c r="M21" s="39" t="n">
         <v>1.666667</v>
       </c>
       <c r="N21" s="28" t="n">
@@ -7116,7 +7159,7 @@
         <v>6</v>
       </c>
       <c r="S21" s="29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T21" s="24" t="inlineStr">
         <is>
@@ -7139,12 +7182,12 @@
       <c r="X21" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y21" s="25" t="n"/>
+      <c r="Y21" s="38" t="n"/>
       <c r="Z21" s="26" t="n"/>
       <c r="AA21" s="28" t="n"/>
       <c r="AB21" s="28" t="n"/>
-      <c r="AC21" s="30" t="n">
-        <v>0</v>
+      <c r="AC21" s="40" t="n">
+        <v>0.8333</v>
       </c>
       <c r="AD21" s="24" t="inlineStr">
         <is>
@@ -7168,7 +7211,11 @@
       </c>
       <c r="AH21" s="24" t="n"/>
       <c r="AI21" s="31" t="n"/>
-      <c r="AJ21" s="31" t="n"/>
+      <c r="AJ21" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK21" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -7280,11 +7327,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ21" s="25" t="n"/>
+      <c r="BJ21" s="38" t="n"/>
       <c r="BK21" s="26" t="n">
         <v>-150</v>
       </c>
-      <c r="BL21" s="27" t="n">
+      <c r="BL21" s="39" t="n">
         <v>1.666667</v>
       </c>
       <c r="BM21" s="28" t="n">
@@ -7292,18 +7339,18 @@
       </c>
       <c r="BN21" s="28" t="n"/>
       <c r="BO21" s="28" t="n"/>
-      <c r="BP21" s="25" t="n"/>
-      <c r="BQ21" s="27" t="n"/>
+      <c r="BP21" s="38" t="n"/>
+      <c r="BQ21" s="39" t="n"/>
       <c r="BR21" s="28" t="n"/>
       <c r="BS21" s="28" t="n"/>
       <c r="BT21" s="28" t="n"/>
-      <c r="BU21" s="25" t="n"/>
+      <c r="BU21" s="38" t="n"/>
       <c r="BV21" s="29" t="n"/>
       <c r="BW21" s="24" t="n"/>
-      <c r="BX21" s="30" t="n">
+      <c r="BX21" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY21" s="27" t="n">
+      <c r="BY21" s="39" t="n">
         <v>0.91</v>
       </c>
       <c r="BZ21" s="24" t="n"/>
@@ -7377,7 +7424,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J22" s="25" t="n"/>
+      <c r="J22" s="38" t="n"/>
       <c r="K22" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -7386,7 +7433,7 @@
       <c r="L22" s="26" t="n">
         <v>-113</v>
       </c>
-      <c r="M22" s="27" t="n">
+      <c r="M22" s="39" t="n">
         <v>1.884956</v>
       </c>
       <c r="N22" s="28" t="n">
@@ -7403,7 +7450,7 @@
         <v>31</v>
       </c>
       <c r="S22" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T22" s="24" t="inlineStr">
         <is>
@@ -7426,12 +7473,12 @@
       <c r="X22" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y22" s="25" t="n"/>
+      <c r="Y22" s="38" t="n"/>
       <c r="Z22" s="26" t="n"/>
       <c r="AA22" s="28" t="n"/>
       <c r="AB22" s="28" t="n"/>
-      <c r="AC22" s="30" t="n">
-        <v>0</v>
+      <c r="AC22" s="40" t="n">
+        <v>-1</v>
       </c>
       <c r="AD22" s="24" t="inlineStr">
         <is>
@@ -7455,7 +7502,11 @@
       </c>
       <c r="AH22" s="24" t="n"/>
       <c r="AI22" s="31" t="n"/>
-      <c r="AJ22" s="31" t="n"/>
+      <c r="AJ22" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK22" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -7567,11 +7618,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ22" s="25" t="n"/>
+      <c r="BJ22" s="38" t="n"/>
       <c r="BK22" s="26" t="n">
         <v>-113</v>
       </c>
-      <c r="BL22" s="27" t="n">
+      <c r="BL22" s="39" t="n">
         <v>1.884956</v>
       </c>
       <c r="BM22" s="28" t="n">
@@ -7579,18 +7630,18 @@
       </c>
       <c r="BN22" s="28" t="n"/>
       <c r="BO22" s="28" t="n"/>
-      <c r="BP22" s="25" t="n"/>
-      <c r="BQ22" s="27" t="n"/>
+      <c r="BP22" s="38" t="n"/>
+      <c r="BQ22" s="39" t="n"/>
       <c r="BR22" s="28" t="n"/>
       <c r="BS22" s="28" t="n"/>
       <c r="BT22" s="28" t="n"/>
-      <c r="BU22" s="25" t="n"/>
+      <c r="BU22" s="38" t="n"/>
       <c r="BV22" s="29" t="n"/>
       <c r="BW22" s="24" t="n"/>
-      <c r="BX22" s="30" t="n">
+      <c r="BX22" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY22" s="27" t="n">
+      <c r="BY22" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ22" s="24" t="n"/>
@@ -7664,7 +7715,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J23" s="25" t="n"/>
+      <c r="J23" s="38" t="n"/>
       <c r="K23" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -7673,7 +7724,7 @@
       <c r="L23" s="26" t="n">
         <v>-178</v>
       </c>
-      <c r="M23" s="27" t="n">
+      <c r="M23" s="39" t="n">
         <v>1.561798</v>
       </c>
       <c r="N23" s="28" t="n">
@@ -7690,7 +7741,7 @@
         <v>27</v>
       </c>
       <c r="S23" s="29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="T23" s="24" t="inlineStr">
         <is>
@@ -7713,12 +7764,12 @@
       <c r="X23" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="Y23" s="25" t="n"/>
+      <c r="Y23" s="38" t="n"/>
       <c r="Z23" s="26" t="n"/>
       <c r="AA23" s="28" t="n"/>
       <c r="AB23" s="28" t="n"/>
-      <c r="AC23" s="30" t="n">
-        <v>0</v>
+      <c r="AC23" s="40" t="n">
+        <v>-1.75</v>
       </c>
       <c r="AD23" s="24" t="inlineStr">
         <is>
@@ -7742,7 +7793,11 @@
       </c>
       <c r="AH23" s="24" t="n"/>
       <c r="AI23" s="31" t="n"/>
-      <c r="AJ23" s="31" t="n"/>
+      <c r="AJ23" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK23" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -7854,11 +7909,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ23" s="25" t="n"/>
+      <c r="BJ23" s="38" t="n"/>
       <c r="BK23" s="26" t="n">
         <v>-178</v>
       </c>
-      <c r="BL23" s="27" t="n">
+      <c r="BL23" s="39" t="n">
         <v>1.561798</v>
       </c>
       <c r="BM23" s="28" t="n">
@@ -7866,18 +7921,18 @@
       </c>
       <c r="BN23" s="28" t="n"/>
       <c r="BO23" s="28" t="n"/>
-      <c r="BP23" s="25" t="n"/>
-      <c r="BQ23" s="27" t="n"/>
+      <c r="BP23" s="38" t="n"/>
+      <c r="BQ23" s="39" t="n"/>
       <c r="BR23" s="28" t="n"/>
       <c r="BS23" s="28" t="n"/>
       <c r="BT23" s="28" t="n"/>
-      <c r="BU23" s="25" t="n"/>
+      <c r="BU23" s="38" t="n"/>
       <c r="BV23" s="29" t="n"/>
       <c r="BW23" s="24" t="n"/>
-      <c r="BX23" s="30" t="n">
+      <c r="BX23" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY23" s="27" t="n">
+      <c r="BY23" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ23" s="24" t="n"/>
@@ -7951,7 +8006,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J24" s="25" t="n"/>
+      <c r="J24" s="38" t="n"/>
       <c r="K24" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -7960,7 +8015,7 @@
       <c r="L24" s="26" t="n">
         <v>-127</v>
       </c>
-      <c r="M24" s="27" t="n">
+      <c r="M24" s="39" t="n">
         <v>1.787402</v>
       </c>
       <c r="N24" s="28" t="n">
@@ -8000,11 +8055,11 @@
       <c r="X24" s="26" t="n">
         <v>8</v>
       </c>
-      <c r="Y24" s="25" t="n"/>
+      <c r="Y24" s="38" t="n"/>
       <c r="Z24" s="26" t="n"/>
       <c r="AA24" s="28" t="n"/>
       <c r="AB24" s="28" t="n"/>
-      <c r="AC24" s="30" t="n">
+      <c r="AC24" s="40" t="n">
         <v>1.378</v>
       </c>
       <c r="AD24" s="24" t="inlineStr">
@@ -8141,11 +8196,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ24" s="25" t="n"/>
+      <c r="BJ24" s="38" t="n"/>
       <c r="BK24" s="26" t="n">
         <v>-127</v>
       </c>
-      <c r="BL24" s="27" t="n">
+      <c r="BL24" s="39" t="n">
         <v>1.787402</v>
       </c>
       <c r="BM24" s="28" t="n">
@@ -8153,18 +8208,18 @@
       </c>
       <c r="BN24" s="28" t="n"/>
       <c r="BO24" s="28" t="n"/>
-      <c r="BP24" s="25" t="n"/>
-      <c r="BQ24" s="27" t="n"/>
+      <c r="BP24" s="38" t="n"/>
+      <c r="BQ24" s="39" t="n"/>
       <c r="BR24" s="28" t="n"/>
       <c r="BS24" s="28" t="n"/>
       <c r="BT24" s="28" t="n"/>
-      <c r="BU24" s="25" t="n"/>
+      <c r="BU24" s="38" t="n"/>
       <c r="BV24" s="29" t="n"/>
       <c r="BW24" s="24" t="n"/>
-      <c r="BX24" s="30" t="n">
+      <c r="BX24" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY24" s="27" t="n">
+      <c r="BY24" s="39" t="n">
         <v>0.91</v>
       </c>
       <c r="BZ24" s="24" t="n"/>
@@ -8238,7 +8293,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J25" s="25" t="n"/>
+      <c r="J25" s="38" t="n"/>
       <c r="K25" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8247,7 +8302,7 @@
       <c r="L25" s="26" t="n">
         <v>-122</v>
       </c>
-      <c r="M25" s="27" t="n">
+      <c r="M25" s="39" t="n">
         <v>1.819672</v>
       </c>
       <c r="N25" s="28" t="n">
@@ -8264,7 +8319,7 @@
         <v>38</v>
       </c>
       <c r="S25" s="29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T25" s="24" t="inlineStr">
         <is>
@@ -8287,12 +8342,12 @@
       <c r="X25" s="26" t="n">
         <v>2</v>
       </c>
-      <c r="Y25" s="25" t="n"/>
+      <c r="Y25" s="38" t="n"/>
       <c r="Z25" s="26" t="n"/>
       <c r="AA25" s="28" t="n"/>
       <c r="AB25" s="28" t="n"/>
-      <c r="AC25" s="30" t="n">
-        <v>0</v>
+      <c r="AC25" s="40" t="n">
+        <v>-1.25</v>
       </c>
       <c r="AD25" s="24" t="inlineStr">
         <is>
@@ -8316,7 +8371,11 @@
       </c>
       <c r="AH25" s="24" t="n"/>
       <c r="AI25" s="31" t="n"/>
-      <c r="AJ25" s="31" t="n"/>
+      <c r="AJ25" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK25" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -8428,11 +8487,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ25" s="25" t="n"/>
+      <c r="BJ25" s="38" t="n"/>
       <c r="BK25" s="26" t="n">
         <v>-122</v>
       </c>
-      <c r="BL25" s="27" t="n">
+      <c r="BL25" s="39" t="n">
         <v>1.819672</v>
       </c>
       <c r="BM25" s="28" t="n">
@@ -8440,18 +8499,18 @@
       </c>
       <c r="BN25" s="28" t="n"/>
       <c r="BO25" s="28" t="n"/>
-      <c r="BP25" s="25" t="n"/>
-      <c r="BQ25" s="27" t="n"/>
+      <c r="BP25" s="38" t="n"/>
+      <c r="BQ25" s="39" t="n"/>
       <c r="BR25" s="28" t="n"/>
       <c r="BS25" s="28" t="n"/>
       <c r="BT25" s="28" t="n"/>
-      <c r="BU25" s="25" t="n"/>
+      <c r="BU25" s="38" t="n"/>
       <c r="BV25" s="29" t="n"/>
       <c r="BW25" s="24" t="n"/>
-      <c r="BX25" s="30" t="n">
+      <c r="BX25" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY25" s="27" t="n">
+      <c r="BY25" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ25" s="24" t="n"/>
@@ -8525,7 +8584,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J26" s="25" t="n"/>
+      <c r="J26" s="38" t="n"/>
       <c r="K26" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8534,7 +8593,7 @@
       <c r="L26" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="M26" s="27" t="n">
+      <c r="M26" s="39" t="n">
         <v>2.08</v>
       </c>
       <c r="N26" s="28" t="n">
@@ -8551,7 +8610,7 @@
         <v>45</v>
       </c>
       <c r="S26" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T26" s="24" t="inlineStr">
         <is>
@@ -8574,12 +8633,12 @@
       <c r="X26" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y26" s="25" t="n"/>
+      <c r="Y26" s="38" t="n"/>
       <c r="Z26" s="26" t="n"/>
       <c r="AA26" s="28" t="n"/>
       <c r="AB26" s="28" t="n"/>
-      <c r="AC26" s="30" t="n">
-        <v>0</v>
+      <c r="AC26" s="40" t="n">
+        <v>1.08</v>
       </c>
       <c r="AD26" s="24" t="inlineStr">
         <is>
@@ -8603,7 +8662,11 @@
       </c>
       <c r="AH26" s="24" t="n"/>
       <c r="AI26" s="31" t="n"/>
-      <c r="AJ26" s="31" t="n"/>
+      <c r="AJ26" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK26" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -8715,11 +8778,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ26" s="25" t="n"/>
+      <c r="BJ26" s="38" t="n"/>
       <c r="BK26" s="26" t="n">
         <v>108</v>
       </c>
-      <c r="BL26" s="27" t="n">
+      <c r="BL26" s="39" t="n">
         <v>2.08</v>
       </c>
       <c r="BM26" s="28" t="n">
@@ -8727,18 +8790,18 @@
       </c>
       <c r="BN26" s="28" t="n"/>
       <c r="BO26" s="28" t="n"/>
-      <c r="BP26" s="25" t="n"/>
-      <c r="BQ26" s="27" t="n"/>
+      <c r="BP26" s="38" t="n"/>
+      <c r="BQ26" s="39" t="n"/>
       <c r="BR26" s="28" t="n"/>
       <c r="BS26" s="28" t="n"/>
       <c r="BT26" s="28" t="n"/>
-      <c r="BU26" s="25" t="n"/>
+      <c r="BU26" s="38" t="n"/>
       <c r="BV26" s="29" t="n"/>
       <c r="BW26" s="24" t="n"/>
-      <c r="BX26" s="30" t="n">
+      <c r="BX26" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY26" s="27" t="n">
+      <c r="BY26" s="39" t="n">
         <v>0.91</v>
       </c>
       <c r="BZ26" s="24" t="n"/>
@@ -8812,7 +8875,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J27" s="25" t="n"/>
+      <c r="J27" s="38" t="n"/>
       <c r="K27" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -8821,7 +8884,7 @@
       <c r="L27" s="26" t="n">
         <v>-127</v>
       </c>
-      <c r="M27" s="27" t="n">
+      <c r="M27" s="39" t="n">
         <v>1.787402</v>
       </c>
       <c r="N27" s="28" t="n">
@@ -8838,7 +8901,7 @@
         <v>23</v>
       </c>
       <c r="S27" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T27" s="24" t="inlineStr">
         <is>
@@ -8861,12 +8924,12 @@
       <c r="X27" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y27" s="25" t="n"/>
+      <c r="Y27" s="38" t="n"/>
       <c r="Z27" s="26" t="n"/>
       <c r="AA27" s="28" t="n"/>
       <c r="AB27" s="28" t="n"/>
-      <c r="AC27" s="30" t="n">
-        <v>0</v>
+      <c r="AC27" s="40" t="n">
+        <v>-1</v>
       </c>
       <c r="AD27" s="24" t="inlineStr">
         <is>
@@ -8890,7 +8953,11 @@
       </c>
       <c r="AH27" s="24" t="n"/>
       <c r="AI27" s="31" t="n"/>
-      <c r="AJ27" s="31" t="n"/>
+      <c r="AJ27" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK27" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -9002,11 +9069,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ27" s="25" t="n"/>
+      <c r="BJ27" s="38" t="n"/>
       <c r="BK27" s="26" t="n">
         <v>-127</v>
       </c>
-      <c r="BL27" s="27" t="n">
+      <c r="BL27" s="39" t="n">
         <v>1.787402</v>
       </c>
       <c r="BM27" s="28" t="n">
@@ -9014,18 +9081,18 @@
       </c>
       <c r="BN27" s="28" t="n"/>
       <c r="BO27" s="28" t="n"/>
-      <c r="BP27" s="25" t="n"/>
-      <c r="BQ27" s="27" t="n"/>
+      <c r="BP27" s="38" t="n"/>
+      <c r="BQ27" s="39" t="n"/>
       <c r="BR27" s="28" t="n"/>
       <c r="BS27" s="28" t="n"/>
       <c r="BT27" s="28" t="n"/>
-      <c r="BU27" s="25" t="n"/>
+      <c r="BU27" s="38" t="n"/>
       <c r="BV27" s="29" t="n"/>
       <c r="BW27" s="24" t="n"/>
-      <c r="BX27" s="30" t="n">
+      <c r="BX27" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY27" s="27" t="n">
+      <c r="BY27" s="39" t="n">
         <v>-1</v>
       </c>
       <c r="BZ27" s="24" t="n"/>
@@ -9099,7 +9166,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J28" s="25" t="n"/>
+      <c r="J28" s="38" t="n"/>
       <c r="K28" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9108,7 +9175,7 @@
       <c r="L28" s="26" t="n">
         <v>-150</v>
       </c>
-      <c r="M28" s="27" t="n">
+      <c r="M28" s="39" t="n">
         <v>1.666667</v>
       </c>
       <c r="N28" s="28" t="n">
@@ -9125,7 +9192,7 @@
         <v>18</v>
       </c>
       <c r="S28" s="29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T28" s="24" t="inlineStr">
         <is>
@@ -9148,12 +9215,12 @@
       <c r="X28" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="Y28" s="25" t="n"/>
+      <c r="Y28" s="38" t="n"/>
       <c r="Z28" s="26" t="n"/>
       <c r="AA28" s="28" t="n"/>
       <c r="AB28" s="28" t="n"/>
-      <c r="AC28" s="30" t="n">
-        <v>0</v>
+      <c r="AC28" s="40" t="n">
+        <v>0.8333</v>
       </c>
       <c r="AD28" s="24" t="inlineStr">
         <is>
@@ -9177,7 +9244,11 @@
       </c>
       <c r="AH28" s="24" t="n"/>
       <c r="AI28" s="31" t="n"/>
-      <c r="AJ28" s="31" t="n"/>
+      <c r="AJ28" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK28" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -9289,11 +9360,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ28" s="25" t="n"/>
+      <c r="BJ28" s="38" t="n"/>
       <c r="BK28" s="26" t="n">
         <v>-150</v>
       </c>
-      <c r="BL28" s="27" t="n">
+      <c r="BL28" s="39" t="n">
         <v>1.666667</v>
       </c>
       <c r="BM28" s="28" t="n">
@@ -9301,18 +9372,18 @@
       </c>
       <c r="BN28" s="28" t="n"/>
       <c r="BO28" s="28" t="n"/>
-      <c r="BP28" s="25" t="n"/>
-      <c r="BQ28" s="27" t="n"/>
+      <c r="BP28" s="38" t="n"/>
+      <c r="BQ28" s="39" t="n"/>
       <c r="BR28" s="28" t="n"/>
       <c r="BS28" s="28" t="n"/>
       <c r="BT28" s="28" t="n"/>
-      <c r="BU28" s="25" t="n"/>
+      <c r="BU28" s="38" t="n"/>
       <c r="BV28" s="29" t="n"/>
       <c r="BW28" s="24" t="n"/>
-      <c r="BX28" s="30" t="n">
+      <c r="BX28" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY28" s="27" t="n">
+      <c r="BY28" s="39" t="n">
         <v>0.91</v>
       </c>
       <c r="BZ28" s="24" t="n"/>
@@ -9386,7 +9457,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J29" s="25" t="n"/>
+      <c r="J29" s="38" t="n"/>
       <c r="K29" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9395,7 +9466,7 @@
       <c r="L29" s="26" t="n">
         <v>104</v>
       </c>
-      <c r="M29" s="27" t="n">
+      <c r="M29" s="39" t="n">
         <v>2.04</v>
       </c>
       <c r="N29" s="28" t="n">
@@ -9412,7 +9483,7 @@
         <v>48</v>
       </c>
       <c r="S29" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T29" s="24" t="inlineStr">
         <is>
@@ -9435,12 +9506,12 @@
       <c r="X29" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="Y29" s="25" t="n"/>
+      <c r="Y29" s="38" t="n"/>
       <c r="Z29" s="26" t="n"/>
       <c r="AA29" s="28" t="n"/>
       <c r="AB29" s="28" t="n"/>
-      <c r="AC29" s="30" t="n">
-        <v>0</v>
+      <c r="AC29" s="40" t="n">
+        <v>1.04</v>
       </c>
       <c r="AD29" s="24" t="inlineStr">
         <is>
@@ -9464,7 +9535,11 @@
       </c>
       <c r="AH29" s="24" t="n"/>
       <c r="AI29" s="31" t="n"/>
-      <c r="AJ29" s="31" t="n"/>
+      <c r="AJ29" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK29" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -9576,11 +9651,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ29" s="25" t="n"/>
+      <c r="BJ29" s="38" t="n"/>
       <c r="BK29" s="26" t="n">
         <v>104</v>
       </c>
-      <c r="BL29" s="27" t="n">
+      <c r="BL29" s="39" t="n">
         <v>2.04</v>
       </c>
       <c r="BM29" s="28" t="n">
@@ -9588,18 +9663,18 @@
       </c>
       <c r="BN29" s="28" t="n"/>
       <c r="BO29" s="28" t="n"/>
-      <c r="BP29" s="25" t="n"/>
-      <c r="BQ29" s="27" t="n"/>
+      <c r="BP29" s="38" t="n"/>
+      <c r="BQ29" s="39" t="n"/>
       <c r="BR29" s="28" t="n"/>
       <c r="BS29" s="28" t="n"/>
       <c r="BT29" s="28" t="n"/>
-      <c r="BU29" s="25" t="n"/>
+      <c r="BU29" s="38" t="n"/>
       <c r="BV29" s="29" t="n"/>
       <c r="BW29" s="24" t="n"/>
-      <c r="BX29" s="30" t="n">
+      <c r="BX29" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY29" s="27" t="n">
+      <c r="BY29" s="39" t="n">
         <v>0.91</v>
       </c>
       <c r="BZ29" s="24" t="n"/>
@@ -9673,7 +9748,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J30" s="25" t="n"/>
+      <c r="J30" s="38" t="n"/>
       <c r="K30" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9682,7 +9757,7 @@
       <c r="L30" s="26" t="n">
         <v>-144</v>
       </c>
-      <c r="M30" s="27" t="n">
+      <c r="M30" s="39" t="n">
         <v>1.694444</v>
       </c>
       <c r="N30" s="28" t="n">
@@ -9699,7 +9774,7 @@
         <v>11</v>
       </c>
       <c r="S30" s="29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T30" s="24" t="inlineStr">
         <is>
@@ -9722,12 +9797,12 @@
       <c r="X30" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="Y30" s="25" t="n"/>
+      <c r="Y30" s="38" t="n"/>
       <c r="Z30" s="26" t="n"/>
       <c r="AA30" s="28" t="n"/>
       <c r="AB30" s="28" t="n"/>
-      <c r="AC30" s="30" t="n">
-        <v>0</v>
+      <c r="AC30" s="40" t="n">
+        <v>0.8681</v>
       </c>
       <c r="AD30" s="24" t="inlineStr">
         <is>
@@ -9751,7 +9826,11 @@
       </c>
       <c r="AH30" s="24" t="n"/>
       <c r="AI30" s="31" t="n"/>
-      <c r="AJ30" s="31" t="n"/>
+      <c r="AJ30" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK30" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -9863,11 +9942,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ30" s="25" t="n"/>
+      <c r="BJ30" s="38" t="n"/>
       <c r="BK30" s="26" t="n">
         <v>-144</v>
       </c>
-      <c r="BL30" s="27" t="n">
+      <c r="BL30" s="39" t="n">
         <v>1.694444</v>
       </c>
       <c r="BM30" s="28" t="n">
@@ -9875,18 +9954,18 @@
       </c>
       <c r="BN30" s="28" t="n"/>
       <c r="BO30" s="28" t="n"/>
-      <c r="BP30" s="25" t="n"/>
-      <c r="BQ30" s="27" t="n"/>
+      <c r="BP30" s="38" t="n"/>
+      <c r="BQ30" s="39" t="n"/>
       <c r="BR30" s="28" t="n"/>
       <c r="BS30" s="28" t="n"/>
       <c r="BT30" s="28" t="n"/>
-      <c r="BU30" s="25" t="n"/>
+      <c r="BU30" s="38" t="n"/>
       <c r="BV30" s="29" t="n"/>
       <c r="BW30" s="24" t="n"/>
-      <c r="BX30" s="30" t="n">
+      <c r="BX30" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY30" s="27" t="n">
+      <c r="BY30" s="39" t="n">
         <v>0.91</v>
       </c>
       <c r="BZ30" s="24" t="n"/>
@@ -9960,7 +10039,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J31" s="25" t="n"/>
+      <c r="J31" s="38" t="n"/>
       <c r="K31" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -9969,7 +10048,7 @@
       <c r="L31" s="26" t="n">
         <v>-156</v>
       </c>
-      <c r="M31" s="27" t="n">
+      <c r="M31" s="39" t="n">
         <v>1.641026</v>
       </c>
       <c r="N31" s="28" t="n">
@@ -9986,7 +10065,7 @@
         <v>18</v>
       </c>
       <c r="S31" s="29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T31" s="24" t="inlineStr">
         <is>
@@ -10009,12 +10088,12 @@
       <c r="X31" s="26" t="n">
         <v>3</v>
       </c>
-      <c r="Y31" s="25" t="n"/>
+      <c r="Y31" s="38" t="n"/>
       <c r="Z31" s="26" t="n"/>
       <c r="AA31" s="28" t="n"/>
       <c r="AB31" s="28" t="n"/>
-      <c r="AC31" s="30" t="n">
-        <v>0</v>
+      <c r="AC31" s="40" t="n">
+        <v>0.8013</v>
       </c>
       <c r="AD31" s="24" t="inlineStr">
         <is>
@@ -10038,7 +10117,11 @@
       </c>
       <c r="AH31" s="24" t="n"/>
       <c r="AI31" s="31" t="n"/>
-      <c r="AJ31" s="31" t="n"/>
+      <c r="AJ31" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK31" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -10150,11 +10233,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ31" s="25" t="n"/>
+      <c r="BJ31" s="38" t="n"/>
       <c r="BK31" s="26" t="n">
         <v>-156</v>
       </c>
-      <c r="BL31" s="27" t="n">
+      <c r="BL31" s="39" t="n">
         <v>1.641026</v>
       </c>
       <c r="BM31" s="28" t="n">
@@ -10162,18 +10245,18 @@
       </c>
       <c r="BN31" s="28" t="n"/>
       <c r="BO31" s="28" t="n"/>
-      <c r="BP31" s="25" t="n"/>
-      <c r="BQ31" s="27" t="n"/>
+      <c r="BP31" s="38" t="n"/>
+      <c r="BQ31" s="39" t="n"/>
       <c r="BR31" s="28" t="n"/>
       <c r="BS31" s="28" t="n"/>
       <c r="BT31" s="28" t="n"/>
-      <c r="BU31" s="25" t="n"/>
+      <c r="BU31" s="38" t="n"/>
       <c r="BV31" s="29" t="n"/>
       <c r="BW31" s="24" t="n"/>
-      <c r="BX31" s="30" t="n">
+      <c r="BX31" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY31" s="27" t="n">
+      <c r="BY31" s="39" t="n">
         <v>0.91</v>
       </c>
       <c r="BZ31" s="24" t="n"/>
@@ -10247,7 +10330,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J32" s="25" t="n"/>
+      <c r="J32" s="38" t="n"/>
       <c r="K32" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -10256,7 +10339,7 @@
       <c r="L32" s="26" t="n">
         <v>-163</v>
       </c>
-      <c r="M32" s="27" t="n">
+      <c r="M32" s="39" t="n">
         <v>1.613497</v>
       </c>
       <c r="N32" s="28" t="n">
@@ -10273,7 +10356,7 @@
         <v>0</v>
       </c>
       <c r="S32" s="29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T32" s="24" t="inlineStr">
         <is>
@@ -10296,12 +10379,12 @@
       <c r="X32" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="Y32" s="25" t="n"/>
+      <c r="Y32" s="38" t="n"/>
       <c r="Z32" s="26" t="n"/>
       <c r="AA32" s="28" t="n"/>
       <c r="AB32" s="28" t="n"/>
-      <c r="AC32" s="30" t="n">
-        <v>0</v>
+      <c r="AC32" s="40" t="n">
+        <v>0.6135</v>
       </c>
       <c r="AD32" s="24" t="inlineStr">
         <is>
@@ -10325,7 +10408,11 @@
       </c>
       <c r="AH32" s="24" t="n"/>
       <c r="AI32" s="31" t="n"/>
-      <c r="AJ32" s="31" t="n"/>
+      <c r="AJ32" s="31" t="inlineStr">
+        <is>
+          <t>2026-08-13 data-repair: reason_code NO_CALL_WINNER_OVERVALUED and this row's original units/pnl_units=0 were produced by an unmerged rebuild branch (commit ed580af, tag archive/rebuild-clean-slate-v1-70250b1...) that was checked out in this working tree 2026-08-05..2026-08-09; that branch's "value gate" does not exist in any current code path. units backfilled via the current edge_scaled_units() formula (same one used by every peer NO_CALL row in this ledger); pnl_units recomputed from the recorded result. decision/record_type left as NO_CALL/RESEARCH_OBSERVATION (not promoted to CALL) since reconstructing whether current gates would have qualified it is a separate judgment call, not a mechanical repair.</t>
+        </is>
+      </c>
       <c r="AK32" s="24" t="inlineStr">
         <is>
           <t>research_observation</t>
@@ -10437,11 +10524,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ32" s="25" t="n"/>
+      <c r="BJ32" s="38" t="n"/>
       <c r="BK32" s="26" t="n">
         <v>-163</v>
       </c>
-      <c r="BL32" s="27" t="n">
+      <c r="BL32" s="39" t="n">
         <v>1.613497</v>
       </c>
       <c r="BM32" s="28" t="n">
@@ -10449,18 +10536,18 @@
       </c>
       <c r="BN32" s="28" t="n"/>
       <c r="BO32" s="28" t="n"/>
-      <c r="BP32" s="25" t="n"/>
-      <c r="BQ32" s="27" t="n"/>
+      <c r="BP32" s="38" t="n"/>
+      <c r="BQ32" s="39" t="n"/>
       <c r="BR32" s="28" t="n"/>
       <c r="BS32" s="28" t="n"/>
       <c r="BT32" s="28" t="n"/>
-      <c r="BU32" s="25" t="n"/>
+      <c r="BU32" s="38" t="n"/>
       <c r="BV32" s="29" t="n"/>
       <c r="BW32" s="24" t="n"/>
-      <c r="BX32" s="30" t="n">
+      <c r="BX32" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="BY32" s="27" t="n">
+      <c r="BY32" s="39" t="n">
         <v>0.91</v>
       </c>
       <c r="BZ32" s="24" t="n"/>
@@ -10534,7 +10621,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J33" s="25" t="n"/>
+      <c r="J33" s="38" t="n"/>
       <c r="K33" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -10543,7 +10630,7 @@
       <c r="L33" s="26" t="n">
         <v>127</v>
       </c>
-      <c r="M33" s="27" t="n">
+      <c r="M33" s="39" t="n">
         <v>2.27</v>
       </c>
       <c r="N33" s="28" t="n">
@@ -10569,18 +10656,32 @@
       </c>
       <c r="U33" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V33" s="24" t="n"/>
-      <c r="W33" s="26" t="n"/>
-      <c r="X33" s="26" t="n"/>
-      <c r="Y33" s="25" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V33" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W33" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="X33" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y33" s="38" t="n"/>
       <c r="Z33" s="26" t="n"/>
       <c r="AA33" s="28" t="n"/>
       <c r="AB33" s="28" t="n"/>
-      <c r="AC33" s="30" t="n"/>
-      <c r="AD33" s="24" t="n"/>
+      <c r="AC33" s="40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD33" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:15:45.502496Z</t>
+        </is>
+      </c>
       <c r="AE33" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.4400 (market_slug=aec-npb-ygo-hta-2026-08-12). Tie probability=0.0348.</t>
@@ -10593,7 +10694,7 @@
       </c>
       <c r="AG33" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH33" s="24" t="n"/>
@@ -10710,11 +10811,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ33" s="25" t="n"/>
+      <c r="BJ33" s="38" t="n"/>
       <c r="BK33" s="26" t="n">
         <v>127</v>
       </c>
-      <c r="BL33" s="27" t="n">
+      <c r="BL33" s="39" t="n">
         <v>2.27</v>
       </c>
       <c r="BM33" s="28" t="n">
@@ -10722,16 +10823,16 @@
       </c>
       <c r="BN33" s="28" t="n"/>
       <c r="BO33" s="28" t="n"/>
-      <c r="BP33" s="25" t="n"/>
-      <c r="BQ33" s="27" t="n"/>
+      <c r="BP33" s="38" t="n"/>
+      <c r="BQ33" s="39" t="n"/>
       <c r="BR33" s="28" t="n"/>
       <c r="BS33" s="28" t="n"/>
       <c r="BT33" s="28" t="n"/>
-      <c r="BU33" s="25" t="n"/>
+      <c r="BU33" s="38" t="n"/>
       <c r="BV33" s="29" t="n"/>
       <c r="BW33" s="24" t="n"/>
-      <c r="BX33" s="30" t="n"/>
-      <c r="BY33" s="27" t="n"/>
+      <c r="BX33" s="40" t="n"/>
+      <c r="BY33" s="39" t="n"/>
       <c r="BZ33" s="24" t="n"/>
       <c r="CA33" s="31" t="n"/>
       <c r="CB33" s="24" t="n"/>
@@ -10803,7 +10904,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J34" s="25" t="n"/>
+      <c r="J34" s="38" t="n"/>
       <c r="K34" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -10812,7 +10913,7 @@
       <c r="L34" s="26" t="n">
         <v>127</v>
       </c>
-      <c r="M34" s="27" t="n">
+      <c r="M34" s="39" t="n">
         <v>2.27</v>
       </c>
       <c r="N34" s="28" t="n">
@@ -10838,18 +10939,32 @@
       </c>
       <c r="U34" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V34" s="24" t="n"/>
-      <c r="W34" s="26" t="n"/>
-      <c r="X34" s="26" t="n"/>
-      <c r="Y34" s="25" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V34" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W34" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="X34" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y34" s="38" t="n"/>
       <c r="Z34" s="26" t="n"/>
       <c r="AA34" s="28" t="n"/>
       <c r="AB34" s="28" t="n"/>
-      <c r="AC34" s="30" t="n"/>
-      <c r="AD34" s="24" t="n"/>
+      <c r="AC34" s="40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD34" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:15:45.654852Z</t>
+        </is>
+      </c>
       <c r="AE34" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.4400 (market_slug=aec-npb-cdh-ybo-2026-08-12). Tie probability=0.0333.</t>
@@ -10862,7 +10977,7 @@
       </c>
       <c r="AG34" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH34" s="24" t="n"/>
@@ -10979,11 +11094,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ34" s="25" t="n"/>
+      <c r="BJ34" s="38" t="n"/>
       <c r="BK34" s="26" t="n">
         <v>127</v>
       </c>
-      <c r="BL34" s="27" t="n">
+      <c r="BL34" s="39" t="n">
         <v>2.27</v>
       </c>
       <c r="BM34" s="28" t="n">
@@ -10991,16 +11106,16 @@
       </c>
       <c r="BN34" s="28" t="n"/>
       <c r="BO34" s="28" t="n"/>
-      <c r="BP34" s="25" t="n"/>
-      <c r="BQ34" s="27" t="n"/>
+      <c r="BP34" s="38" t="n"/>
+      <c r="BQ34" s="39" t="n"/>
       <c r="BR34" s="28" t="n"/>
       <c r="BS34" s="28" t="n"/>
       <c r="BT34" s="28" t="n"/>
-      <c r="BU34" s="25" t="n"/>
+      <c r="BU34" s="38" t="n"/>
       <c r="BV34" s="29" t="n"/>
       <c r="BW34" s="24" t="n"/>
-      <c r="BX34" s="30" t="n"/>
-      <c r="BY34" s="27" t="n"/>
+      <c r="BX34" s="40" t="n"/>
+      <c r="BY34" s="39" t="n"/>
       <c r="BZ34" s="24" t="n"/>
       <c r="CA34" s="31" t="n"/>
       <c r="CB34" s="24" t="n"/>
@@ -11072,7 +11187,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J35" s="25" t="n"/>
+      <c r="J35" s="38" t="n"/>
       <c r="K35" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -11081,7 +11196,7 @@
       <c r="L35" s="26" t="n">
         <v>-203</v>
       </c>
-      <c r="M35" s="27" t="n">
+      <c r="M35" s="39" t="n">
         <v>1.492611</v>
       </c>
       <c r="N35" s="28" t="n">
@@ -11107,18 +11222,32 @@
       </c>
       <c r="U35" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V35" s="24" t="n"/>
-      <c r="W35" s="26" t="n"/>
-      <c r="X35" s="26" t="n"/>
-      <c r="Y35" s="25" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V35" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W35" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="X35" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y35" s="38" t="n"/>
       <c r="Z35" s="26" t="n"/>
       <c r="AA35" s="28" t="n"/>
       <c r="AB35" s="28" t="n"/>
-      <c r="AC35" s="30" t="n"/>
-      <c r="AD35" s="24" t="n"/>
+      <c r="AC35" s="40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD35" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:15:45.796432Z</t>
+        </is>
+      </c>
       <c r="AE35" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.6700 (market_slug=aec-npb-nhf-ssl-2026-08-12). Tie probability=0.0303.</t>
@@ -11131,7 +11260,7 @@
       </c>
       <c r="AG35" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH35" s="24" t="n"/>
@@ -11248,11 +11377,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ35" s="25" t="n"/>
+      <c r="BJ35" s="38" t="n"/>
       <c r="BK35" s="26" t="n">
         <v>-203</v>
       </c>
-      <c r="BL35" s="27" t="n">
+      <c r="BL35" s="39" t="n">
         <v>1.492611</v>
       </c>
       <c r="BM35" s="28" t="n">
@@ -11260,16 +11389,16 @@
       </c>
       <c r="BN35" s="28" t="n"/>
       <c r="BO35" s="28" t="n"/>
-      <c r="BP35" s="25" t="n"/>
-      <c r="BQ35" s="27" t="n"/>
+      <c r="BP35" s="38" t="n"/>
+      <c r="BQ35" s="39" t="n"/>
       <c r="BR35" s="28" t="n"/>
       <c r="BS35" s="28" t="n"/>
       <c r="BT35" s="28" t="n"/>
-      <c r="BU35" s="25" t="n"/>
+      <c r="BU35" s="38" t="n"/>
       <c r="BV35" s="29" t="n"/>
       <c r="BW35" s="24" t="n"/>
-      <c r="BX35" s="30" t="n"/>
-      <c r="BY35" s="27" t="n"/>
+      <c r="BX35" s="40" t="n"/>
+      <c r="BY35" s="39" t="n"/>
       <c r="BZ35" s="24" t="n"/>
       <c r="CA35" s="31" t="n"/>
       <c r="CB35" s="24" t="n"/>
@@ -11341,7 +11470,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J36" s="25" t="n"/>
+      <c r="J36" s="38" t="n"/>
       <c r="K36" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -11350,7 +11479,7 @@
       <c r="L36" s="26" t="n">
         <v>-113</v>
       </c>
-      <c r="M36" s="27" t="n">
+      <c r="M36" s="39" t="n">
         <v>1.884956</v>
       </c>
       <c r="N36" s="28" t="n">
@@ -11376,18 +11505,32 @@
       </c>
       <c r="U36" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V36" s="24" t="n"/>
-      <c r="W36" s="26" t="n"/>
-      <c r="X36" s="26" t="n"/>
-      <c r="Y36" s="25" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V36" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W36" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="X36" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y36" s="38" t="n"/>
       <c r="Z36" s="26" t="n"/>
       <c r="AA36" s="28" t="n"/>
       <c r="AB36" s="28" t="n"/>
-      <c r="AC36" s="30" t="n"/>
-      <c r="AD36" s="24" t="n"/>
+      <c r="AC36" s="40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD36" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:15:45.937916Z</t>
+        </is>
+      </c>
       <c r="AE36" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.5300 (market_slug=aec-npb-trge-obr-2026-08-12). Tie probability=0.0349.</t>
@@ -11400,7 +11543,7 @@
       </c>
       <c r="AG36" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH36" s="24" t="n"/>
@@ -11517,11 +11660,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ36" s="25" t="n"/>
+      <c r="BJ36" s="38" t="n"/>
       <c r="BK36" s="26" t="n">
         <v>-113</v>
       </c>
-      <c r="BL36" s="27" t="n">
+      <c r="BL36" s="39" t="n">
         <v>1.884956</v>
       </c>
       <c r="BM36" s="28" t="n">
@@ -11529,16 +11672,16 @@
       </c>
       <c r="BN36" s="28" t="n"/>
       <c r="BO36" s="28" t="n"/>
-      <c r="BP36" s="25" t="n"/>
-      <c r="BQ36" s="27" t="n"/>
+      <c r="BP36" s="38" t="n"/>
+      <c r="BQ36" s="39" t="n"/>
       <c r="BR36" s="28" t="n"/>
       <c r="BS36" s="28" t="n"/>
       <c r="BT36" s="28" t="n"/>
-      <c r="BU36" s="25" t="n"/>
+      <c r="BU36" s="38" t="n"/>
       <c r="BV36" s="29" t="n"/>
       <c r="BW36" s="24" t="n"/>
-      <c r="BX36" s="30" t="n"/>
-      <c r="BY36" s="27" t="n"/>
+      <c r="BX36" s="40" t="n"/>
+      <c r="BY36" s="39" t="n"/>
       <c r="BZ36" s="24" t="n"/>
       <c r="CA36" s="31" t="n"/>
       <c r="CB36" s="24" t="n"/>
@@ -11610,7 +11753,7 @@
           <t>home</t>
         </is>
       </c>
-      <c r="J37" s="25" t="n"/>
+      <c r="J37" s="38" t="n"/>
       <c r="K37" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -11619,7 +11762,7 @@
       <c r="L37" s="26" t="n">
         <v>-257</v>
       </c>
-      <c r="M37" s="27" t="n">
+      <c r="M37" s="39" t="n">
         <v>1.389105</v>
       </c>
       <c r="N37" s="28" t="n">
@@ -11645,18 +11788,32 @@
       </c>
       <c r="U37" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V37" s="24" t="n"/>
-      <c r="W37" s="26" t="n"/>
-      <c r="X37" s="26" t="n"/>
-      <c r="Y37" s="25" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V37" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W37" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="X37" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y37" s="38" t="n"/>
       <c r="Z37" s="26" t="n"/>
       <c r="AA37" s="28" t="n"/>
       <c r="AB37" s="28" t="n"/>
-      <c r="AC37" s="30" t="n"/>
-      <c r="AD37" s="24" t="n"/>
+      <c r="AC37" s="40" t="n">
+        <v>0.6808999999999999</v>
+      </c>
+      <c r="AD37" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:15:46.081630Z</t>
+        </is>
+      </c>
       <c r="AE37" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.7200 (market_slug=aec-npb-fsh-clm-2026-08-12). Tie probability=0.0224.</t>
@@ -11786,11 +11943,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ37" s="25" t="n"/>
+      <c r="BJ37" s="38" t="n"/>
       <c r="BK37" s="26" t="n">
         <v>-257</v>
       </c>
-      <c r="BL37" s="27" t="n">
+      <c r="BL37" s="39" t="n">
         <v>1.389105</v>
       </c>
       <c r="BM37" s="28" t="n">
@@ -11798,16 +11955,16 @@
       </c>
       <c r="BN37" s="28" t="n"/>
       <c r="BO37" s="28" t="n"/>
-      <c r="BP37" s="25" t="n"/>
-      <c r="BQ37" s="27" t="n"/>
+      <c r="BP37" s="38" t="n"/>
+      <c r="BQ37" s="39" t="n"/>
       <c r="BR37" s="28" t="n"/>
       <c r="BS37" s="28" t="n"/>
       <c r="BT37" s="28" t="n"/>
-      <c r="BU37" s="25" t="n"/>
+      <c r="BU37" s="38" t="n"/>
       <c r="BV37" s="29" t="n"/>
       <c r="BW37" s="24" t="n"/>
-      <c r="BX37" s="30" t="n"/>
-      <c r="BY37" s="27" t="n"/>
+      <c r="BX37" s="40" t="n"/>
+      <c r="BY37" s="39" t="n"/>
       <c r="BZ37" s="24" t="n"/>
       <c r="CA37" s="31" t="n"/>
       <c r="CB37" s="24" t="n"/>
@@ -11879,7 +12036,7 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J38" s="25" t="n"/>
+      <c r="J38" s="38" t="n"/>
       <c r="K38" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
@@ -11888,7 +12045,7 @@
       <c r="L38" s="26" t="n">
         <v>-127</v>
       </c>
-      <c r="M38" s="27" t="n">
+      <c r="M38" s="39" t="n">
         <v>1.787402</v>
       </c>
       <c r="N38" s="28" t="n">
@@ -11914,18 +12071,32 @@
       </c>
       <c r="U38" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V38" s="24" t="n"/>
-      <c r="W38" s="26" t="n"/>
-      <c r="X38" s="26" t="n"/>
-      <c r="Y38" s="25" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V38" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W38" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y38" s="38" t="n"/>
       <c r="Z38" s="26" t="n"/>
       <c r="AA38" s="28" t="n"/>
       <c r="AB38" s="28" t="n"/>
-      <c r="AC38" s="30" t="n"/>
-      <c r="AD38" s="24" t="n"/>
+      <c r="AC38" s="40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD38" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:15:46.267272Z</t>
+        </is>
+      </c>
       <c r="AE38" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.5600 (market_slug=aec-npb-tys-hci-2026-08-12). Tie probability=0.0347.</t>
@@ -11938,7 +12109,7 @@
       </c>
       <c r="AG38" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH38" s="24" t="n"/>
@@ -12055,11 +12226,11 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ38" s="25" t="n"/>
+      <c r="BJ38" s="38" t="n"/>
       <c r="BK38" s="26" t="n">
         <v>-127</v>
       </c>
-      <c r="BL38" s="27" t="n">
+      <c r="BL38" s="39" t="n">
         <v>1.787402</v>
       </c>
       <c r="BM38" s="28" t="n">
@@ -12067,16 +12238,16 @@
       </c>
       <c r="BN38" s="28" t="n"/>
       <c r="BO38" s="28" t="n"/>
-      <c r="BP38" s="25" t="n"/>
-      <c r="BQ38" s="27" t="n"/>
+      <c r="BP38" s="38" t="n"/>
+      <c r="BQ38" s="39" t="n"/>
       <c r="BR38" s="28" t="n"/>
       <c r="BS38" s="28" t="n"/>
       <c r="BT38" s="28" t="n"/>
-      <c r="BU38" s="25" t="n"/>
+      <c r="BU38" s="38" t="n"/>
       <c r="BV38" s="29" t="n"/>
       <c r="BW38" s="24" t="n"/>
-      <c r="BX38" s="30" t="n"/>
-      <c r="BY38" s="27" t="n"/>
+      <c r="BX38" s="40" t="n"/>
+      <c r="BY38" s="39" t="n"/>
       <c r="BZ38" s="24" t="n"/>
       <c r="CA38" s="31" t="n"/>
       <c r="CB38" s="24" t="n"/>
@@ -12102,6 +12273,1620 @@
         </is>
       </c>
     </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>a17ab5132e4a416c</t>
+        </is>
+      </c>
+      <c r="B39" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:32:37.449638Z</t>
+        </is>
+      </c>
+      <c r="C39" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D39" s="24" t="inlineStr">
+        <is>
+          <t>77187</t>
+        </is>
+      </c>
+      <c r="E39" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F39" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="G39" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="H39" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I39" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J39" s="38" t="n"/>
+      <c r="K39" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L39" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M39" s="39" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="N39" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="O39" s="28" t="n">
+        <v>0.50388</v>
+      </c>
+      <c r="P39" s="28" t="n"/>
+      <c r="Q39" s="28" t="n">
+        <v>-0.015351</v>
+      </c>
+      <c r="R39" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="S39" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T39" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U39" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V39" s="24" t="n"/>
+      <c r="W39" s="26" t="n"/>
+      <c r="X39" s="26" t="n"/>
+      <c r="Y39" s="38" t="n"/>
+      <c r="Z39" s="26" t="n"/>
+      <c r="AA39" s="28" t="n"/>
+      <c r="AB39" s="28" t="n"/>
+      <c r="AC39" s="40" t="n"/>
+      <c r="AD39" s="24" t="n"/>
+      <c r="AE39" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5200 (market_slug=aec-npb-ygo-hta-2026-08-13). Tie probability=0.0358.</t>
+        </is>
+      </c>
+      <c r="AF39" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG39" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH39" s="24" t="n"/>
+      <c r="AI39" s="31" t="n"/>
+      <c r="AJ39" s="31" t="n"/>
+      <c r="AK39" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL39" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM39" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN39" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO39" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP39" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AQ39" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AR39" s="24" t="inlineStr">
+        <is>
+          <t>Hanshin Tigers</t>
+        </is>
+      </c>
+      <c r="AS39" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="AT39" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="AU39" s="24" t="inlineStr">
+        <is>
+          <t>Yomiuri Giants</t>
+        </is>
+      </c>
+      <c r="AV39" s="24" t="n"/>
+      <c r="AW39" s="24" t="n"/>
+      <c r="AX39" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY39" s="24" t="n"/>
+      <c r="AZ39" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA39" s="24" t="inlineStr">
+        <is>
+          <t>73d0572d55d5e962df216a5bc7e253f751021ae8c682a42661cae540d10ca7e1</t>
+        </is>
+      </c>
+      <c r="BB39" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC39" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD39" s="24" t="inlineStr">
+        <is>
+          <t>73d0572d55d5e962df216a5bc7e253f751021ae8c682a42661cae540d10ca7e1</t>
+        </is>
+      </c>
+      <c r="BE39" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF39" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG39" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH39" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:32:34.900584Z</t>
+        </is>
+      </c>
+      <c r="BI39" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ39" s="38" t="n"/>
+      <c r="BK39" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="BL39" s="39" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="BM39" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="BN39" s="28" t="n"/>
+      <c r="BO39" s="28" t="n"/>
+      <c r="BP39" s="38" t="n"/>
+      <c r="BQ39" s="39" t="n"/>
+      <c r="BR39" s="28" t="n"/>
+      <c r="BS39" s="28" t="n"/>
+      <c r="BT39" s="28" t="n"/>
+      <c r="BU39" s="38" t="n"/>
+      <c r="BV39" s="29" t="n"/>
+      <c r="BW39" s="24" t="n"/>
+      <c r="BX39" s="40" t="n"/>
+      <c r="BY39" s="39" t="n"/>
+      <c r="BZ39" s="24" t="n"/>
+      <c r="CA39" s="31" t="n"/>
+      <c r="CB39" s="24" t="n"/>
+      <c r="CC39" s="24" t="n"/>
+      <c r="CD39" s="24" t="n"/>
+      <c r="CE39" s="24" t="n"/>
+      <c r="CF39" s="24" t="n"/>
+      <c r="CG39" s="24" t="n"/>
+      <c r="CH39" s="24" t="n"/>
+      <c r="CI39" s="24" t="n"/>
+      <c r="CJ39" s="24" t="n"/>
+      <c r="CK39" s="24" t="n"/>
+      <c r="CL39" s="24" t="n"/>
+      <c r="CM39" s="24" t="n"/>
+      <c r="CN39" s="24" t="n"/>
+      <c r="CO39" s="24" t="n"/>
+      <c r="CP39" s="24" t="n"/>
+      <c r="CQ39" s="24" t="n"/>
+      <c r="CR39" s="24" t="n"/>
+      <c r="CS39" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="36" customHeight="1">
+      <c r="A40" s="24" t="inlineStr">
+        <is>
+          <t>7118096a03f74add</t>
+        </is>
+      </c>
+      <c r="B40" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:32:37.449638Z</t>
+        </is>
+      </c>
+      <c r="C40" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D40" s="24" t="inlineStr">
+        <is>
+          <t>77188</t>
+        </is>
+      </c>
+      <c r="E40" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F40" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="G40" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="H40" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I40" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J40" s="38" t="n"/>
+      <c r="K40" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L40" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="M40" s="39" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="N40" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="O40" s="28" t="n">
+        <v>0.50975</v>
+      </c>
+      <c r="P40" s="28" t="n"/>
+      <c r="Q40" s="28" t="n">
+        <v>-0.0398</v>
+      </c>
+      <c r="R40" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T40" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U40" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V40" s="24" t="n"/>
+      <c r="W40" s="26" t="n"/>
+      <c r="X40" s="26" t="n"/>
+      <c r="Y40" s="38" t="n"/>
+      <c r="Z40" s="26" t="n"/>
+      <c r="AA40" s="28" t="n"/>
+      <c r="AB40" s="28" t="n"/>
+      <c r="AC40" s="40" t="n"/>
+      <c r="AD40" s="24" t="n"/>
+      <c r="AE40" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5500 (market_slug=aec-npb-tys-hci-2026-08-13). Tie probability=0.0353.</t>
+        </is>
+      </c>
+      <c r="AF40" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG40" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH40" s="24" t="n"/>
+      <c r="AI40" s="31" t="n"/>
+      <c r="AJ40" s="31" t="n"/>
+      <c r="AK40" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL40" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM40" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN40" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO40" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP40" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="AQ40" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="AR40" s="24" t="inlineStr">
+        <is>
+          <t>Hiroshima Carp</t>
+        </is>
+      </c>
+      <c r="AS40" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AT40" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AU40" s="24" t="inlineStr">
+        <is>
+          <t>Tokyo Yakult Swallows</t>
+        </is>
+      </c>
+      <c r="AV40" s="24" t="n"/>
+      <c r="AW40" s="24" t="n"/>
+      <c r="AX40" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY40" s="24" t="n"/>
+      <c r="AZ40" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA40" s="24" t="inlineStr">
+        <is>
+          <t>73d0572d55d5e962df216a5bc7e253f751021ae8c682a42661cae540d10ca7e1</t>
+        </is>
+      </c>
+      <c r="BB40" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC40" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD40" s="24" t="inlineStr">
+        <is>
+          <t>73d0572d55d5e962df216a5bc7e253f751021ae8c682a42661cae540d10ca7e1</t>
+        </is>
+      </c>
+      <c r="BE40" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF40" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG40" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH40" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:32:35.510747Z</t>
+        </is>
+      </c>
+      <c r="BI40" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ40" s="38" t="n"/>
+      <c r="BK40" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="BL40" s="39" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="BM40" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="BN40" s="28" t="n"/>
+      <c r="BO40" s="28" t="n"/>
+      <c r="BP40" s="38" t="n"/>
+      <c r="BQ40" s="39" t="n"/>
+      <c r="BR40" s="28" t="n"/>
+      <c r="BS40" s="28" t="n"/>
+      <c r="BT40" s="28" t="n"/>
+      <c r="BU40" s="38" t="n"/>
+      <c r="BV40" s="29" t="n"/>
+      <c r="BW40" s="24" t="n"/>
+      <c r="BX40" s="40" t="n"/>
+      <c r="BY40" s="39" t="n"/>
+      <c r="BZ40" s="24" t="n"/>
+      <c r="CA40" s="31" t="n"/>
+      <c r="CB40" s="24" t="n"/>
+      <c r="CC40" s="24" t="n"/>
+      <c r="CD40" s="24" t="n"/>
+      <c r="CE40" s="24" t="n"/>
+      <c r="CF40" s="24" t="n"/>
+      <c r="CG40" s="24" t="n"/>
+      <c r="CH40" s="24" t="n"/>
+      <c r="CI40" s="24" t="n"/>
+      <c r="CJ40" s="24" t="n"/>
+      <c r="CK40" s="24" t="n"/>
+      <c r="CL40" s="24" t="n"/>
+      <c r="CM40" s="24" t="n"/>
+      <c r="CN40" s="24" t="n"/>
+      <c r="CO40" s="24" t="n"/>
+      <c r="CP40" s="24" t="n"/>
+      <c r="CQ40" s="24" t="n"/>
+      <c r="CR40" s="24" t="n"/>
+      <c r="CS40" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="36" customHeight="1">
+      <c r="A41" s="24" t="inlineStr">
+        <is>
+          <t>83e37e49db7a449f</t>
+        </is>
+      </c>
+      <c r="B41" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:32:37.449638Z</t>
+        </is>
+      </c>
+      <c r="C41" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D41" s="24" t="inlineStr">
+        <is>
+          <t>77189</t>
+        </is>
+      </c>
+      <c r="E41" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F41" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="G41" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="H41" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I41" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J41" s="38" t="n"/>
+      <c r="K41" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L41" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M41" s="39" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="N41" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="O41" s="28" t="n">
+        <v>0.5144570000000001</v>
+      </c>
+      <c r="P41" s="28" t="n"/>
+      <c r="Q41" s="28" t="n">
+        <v>-0.004774</v>
+      </c>
+      <c r="R41" s="26" t="n">
+        <v>18</v>
+      </c>
+      <c r="S41" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T41" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U41" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V41" s="24" t="n"/>
+      <c r="W41" s="26" t="n"/>
+      <c r="X41" s="26" t="n"/>
+      <c r="Y41" s="38" t="n"/>
+      <c r="Z41" s="26" t="n"/>
+      <c r="AA41" s="28" t="n"/>
+      <c r="AB41" s="28" t="n"/>
+      <c r="AC41" s="40" t="n"/>
+      <c r="AD41" s="24" t="n"/>
+      <c r="AE41" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5200 (market_slug=aec-npb-cdh-ybo-2026-08-13). Tie probability=0.0349.</t>
+        </is>
+      </c>
+      <c r="AF41" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG41" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH41" s="24" t="n"/>
+      <c r="AI41" s="31" t="n"/>
+      <c r="AJ41" s="31" t="n"/>
+      <c r="AK41" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL41" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM41" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN41" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO41" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP41" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AQ41" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AR41" s="24" t="inlineStr">
+        <is>
+          <t>Yokohama BayStars</t>
+        </is>
+      </c>
+      <c r="AS41" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="AT41" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="AU41" s="24" t="inlineStr">
+        <is>
+          <t>Chunichi Dragons</t>
+        </is>
+      </c>
+      <c r="AV41" s="24" t="n"/>
+      <c r="AW41" s="24" t="n"/>
+      <c r="AX41" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY41" s="24" t="n"/>
+      <c r="AZ41" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA41" s="24" t="inlineStr">
+        <is>
+          <t>73d0572d55d5e962df216a5bc7e253f751021ae8c682a42661cae540d10ca7e1</t>
+        </is>
+      </c>
+      <c r="BB41" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC41" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD41" s="24" t="inlineStr">
+        <is>
+          <t>73d0572d55d5e962df216a5bc7e253f751021ae8c682a42661cae540d10ca7e1</t>
+        </is>
+      </c>
+      <c r="BE41" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF41" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG41" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH41" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:32:36.017681Z</t>
+        </is>
+      </c>
+      <c r="BI41" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ41" s="38" t="n"/>
+      <c r="BK41" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="BL41" s="39" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="BM41" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="BN41" s="28" t="n"/>
+      <c r="BO41" s="28" t="n"/>
+      <c r="BP41" s="38" t="n"/>
+      <c r="BQ41" s="39" t="n"/>
+      <c r="BR41" s="28" t="n"/>
+      <c r="BS41" s="28" t="n"/>
+      <c r="BT41" s="28" t="n"/>
+      <c r="BU41" s="38" t="n"/>
+      <c r="BV41" s="29" t="n"/>
+      <c r="BW41" s="24" t="n"/>
+      <c r="BX41" s="40" t="n"/>
+      <c r="BY41" s="39" t="n"/>
+      <c r="BZ41" s="24" t="n"/>
+      <c r="CA41" s="31" t="n"/>
+      <c r="CB41" s="24" t="n"/>
+      <c r="CC41" s="24" t="n"/>
+      <c r="CD41" s="24" t="n"/>
+      <c r="CE41" s="24" t="n"/>
+      <c r="CF41" s="24" t="n"/>
+      <c r="CG41" s="24" t="n"/>
+      <c r="CH41" s="24" t="n"/>
+      <c r="CI41" s="24" t="n"/>
+      <c r="CJ41" s="24" t="n"/>
+      <c r="CK41" s="24" t="n"/>
+      <c r="CL41" s="24" t="n"/>
+      <c r="CM41" s="24" t="n"/>
+      <c r="CN41" s="24" t="n"/>
+      <c r="CO41" s="24" t="n"/>
+      <c r="CP41" s="24" t="n"/>
+      <c r="CQ41" s="24" t="n"/>
+      <c r="CR41" s="24" t="n"/>
+      <c r="CS41" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="36" customHeight="1">
+      <c r="A42" s="24" t="inlineStr">
+        <is>
+          <t>a91f4d493230419e</t>
+        </is>
+      </c>
+      <c r="B42" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:32:37.449638Z</t>
+        </is>
+      </c>
+      <c r="C42" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D42" s="24" t="inlineStr">
+        <is>
+          <t>77190</t>
+        </is>
+      </c>
+      <c r="E42" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F42" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="G42" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="H42" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I42" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J42" s="38" t="n"/>
+      <c r="K42" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L42" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="M42" s="39" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="N42" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="O42" s="28" t="n">
+        <v>0.5480120000000001</v>
+      </c>
+      <c r="P42" s="28" t="n"/>
+      <c r="Q42" s="28" t="n">
+        <v>-0.061363</v>
+      </c>
+      <c r="R42" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U42" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V42" s="24" t="n"/>
+      <c r="W42" s="26" t="n"/>
+      <c r="X42" s="26" t="n"/>
+      <c r="Y42" s="38" t="n"/>
+      <c r="Z42" s="26" t="n"/>
+      <c r="AA42" s="28" t="n"/>
+      <c r="AB42" s="28" t="n"/>
+      <c r="AC42" s="40" t="n"/>
+      <c r="AD42" s="24" t="n"/>
+      <c r="AE42" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6100 (market_slug=aec-npb-nhf-ssl-2026-08-13). Tie probability=0.0319.</t>
+        </is>
+      </c>
+      <c r="AF42" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG42" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH42" s="24" t="n"/>
+      <c r="AI42" s="31" t="n"/>
+      <c r="AJ42" s="31" t="n"/>
+      <c r="AK42" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL42" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM42" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN42" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO42" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP42" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AQ42" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AR42" s="24" t="inlineStr">
+        <is>
+          <t>Saitama Seibu Lions</t>
+        </is>
+      </c>
+      <c r="AS42" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AT42" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AU42" s="24" t="inlineStr">
+        <is>
+          <t>Nippon Ham Fighters</t>
+        </is>
+      </c>
+      <c r="AV42" s="24" t="n"/>
+      <c r="AW42" s="24" t="n"/>
+      <c r="AX42" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY42" s="24" t="n"/>
+      <c r="AZ42" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA42" s="24" t="inlineStr">
+        <is>
+          <t>73d0572d55d5e962df216a5bc7e253f751021ae8c682a42661cae540d10ca7e1</t>
+        </is>
+      </c>
+      <c r="BB42" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC42" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD42" s="24" t="inlineStr">
+        <is>
+          <t>73d0572d55d5e962df216a5bc7e253f751021ae8c682a42661cae540d10ca7e1</t>
+        </is>
+      </c>
+      <c r="BE42" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF42" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG42" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH42" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:32:36.479497Z</t>
+        </is>
+      </c>
+      <c r="BI42" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ42" s="38" t="n"/>
+      <c r="BK42" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="BL42" s="39" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BM42" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="BN42" s="28" t="n"/>
+      <c r="BO42" s="28" t="n"/>
+      <c r="BP42" s="38" t="n"/>
+      <c r="BQ42" s="39" t="n"/>
+      <c r="BR42" s="28" t="n"/>
+      <c r="BS42" s="28" t="n"/>
+      <c r="BT42" s="28" t="n"/>
+      <c r="BU42" s="38" t="n"/>
+      <c r="BV42" s="29" t="n"/>
+      <c r="BW42" s="24" t="n"/>
+      <c r="BX42" s="40" t="n"/>
+      <c r="BY42" s="39" t="n"/>
+      <c r="BZ42" s="24" t="n"/>
+      <c r="CA42" s="31" t="n"/>
+      <c r="CB42" s="24" t="n"/>
+      <c r="CC42" s="24" t="n"/>
+      <c r="CD42" s="24" t="n"/>
+      <c r="CE42" s="24" t="n"/>
+      <c r="CF42" s="24" t="n"/>
+      <c r="CG42" s="24" t="n"/>
+      <c r="CH42" s="24" t="n"/>
+      <c r="CI42" s="24" t="n"/>
+      <c r="CJ42" s="24" t="n"/>
+      <c r="CK42" s="24" t="n"/>
+      <c r="CL42" s="24" t="n"/>
+      <c r="CM42" s="24" t="n"/>
+      <c r="CN42" s="24" t="n"/>
+      <c r="CO42" s="24" t="n"/>
+      <c r="CP42" s="24" t="n"/>
+      <c r="CQ42" s="24" t="n"/>
+      <c r="CR42" s="24" t="n"/>
+      <c r="CS42" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="36" customHeight="1">
+      <c r="A43" s="24" t="inlineStr">
+        <is>
+          <t>634f5e09a84d49d4</t>
+        </is>
+      </c>
+      <c r="B43" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:32:37.449638Z</t>
+        </is>
+      </c>
+      <c r="C43" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D43" s="24" t="inlineStr">
+        <is>
+          <t>77186</t>
+        </is>
+      </c>
+      <c r="E43" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F43" s="24" t="inlineStr">
+        <is>
+          <t>Orix Buffaloes</t>
+        </is>
+      </c>
+      <c r="G43" s="24" t="inlineStr">
+        <is>
+          <t>Tohoku Rakuten Golden Eagles</t>
+        </is>
+      </c>
+      <c r="H43" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I43" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J43" s="38" t="n"/>
+      <c r="K43" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L43" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="M43" s="39" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="N43" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="O43" s="28" t="n">
+        <v>0.507038</v>
+      </c>
+      <c r="P43" s="28" t="n"/>
+      <c r="Q43" s="28" t="n">
+        <v>-0.042512</v>
+      </c>
+      <c r="R43" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T43" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U43" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V43" s="24" t="n"/>
+      <c r="W43" s="26" t="n"/>
+      <c r="X43" s="26" t="n"/>
+      <c r="Y43" s="38" t="n"/>
+      <c r="Z43" s="26" t="n"/>
+      <c r="AA43" s="28" t="n"/>
+      <c r="AB43" s="28" t="n"/>
+      <c r="AC43" s="40" t="n"/>
+      <c r="AD43" s="24" t="n"/>
+      <c r="AE43" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5500 (market_slug=aec-npb-trge-obr-2026-08-13). Tie probability=0.0355.</t>
+        </is>
+      </c>
+      <c r="AF43" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG43" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH43" s="24" t="n"/>
+      <c r="AI43" s="31" t="n"/>
+      <c r="AJ43" s="31" t="n"/>
+      <c r="AK43" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL43" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM43" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN43" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO43" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP43" s="24" t="inlineStr">
+        <is>
+          <t>Orix Buffaloes</t>
+        </is>
+      </c>
+      <c r="AQ43" s="24" t="inlineStr">
+        <is>
+          <t>Orix Buffaloes</t>
+        </is>
+      </c>
+      <c r="AR43" s="24" t="inlineStr">
+        <is>
+          <t>Orix Buffaloes</t>
+        </is>
+      </c>
+      <c r="AS43" s="24" t="inlineStr">
+        <is>
+          <t>Tohoku Rakuten Golden Eagles</t>
+        </is>
+      </c>
+      <c r="AT43" s="24" t="inlineStr">
+        <is>
+          <t>Tohoku Rakuten Golden Eagles</t>
+        </is>
+      </c>
+      <c r="AU43" s="24" t="inlineStr">
+        <is>
+          <t>Tohoku Rakuten Golden Eagles</t>
+        </is>
+      </c>
+      <c r="AV43" s="24" t="n"/>
+      <c r="AW43" s="24" t="n"/>
+      <c r="AX43" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY43" s="24" t="n"/>
+      <c r="AZ43" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA43" s="24" t="inlineStr">
+        <is>
+          <t>73d0572d55d5e962df216a5bc7e253f751021ae8c682a42661cae540d10ca7e1</t>
+        </is>
+      </c>
+      <c r="BB43" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC43" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD43" s="24" t="inlineStr">
+        <is>
+          <t>73d0572d55d5e962df216a5bc7e253f751021ae8c682a42661cae540d10ca7e1</t>
+        </is>
+      </c>
+      <c r="BE43" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF43" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG43" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH43" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:32:36.966712Z</t>
+        </is>
+      </c>
+      <c r="BI43" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ43" s="38" t="n"/>
+      <c r="BK43" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="BL43" s="39" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="BM43" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="BN43" s="28" t="n"/>
+      <c r="BO43" s="28" t="n"/>
+      <c r="BP43" s="38" t="n"/>
+      <c r="BQ43" s="39" t="n"/>
+      <c r="BR43" s="28" t="n"/>
+      <c r="BS43" s="28" t="n"/>
+      <c r="BT43" s="28" t="n"/>
+      <c r="BU43" s="38" t="n"/>
+      <c r="BV43" s="29" t="n"/>
+      <c r="BW43" s="24" t="n"/>
+      <c r="BX43" s="40" t="n"/>
+      <c r="BY43" s="39" t="n"/>
+      <c r="BZ43" s="24" t="n"/>
+      <c r="CA43" s="31" t="n"/>
+      <c r="CB43" s="24" t="n"/>
+      <c r="CC43" s="24" t="n"/>
+      <c r="CD43" s="24" t="n"/>
+      <c r="CE43" s="24" t="n"/>
+      <c r="CF43" s="24" t="n"/>
+      <c r="CG43" s="24" t="n"/>
+      <c r="CH43" s="24" t="n"/>
+      <c r="CI43" s="24" t="n"/>
+      <c r="CJ43" s="24" t="n"/>
+      <c r="CK43" s="24" t="n"/>
+      <c r="CL43" s="24" t="n"/>
+      <c r="CM43" s="24" t="n"/>
+      <c r="CN43" s="24" t="n"/>
+      <c r="CO43" s="24" t="n"/>
+      <c r="CP43" s="24" t="n"/>
+      <c r="CQ43" s="24" t="n"/>
+      <c r="CR43" s="24" t="n"/>
+      <c r="CS43" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="36" customHeight="1">
+      <c r="A44" s="24" t="inlineStr">
+        <is>
+          <t>24acc1da6c4a4dae</t>
+        </is>
+      </c>
+      <c r="B44" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:32:37.449638Z</t>
+        </is>
+      </c>
+      <c r="C44" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D44" s="24" t="inlineStr">
+        <is>
+          <t>77191</t>
+        </is>
+      </c>
+      <c r="E44" s="24" t="inlineStr">
+        <is>
+          <t>NPB</t>
+        </is>
+      </c>
+      <c r="F44" s="24" t="inlineStr">
+        <is>
+          <t>Chiba Lotte Marines</t>
+        </is>
+      </c>
+      <c r="G44" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="H44" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I44" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J44" s="38" t="n"/>
+      <c r="K44" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L44" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="M44" s="39" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="N44" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="O44" s="28" t="n">
+        <v>0.666743</v>
+      </c>
+      <c r="P44" s="28" t="n"/>
+      <c r="Q44" s="28" t="n">
+        <v>-0.003224</v>
+      </c>
+      <c r="R44" s="26" t="n">
+        <v>18</v>
+      </c>
+      <c r="S44" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T44" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U44" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V44" s="24" t="n"/>
+      <c r="W44" s="26" t="n"/>
+      <c r="X44" s="26" t="n"/>
+      <c r="Y44" s="38" t="n"/>
+      <c r="Z44" s="26" t="n"/>
+      <c r="AA44" s="28" t="n"/>
+      <c r="AB44" s="28" t="n"/>
+      <c r="AC44" s="40" t="n"/>
+      <c r="AD44" s="24" t="n"/>
+      <c r="AE44" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6700 (market_slug=aec-npb-fsh-clm-2026-08-13). Tie probability=0.0213.</t>
+        </is>
+      </c>
+      <c r="AF44" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG44" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH44" s="24" t="n"/>
+      <c r="AI44" s="31" t="n"/>
+      <c r="AJ44" s="31" t="n"/>
+      <c r="AK44" s="24" t="inlineStr">
+        <is>
+          <t>research_observation</t>
+        </is>
+      </c>
+      <c r="AL44" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM44" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN44" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL</t>
+        </is>
+      </c>
+      <c r="AO44" s="24" t="inlineStr">
+        <is>
+          <t>NO_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP44" s="24" t="inlineStr">
+        <is>
+          <t>Chiba Lotte Marines</t>
+        </is>
+      </c>
+      <c r="AQ44" s="24" t="inlineStr">
+        <is>
+          <t>Chiba Lotte Marines</t>
+        </is>
+      </c>
+      <c r="AR44" s="24" t="inlineStr">
+        <is>
+          <t>Chiba Lotte Marines</t>
+        </is>
+      </c>
+      <c r="AS44" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="AT44" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="AU44" s="24" t="inlineStr">
+        <is>
+          <t>Fukuoka SoftBank Hawks</t>
+        </is>
+      </c>
+      <c r="AV44" s="24" t="n"/>
+      <c r="AW44" s="24" t="n"/>
+      <c r="AX44" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY44" s="24" t="n"/>
+      <c r="AZ44" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA44" s="24" t="inlineStr">
+        <is>
+          <t>73d0572d55d5e962df216a5bc7e253f751021ae8c682a42661cae540d10ca7e1</t>
+        </is>
+      </c>
+      <c r="BB44" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC44" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD44" s="24" t="inlineStr">
+        <is>
+          <t>73d0572d55d5e962df216a5bc7e253f751021ae8c682a42661cae540d10ca7e1</t>
+        </is>
+      </c>
+      <c r="BE44" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF44" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG44" s="24" t="inlineStr">
+        <is>
+          <t>npb-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH44" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T07:32:37.449581Z</t>
+        </is>
+      </c>
+      <c r="BI44" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ44" s="38" t="n"/>
+      <c r="BK44" s="26" t="n">
+        <v>-203</v>
+      </c>
+      <c r="BL44" s="39" t="n">
+        <v>1.492611</v>
+      </c>
+      <c r="BM44" s="28" t="n">
+        <v>0.669967</v>
+      </c>
+      <c r="BN44" s="28" t="n"/>
+      <c r="BO44" s="28" t="n"/>
+      <c r="BP44" s="38" t="n"/>
+      <c r="BQ44" s="39" t="n"/>
+      <c r="BR44" s="28" t="n"/>
+      <c r="BS44" s="28" t="n"/>
+      <c r="BT44" s="28" t="n"/>
+      <c r="BU44" s="38" t="n"/>
+      <c r="BV44" s="29" t="n"/>
+      <c r="BW44" s="24" t="n"/>
+      <c r="BX44" s="40" t="n"/>
+      <c r="BY44" s="39" t="n"/>
+      <c r="BZ44" s="24" t="n"/>
+      <c r="CA44" s="31" t="n"/>
+      <c r="CB44" s="24" t="n"/>
+      <c r="CC44" s="24" t="n"/>
+      <c r="CD44" s="24" t="n"/>
+      <c r="CE44" s="24" t="n"/>
+      <c r="CF44" s="24" t="n"/>
+      <c r="CG44" s="24" t="n"/>
+      <c r="CH44" s="24" t="n"/>
+      <c r="CI44" s="24" t="n"/>
+      <c r="CJ44" s="24" t="n"/>
+      <c r="CK44" s="24" t="n"/>
+      <c r="CL44" s="24" t="n"/>
+      <c r="CM44" s="24" t="n"/>
+      <c r="CN44" s="24" t="n"/>
+      <c r="CO44" s="24" t="n"/>
+      <c r="CP44" s="24" t="n"/>
+      <c r="CQ44" s="24" t="n"/>
+      <c r="CR44" s="24" t="n"/>
+      <c r="CS44" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
